--- a/docs/scrum/SIGRO - Product Backlog y Sprint Backlog.xlsx
+++ b/docs/scrum/SIGRO - Product Backlog y Sprint Backlog.xlsx
@@ -12,9 +12,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tarjetas DoR y DoD" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Criterios DoR y DoD" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Sprint Backlog" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Historias técnicas" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'2. Tarjetas DoR y DoD'!$A$1:$P$1747</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2. Tarjetas DoR y DoD'!$A$1:$P$1955</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -294,7 +295,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -399,6 +400,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -412,6 +416,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -779,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E72"/>
+  <dimension ref="B2:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2059,11 +2066,153 @@
         </is>
       </c>
     </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>HT. Historias técnicas (habilitadoras)</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>HT-01</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero un ambiente de pruebas desplegado con la API, la base de datos y la web, para que cada HU se pruebe y se acepte fuera de la máquina de quien la programó.</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>Desplegar el ambiente de pruebas</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="32" customHeight="1">
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>HT-02</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero que cada Pull Request compile y corra las pruebas automáticamente, para detectar un error antes de que llegue a main.</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Configurar la integración continua</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="32" customHeight="1">
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>HT-03</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero el repositorio privado y la rama main protegida, para que los datos del cliente no queden expuestos y nada entre sin revisión.</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>Proteger el repositorio y main</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="32" customHeight="1">
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>HT-04</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero un cliente HTTP único en la web que hable con la API, para conectar todas las pantallas sin rehacerlas.</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Conectar la web con la API real</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="32" customHeight="1">
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>HT-05</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero el proyecto base de la app con Compose, Room, WorkManager, sesión y cliente de la API, para construir encima las pantallas del almacenero.</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>Crear la base de la app Android</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="32" customHeight="1">
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>HT-06</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero el contrato de la API publicado (OpenAPI) y una colección de Postman compartida, para probar cada endpoint igual y sin adivinar cómo llamarlo.</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>Publicar el contrato de la API y Postman</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="32" customHeight="1">
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>HT-07</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero la base de pruebas cargada con los datos reales del cliente, para que ninguna HU se pruebe con datos inventados.</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>Cargar los datos de prueba reales</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="32" customHeight="1">
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>HT-08</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero que Integraciones y Notificaciones solo atiendan a la API con un token de servicio, para que nadie gaste las consultas de Factiliza ni envíe avisos falsos.</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>Autenticar a los servicios entre sí</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="B6:B20"/>
     <mergeCell ref="B62:B68"/>
     <mergeCell ref="B69:B72"/>
+    <mergeCell ref="B73:B80"/>
     <mergeCell ref="B55:B61"/>
     <mergeCell ref="B21:B35"/>
     <mergeCell ref="B3:E3"/>
@@ -5842,7 +5991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:O1744"/>
+  <dimension ref="B2:O1952"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -5873,7 +6022,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>67 historias · 201 tarjetas · una historia por página al imprimir · criterios completos en la hoja «3. Criterios DoR y DoD»</t>
+          <t>67 historias de usuario + 8 técnicas · 225 tarjetas · una historia por página al imprimir · criterios completos en la hoja «3. Criterios DoR y DoD»</t>
         </is>
       </c>
     </row>
@@ -41280,15 +41429,4257 @@
       <c r="I1744" s="37" t="n"/>
       <c r="J1744" s="38" t="n"/>
     </row>
+    <row r="1747">
+      <c r="B1747" s="18" t="inlineStr">
+        <is>
+          <t>HT-01 · Desplegar el ambiente de pruebas (historia técnica)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748" ht="18" customHeight="1">
+      <c r="B1748" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 1 · Historia técnica</t>
+        </is>
+      </c>
+      <c r="C1748" s="20" t="n"/>
+      <c r="D1748" s="20" t="n"/>
+      <c r="E1748" s="21" t="n"/>
+      <c r="G1748" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 2 · Definición de Listo</t>
+        </is>
+      </c>
+      <c r="H1748" s="20" t="n"/>
+      <c r="I1748" s="20" t="n"/>
+      <c r="J1748" s="21" t="n"/>
+      <c r="L1748" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 3 · Definición de Terminado</t>
+        </is>
+      </c>
+      <c r="M1748" s="20" t="n"/>
+      <c r="N1748" s="20" t="n"/>
+      <c r="O1748" s="21" t="n"/>
+    </row>
+    <row r="1749" ht="28" customHeight="1">
+      <c r="B1749" s="22" t="inlineStr">
+        <is>
+          <t>Habilita a las HU de usuario: no entrega una función al usuario final</t>
+        </is>
+      </c>
+      <c r="C1749" s="8" t="n"/>
+      <c r="D1749" s="8" t="n"/>
+      <c r="E1749" s="23" t="n"/>
+      <c r="G1749" s="22" t="inlineStr">
+        <is>
+          <t>El enfoque está en la consideración del equipo de desarrollo sobre si la historia está lista para un Sprint</t>
+        </is>
+      </c>
+      <c r="H1749" s="8" t="n"/>
+      <c r="I1749" s="8" t="n"/>
+      <c r="J1749" s="23" t="n"/>
+      <c r="L1749" s="22" t="inlineStr">
+        <is>
+          <t>El enfoque está en la aceptación del cliente cuando se le entregue el producto</t>
+        </is>
+      </c>
+      <c r="M1749" s="8" t="n"/>
+      <c r="N1749" s="8" t="n"/>
+      <c r="O1749" s="23" t="n"/>
+    </row>
+    <row r="1750">
+      <c r="B1750" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="C1750" s="8" t="n"/>
+      <c r="D1750" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="E1750" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="G1750" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="H1750" s="8" t="n"/>
+      <c r="I1750" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="J1750" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="L1750" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="M1750" s="8" t="n"/>
+      <c r="N1750" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="O1750" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751" ht="30" customHeight="1">
+      <c r="B1751" s="27" t="inlineStr">
+        <is>
+          <t>HT-01 · Desplegar el ambiente de pruebas</t>
+        </is>
+      </c>
+      <c r="C1751" s="8" t="n"/>
+      <c r="D1751" s="9" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="E1751" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+      <c r="G1751" s="27" t="inlineStr">
+        <is>
+          <t>HT-01 · Desplegar el ambiente de pruebas</t>
+        </is>
+      </c>
+      <c r="H1751" s="8" t="n"/>
+      <c r="I1751" s="9" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J1751" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+      <c r="L1751" s="27" t="inlineStr">
+        <is>
+          <t>HT-01 · Desplegar el ambiente de pruebas</t>
+        </is>
+      </c>
+      <c r="M1751" s="8" t="n"/>
+      <c r="N1751" s="9" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="O1751" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="B1752" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="C1752" s="8" t="n"/>
+      <c r="D1752" s="8" t="n"/>
+      <c r="E1752" s="23" t="n"/>
+      <c r="G1752" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="H1752" s="8" t="n"/>
+      <c r="I1752" s="8" t="n"/>
+      <c r="J1752" s="23" t="n"/>
+      <c r="L1752" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="M1752" s="8" t="n"/>
+      <c r="N1752" s="8" t="n"/>
+      <c r="O1752" s="23" t="n"/>
+    </row>
+    <row r="1753" ht="28" customHeight="1">
+      <c r="B1753" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero un ambiente de pruebas desplegado con la API, la base de datos y la web, para que cada HU se pruebe y se acepte fuera de la máquina de quien la programó.</t>
+        </is>
+      </c>
+      <c r="C1753" s="8" t="n"/>
+      <c r="D1753" s="8" t="n"/>
+      <c r="E1753" s="23" t="n"/>
+      <c r="G1753" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero un ambiente de pruebas desplegado con la API, la base de datos y la web, para que cada HU se pruebe y se acepte fuera de la máquina de quien la programó.</t>
+        </is>
+      </c>
+      <c r="H1753" s="8" t="n"/>
+      <c r="I1753" s="8" t="n"/>
+      <c r="J1753" s="23" t="n"/>
+      <c r="L1753" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero un ambiente de pruebas desplegado con la API, la base de datos y la web, para que cada HU se pruebe y se acepte fuera de la máquina de quien la programó.</t>
+        </is>
+      </c>
+      <c r="M1753" s="8" t="n"/>
+      <c r="N1753" s="8" t="n"/>
+      <c r="O1753" s="23" t="n"/>
+    </row>
+    <row r="1754" ht="28" customHeight="1">
+      <c r="B1754" s="31" t="n"/>
+      <c r="C1754" s="8" t="n"/>
+      <c r="D1754" s="8" t="n"/>
+      <c r="E1754" s="23" t="n"/>
+      <c r="G1754" s="31" t="n"/>
+      <c r="H1754" s="8" t="n"/>
+      <c r="I1754" s="8" t="n"/>
+      <c r="J1754" s="23" t="n"/>
+      <c r="L1754" s="31" t="n"/>
+      <c r="M1754" s="8" t="n"/>
+      <c r="N1754" s="8" t="n"/>
+      <c r="O1754" s="23" t="n"/>
+    </row>
+    <row r="1755">
+      <c r="B1755" s="29" t="inlineStr">
+        <is>
+          <t>Ficha de la historia</t>
+        </is>
+      </c>
+      <c r="C1755" s="8" t="n"/>
+      <c r="D1755" s="8" t="n"/>
+      <c r="E1755" s="23" t="n"/>
+      <c r="G1755" s="29" t="inlineStr">
+        <is>
+          <t>Criterios de listo:</t>
+        </is>
+      </c>
+      <c r="H1755" s="8" t="n"/>
+      <c r="I1755" s="8" t="n"/>
+      <c r="J1755" s="23" t="n"/>
+      <c r="L1755" s="29" t="inlineStr">
+        <is>
+          <t>Condiciones finales (se marcan cuando el PO acepta la historia en la Review):</t>
+        </is>
+      </c>
+      <c r="M1755" s="8" t="n"/>
+      <c r="N1755" s="8" t="n"/>
+      <c r="O1755" s="23" t="n"/>
+    </row>
+    <row r="1756" ht="30" customHeight="1">
+      <c r="B1756" s="32" t="inlineStr">
+        <is>
+          <t>Tipo: Historia técnica (habilitadora)</t>
+        </is>
+      </c>
+      <c r="C1756" s="8" t="n"/>
+      <c r="D1756" s="8" t="n"/>
+      <c r="E1756" s="23" t="n"/>
+      <c r="G1756" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1756" s="34" t="inlineStr">
+        <is>
+          <t>L1 · Redactada en el formato acordado — Cumple</t>
+        </is>
+      </c>
+      <c r="I1756" s="8" t="n"/>
+      <c r="J1756" s="23" t="n"/>
+      <c r="L1756" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1756" s="34" t="inlineStr">
+        <is>
+          <t>La API, la base y la web se han desplegado y responden desde una URL pública de pruebas</t>
+        </is>
+      </c>
+      <c r="N1756" s="8" t="n"/>
+      <c r="O1756" s="23" t="n"/>
+    </row>
+    <row r="1757" ht="30" customHeight="1">
+      <c r="B1757" s="32" t="inlineStr">
+        <is>
+          <t>Qué destraba: T8 de la DoD: sin esto ninguna HU llega a Done</t>
+        </is>
+      </c>
+      <c r="C1757" s="8" t="n"/>
+      <c r="D1757" s="8" t="n"/>
+      <c r="E1757" s="23" t="n"/>
+      <c r="G1757" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1757" s="34" t="inlineStr">
+        <is>
+          <t>L2 · Nombre corto en forma de acción — Cumple</t>
+        </is>
+      </c>
+      <c r="I1757" s="8" t="n"/>
+      <c r="J1757" s="23" t="n"/>
+      <c r="L1757" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1757" s="34" t="inlineStr">
+        <is>
+          <t>Las migraciones se han aplicado solas al desplegar (alembic upgrade head)</t>
+        </is>
+      </c>
+      <c r="N1757" s="8" t="n"/>
+      <c r="O1757" s="23" t="n"/>
+    </row>
+    <row r="1758" ht="30" customHeight="1">
+      <c r="B1758" s="32" t="inlineStr">
+        <is>
+          <t>Responsable técnico: Fernando</t>
+        </is>
+      </c>
+      <c r="C1758" s="8" t="n"/>
+      <c r="D1758" s="8" t="n"/>
+      <c r="E1758" s="23" t="n"/>
+      <c r="G1758" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1758" s="34" t="inlineStr">
+        <is>
+          <t>L3 · Criterios de aceptación escritos — Cumple</t>
+        </is>
+      </c>
+      <c r="I1758" s="8" t="n"/>
+      <c r="J1758" s="23" t="n"/>
+      <c r="L1758" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1758" s="34" t="inlineStr">
+        <is>
+          <t>Los secretos se han configurado como variables del servicio, nunca en el repositorio</t>
+        </is>
+      </c>
+      <c r="N1758" s="8" t="n"/>
+      <c r="O1758" s="23" t="n"/>
+    </row>
+    <row r="1759" ht="30" customHeight="1">
+      <c r="B1759" s="36" t="inlineStr">
+        <is>
+          <t>Depende de: Ninguna</t>
+        </is>
+      </c>
+      <c r="C1759" s="37" t="n"/>
+      <c r="D1759" s="37" t="n"/>
+      <c r="E1759" s="38" t="n"/>
+      <c r="G1759" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1759" s="34" t="inlineStr">
+        <is>
+          <t>L4 · Dependencias resueltas — Cumple</t>
+        </is>
+      </c>
+      <c r="I1759" s="8" t="n"/>
+      <c r="J1759" s="23" t="n"/>
+      <c r="L1759" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1759" s="34" t="inlineStr">
+        <is>
+          <t>Alguien distinto de quien desplegó ha entrado a la web de pruebas y ha iniciado sesión</t>
+        </is>
+      </c>
+      <c r="N1759" s="8" t="n"/>
+      <c r="O1759" s="23" t="n"/>
+    </row>
+    <row r="1760" ht="36" customHeight="1">
+      <c r="G1760" s="40" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1760" s="34" t="inlineStr">
+        <is>
+          <t>L5 · Estimada por los Developers — No cumple: se vota en el próximo Daily</t>
+        </is>
+      </c>
+      <c r="I1760" s="8" t="n"/>
+      <c r="J1760" s="23" t="n"/>
+      <c r="L1760" s="36" t="inlineStr">
+        <is>
+          <t>Mitad técnica: Además, los criterios T1 a T10 de la hoja «3. Criterios DoR y DoD» que le apliquen</t>
+        </is>
+      </c>
+      <c r="M1760" s="37" t="n"/>
+      <c r="N1760" s="37" t="n"/>
+      <c r="O1760" s="38" t="n"/>
+    </row>
+    <row r="1761" ht="30" customHeight="1">
+      <c r="G1761" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1761" s="34" t="inlineStr">
+        <is>
+          <t>L6 · Cabe en un sprint (8 puntos o menos) — Cumple</t>
+        </is>
+      </c>
+      <c r="I1761" s="8" t="n"/>
+      <c r="J1761" s="23" t="n"/>
+    </row>
+    <row r="1762" ht="30" customHeight="1">
+      <c r="G1762" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1762" s="34" t="inlineStr">
+        <is>
+          <t>L7 · Reglas de dominio identificadas — Cumple</t>
+        </is>
+      </c>
+      <c r="I1762" s="8" t="n"/>
+      <c r="J1762" s="23" t="n"/>
+    </row>
+    <row r="1763" ht="30" customHeight="1">
+      <c r="G1763" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1763" s="34" t="inlineStr">
+        <is>
+          <t>L8 · Datos de prueba disponibles — Cumple</t>
+        </is>
+      </c>
+      <c r="I1763" s="8" t="n"/>
+      <c r="J1763" s="23" t="n"/>
+    </row>
+    <row r="1764" ht="30" customHeight="1">
+      <c r="G1764" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1764" s="34" t="inlineStr">
+        <is>
+          <t>L9 · Responsable técnico asignado — Cumple</t>
+        </is>
+      </c>
+      <c r="I1764" s="8" t="n"/>
+      <c r="J1764" s="23" t="n"/>
+    </row>
+    <row r="1765" ht="30" customHeight="1">
+      <c r="G1765" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1765" s="34" t="inlineStr">
+        <is>
+          <t>L10 · Recursos identificados — Cumple: Fernando + equipo</t>
+        </is>
+      </c>
+      <c r="I1765" s="8" t="n"/>
+      <c r="J1765" s="23" t="n"/>
+    </row>
+    <row r="1766" ht="30" customHeight="1">
+      <c r="G1766" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1766" s="34" t="inlineStr">
+        <is>
+          <t>L11 · Requisitos técnicos de programación definidos — Cumple: FastAPI, Docker y la consola del hosting</t>
+        </is>
+      </c>
+      <c r="I1766" s="8" t="n"/>
+      <c r="J1766" s="23" t="n"/>
+    </row>
+    <row r="1767" ht="30" customHeight="1">
+      <c r="G1767" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1767" s="34" t="inlineStr">
+        <is>
+          <t>L12 · Accesos de red disponibles — Cumple: Hosting en la nube (capa gratuita) · PostgreSQL gestionado · GitHub</t>
+        </is>
+      </c>
+      <c r="I1767" s="8" t="n"/>
+      <c r="J1767" s="23" t="n"/>
+    </row>
+    <row r="1768" ht="36" customHeight="1">
+      <c r="G1768" s="39" t="inlineStr">
+        <is>
+          <t>Riesgos: Planes gratuitos con límites o que se duermen · elegir uno con base gestionada y documentar cómo despertarlo</t>
+        </is>
+      </c>
+      <c r="H1768" s="8" t="n"/>
+      <c r="I1768" s="8" t="n"/>
+      <c r="J1768" s="23" t="n"/>
+    </row>
+    <row r="1769" ht="36" customHeight="1">
+      <c r="G1769" s="32" t="inlineStr">
+        <is>
+          <t>Proveedores de servicio: Hosting en la nube (capa gratuita) · PostgreSQL gestionado · GitHub</t>
+        </is>
+      </c>
+      <c r="H1769" s="8" t="n"/>
+      <c r="I1769" s="8" t="n"/>
+      <c r="J1769" s="23" t="n"/>
+    </row>
+    <row r="1770" ht="36" customHeight="1">
+      <c r="G1770" s="36" t="inlineStr">
+        <is>
+          <t>Costos: S/ 0 en servicios (planes gratuitos) · horas según la votación</t>
+        </is>
+      </c>
+      <c r="H1770" s="37" t="n"/>
+      <c r="I1770" s="37" t="n"/>
+      <c r="J1770" s="38" t="n"/>
+    </row>
+    <row r="1773">
+      <c r="B1773" s="18" t="inlineStr">
+        <is>
+          <t>HT-02 · Configurar la integración continua (historia técnica)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774" ht="18" customHeight="1">
+      <c r="B1774" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 1 · Historia técnica</t>
+        </is>
+      </c>
+      <c r="C1774" s="20" t="n"/>
+      <c r="D1774" s="20" t="n"/>
+      <c r="E1774" s="21" t="n"/>
+      <c r="G1774" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 2 · Definición de Listo</t>
+        </is>
+      </c>
+      <c r="H1774" s="20" t="n"/>
+      <c r="I1774" s="20" t="n"/>
+      <c r="J1774" s="21" t="n"/>
+      <c r="L1774" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 3 · Definición de Terminado</t>
+        </is>
+      </c>
+      <c r="M1774" s="20" t="n"/>
+      <c r="N1774" s="20" t="n"/>
+      <c r="O1774" s="21" t="n"/>
+    </row>
+    <row r="1775" ht="28" customHeight="1">
+      <c r="B1775" s="22" t="inlineStr">
+        <is>
+          <t>Habilita a las HU de usuario: no entrega una función al usuario final</t>
+        </is>
+      </c>
+      <c r="C1775" s="8" t="n"/>
+      <c r="D1775" s="8" t="n"/>
+      <c r="E1775" s="23" t="n"/>
+      <c r="G1775" s="22" t="inlineStr">
+        <is>
+          <t>El enfoque está en la consideración del equipo de desarrollo sobre si la historia está lista para un Sprint</t>
+        </is>
+      </c>
+      <c r="H1775" s="8" t="n"/>
+      <c r="I1775" s="8" t="n"/>
+      <c r="J1775" s="23" t="n"/>
+      <c r="L1775" s="22" t="inlineStr">
+        <is>
+          <t>El enfoque está en la aceptación del cliente cuando se le entregue el producto</t>
+        </is>
+      </c>
+      <c r="M1775" s="8" t="n"/>
+      <c r="N1775" s="8" t="n"/>
+      <c r="O1775" s="23" t="n"/>
+    </row>
+    <row r="1776">
+      <c r="B1776" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="C1776" s="8" t="n"/>
+      <c r="D1776" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="E1776" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="G1776" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="H1776" s="8" t="n"/>
+      <c r="I1776" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="J1776" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="L1776" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="M1776" s="8" t="n"/>
+      <c r="N1776" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="O1776" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+    </row>
+    <row r="1777" ht="30" customHeight="1">
+      <c r="B1777" s="27" t="inlineStr">
+        <is>
+          <t>HT-02 · Configurar la integración continua</t>
+        </is>
+      </c>
+      <c r="C1777" s="8" t="n"/>
+      <c r="D1777" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E1777" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+      <c r="G1777" s="27" t="inlineStr">
+        <is>
+          <t>HT-02 · Configurar la integración continua</t>
+        </is>
+      </c>
+      <c r="H1777" s="8" t="n"/>
+      <c r="I1777" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J1777" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+      <c r="L1777" s="27" t="inlineStr">
+        <is>
+          <t>HT-02 · Configurar la integración continua</t>
+        </is>
+      </c>
+      <c r="M1777" s="8" t="n"/>
+      <c r="N1777" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="O1777" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="B1778" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="C1778" s="8" t="n"/>
+      <c r="D1778" s="8" t="n"/>
+      <c r="E1778" s="23" t="n"/>
+      <c r="G1778" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="H1778" s="8" t="n"/>
+      <c r="I1778" s="8" t="n"/>
+      <c r="J1778" s="23" t="n"/>
+      <c r="L1778" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="M1778" s="8" t="n"/>
+      <c r="N1778" s="8" t="n"/>
+      <c r="O1778" s="23" t="n"/>
+    </row>
+    <row r="1779" ht="28" customHeight="1">
+      <c r="B1779" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero que cada Pull Request compile y corra las pruebas automáticamente, para detectar un error antes de que llegue a main.</t>
+        </is>
+      </c>
+      <c r="C1779" s="8" t="n"/>
+      <c r="D1779" s="8" t="n"/>
+      <c r="E1779" s="23" t="n"/>
+      <c r="G1779" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero que cada Pull Request compile y corra las pruebas automáticamente, para detectar un error antes de que llegue a main.</t>
+        </is>
+      </c>
+      <c r="H1779" s="8" t="n"/>
+      <c r="I1779" s="8" t="n"/>
+      <c r="J1779" s="23" t="n"/>
+      <c r="L1779" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero que cada Pull Request compile y corra las pruebas automáticamente, para detectar un error antes de que llegue a main.</t>
+        </is>
+      </c>
+      <c r="M1779" s="8" t="n"/>
+      <c r="N1779" s="8" t="n"/>
+      <c r="O1779" s="23" t="n"/>
+    </row>
+    <row r="1780" ht="28" customHeight="1">
+      <c r="B1780" s="31" t="n"/>
+      <c r="C1780" s="8" t="n"/>
+      <c r="D1780" s="8" t="n"/>
+      <c r="E1780" s="23" t="n"/>
+      <c r="G1780" s="31" t="n"/>
+      <c r="H1780" s="8" t="n"/>
+      <c r="I1780" s="8" t="n"/>
+      <c r="J1780" s="23" t="n"/>
+      <c r="L1780" s="31" t="n"/>
+      <c r="M1780" s="8" t="n"/>
+      <c r="N1780" s="8" t="n"/>
+      <c r="O1780" s="23" t="n"/>
+    </row>
+    <row r="1781">
+      <c r="B1781" s="29" t="inlineStr">
+        <is>
+          <t>Ficha de la historia</t>
+        </is>
+      </c>
+      <c r="C1781" s="8" t="n"/>
+      <c r="D1781" s="8" t="n"/>
+      <c r="E1781" s="23" t="n"/>
+      <c r="G1781" s="29" t="inlineStr">
+        <is>
+          <t>Criterios de listo:</t>
+        </is>
+      </c>
+      <c r="H1781" s="8" t="n"/>
+      <c r="I1781" s="8" t="n"/>
+      <c r="J1781" s="23" t="n"/>
+      <c r="L1781" s="29" t="inlineStr">
+        <is>
+          <t>Condiciones finales (se marcan cuando el PO acepta la historia en la Review):</t>
+        </is>
+      </c>
+      <c r="M1781" s="8" t="n"/>
+      <c r="N1781" s="8" t="n"/>
+      <c r="O1781" s="23" t="n"/>
+    </row>
+    <row r="1782" ht="30" customHeight="1">
+      <c r="B1782" s="32" t="inlineStr">
+        <is>
+          <t>Tipo: Historia técnica (habilitadora)</t>
+        </is>
+      </c>
+      <c r="C1782" s="8" t="n"/>
+      <c r="D1782" s="8" t="n"/>
+      <c r="E1782" s="23" t="n"/>
+      <c r="G1782" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1782" s="34" t="inlineStr">
+        <is>
+          <t>L1 · Redactada en el formato acordado — Cumple</t>
+        </is>
+      </c>
+      <c r="I1782" s="8" t="n"/>
+      <c r="J1782" s="23" t="n"/>
+      <c r="L1782" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1782" s="34" t="inlineStr">
+        <is>
+          <t>Cada PR ha ejecutado el build de la web y las pruebas de la API y del microservicio</t>
+        </is>
+      </c>
+      <c r="N1782" s="8" t="n"/>
+      <c r="O1782" s="23" t="n"/>
+    </row>
+    <row r="1783" ht="30" customHeight="1">
+      <c r="B1783" s="32" t="inlineStr">
+        <is>
+          <t>Qué destraba: T1 y T5 de la DoD</t>
+        </is>
+      </c>
+      <c r="C1783" s="8" t="n"/>
+      <c r="D1783" s="8" t="n"/>
+      <c r="E1783" s="23" t="n"/>
+      <c r="G1783" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1783" s="34" t="inlineStr">
+        <is>
+          <t>L2 · Nombre corto en forma de acción — Cumple</t>
+        </is>
+      </c>
+      <c r="I1783" s="8" t="n"/>
+      <c r="J1783" s="23" t="n"/>
+      <c r="L1783" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1783" s="34" t="inlineStr">
+        <is>
+          <t>Un PR con una prueba fallida ha quedado marcado en rojo y no se ha podido fusionar</t>
+        </is>
+      </c>
+      <c r="N1783" s="8" t="n"/>
+      <c r="O1783" s="23" t="n"/>
+    </row>
+    <row r="1784" ht="30" customHeight="1">
+      <c r="B1784" s="32" t="inlineStr">
+        <is>
+          <t>Responsable técnico: Adiel</t>
+        </is>
+      </c>
+      <c r="C1784" s="8" t="n"/>
+      <c r="D1784" s="8" t="n"/>
+      <c r="E1784" s="23" t="n"/>
+      <c r="G1784" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1784" s="34" t="inlineStr">
+        <is>
+          <t>L3 · Criterios de aceptación escritos — Cumple</t>
+        </is>
+      </c>
+      <c r="I1784" s="8" t="n"/>
+      <c r="J1784" s="23" t="n"/>
+      <c r="L1784" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1784" s="34" t="inlineStr">
+        <is>
+          <t>El resultado se ha visto en el propio PR</t>
+        </is>
+      </c>
+      <c r="N1784" s="8" t="n"/>
+      <c r="O1784" s="23" t="n"/>
+    </row>
+    <row r="1785" ht="36" customHeight="1">
+      <c r="B1785" s="36" t="inlineStr">
+        <is>
+          <t>Depende de: Ninguna</t>
+        </is>
+      </c>
+      <c r="C1785" s="37" t="n"/>
+      <c r="D1785" s="37" t="n"/>
+      <c r="E1785" s="38" t="n"/>
+      <c r="G1785" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1785" s="34" t="inlineStr">
+        <is>
+          <t>L4 · Dependencias resueltas — Cumple</t>
+        </is>
+      </c>
+      <c r="I1785" s="8" t="n"/>
+      <c r="J1785" s="23" t="n"/>
+      <c r="L1785" s="36" t="inlineStr">
+        <is>
+          <t>Mitad técnica: Además, los criterios T1 a T10 de la hoja «3. Criterios DoR y DoD» que le apliquen</t>
+        </is>
+      </c>
+      <c r="M1785" s="37" t="n"/>
+      <c r="N1785" s="37" t="n"/>
+      <c r="O1785" s="38" t="n"/>
+    </row>
+    <row r="1786" ht="30" customHeight="1">
+      <c r="G1786" s="40" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1786" s="34" t="inlineStr">
+        <is>
+          <t>L5 · Estimada por los Developers — No cumple: se vota en el próximo Daily</t>
+        </is>
+      </c>
+      <c r="I1786" s="8" t="n"/>
+      <c r="J1786" s="23" t="n"/>
+    </row>
+    <row r="1787" ht="30" customHeight="1">
+      <c r="G1787" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1787" s="34" t="inlineStr">
+        <is>
+          <t>L6 · Cabe en un sprint (8 puntos o menos) — Cumple</t>
+        </is>
+      </c>
+      <c r="I1787" s="8" t="n"/>
+      <c r="J1787" s="23" t="n"/>
+    </row>
+    <row r="1788" ht="30" customHeight="1">
+      <c r="G1788" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1788" s="34" t="inlineStr">
+        <is>
+          <t>L7 · Reglas de dominio identificadas — Cumple</t>
+        </is>
+      </c>
+      <c r="I1788" s="8" t="n"/>
+      <c r="J1788" s="23" t="n"/>
+    </row>
+    <row r="1789" ht="30" customHeight="1">
+      <c r="G1789" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1789" s="34" t="inlineStr">
+        <is>
+          <t>L8 · Datos de prueba disponibles — Cumple</t>
+        </is>
+      </c>
+      <c r="I1789" s="8" t="n"/>
+      <c r="J1789" s="23" t="n"/>
+    </row>
+    <row r="1790" ht="30" customHeight="1">
+      <c r="G1790" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1790" s="34" t="inlineStr">
+        <is>
+          <t>L9 · Responsable técnico asignado — Cumple</t>
+        </is>
+      </c>
+      <c r="I1790" s="8" t="n"/>
+      <c r="J1790" s="23" t="n"/>
+    </row>
+    <row r="1791" ht="30" customHeight="1">
+      <c r="G1791" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1791" s="34" t="inlineStr">
+        <is>
+          <t>L10 · Recursos identificados — Cumple: Adiel + equipo</t>
+        </is>
+      </c>
+      <c r="I1791" s="8" t="n"/>
+      <c r="J1791" s="23" t="n"/>
+    </row>
+    <row r="1792" ht="30" customHeight="1">
+      <c r="G1792" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1792" s="34" t="inlineStr">
+        <is>
+          <t>L11 · Requisitos técnicos de programación definidos — Cumple: FastAPI, pytest y GitHub Actions</t>
+        </is>
+      </c>
+      <c r="I1792" s="8" t="n"/>
+      <c r="J1792" s="23" t="n"/>
+    </row>
+    <row r="1793" ht="30" customHeight="1">
+      <c r="G1793" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1793" s="34" t="inlineStr">
+        <is>
+          <t>L12 · Accesos de red disponibles — Cumple: GitHub Actions (minutos gratuitos)</t>
+        </is>
+      </c>
+      <c r="I1793" s="8" t="n"/>
+      <c r="J1793" s="23" t="n"/>
+    </row>
+    <row r="1794" ht="36" customHeight="1">
+      <c r="G1794" s="39" t="inlineStr">
+        <is>
+          <t>Riesgos: Pruebas lentas o que dependen de la base · separar las de dominio, que corren sin base</t>
+        </is>
+      </c>
+      <c r="H1794" s="8" t="n"/>
+      <c r="I1794" s="8" t="n"/>
+      <c r="J1794" s="23" t="n"/>
+    </row>
+    <row r="1795" ht="36" customHeight="1">
+      <c r="G1795" s="32" t="inlineStr">
+        <is>
+          <t>Proveedores de servicio: GitHub Actions (minutos gratuitos)</t>
+        </is>
+      </c>
+      <c r="H1795" s="8" t="n"/>
+      <c r="I1795" s="8" t="n"/>
+      <c r="J1795" s="23" t="n"/>
+    </row>
+    <row r="1796" ht="36" customHeight="1">
+      <c r="G1796" s="36" t="inlineStr">
+        <is>
+          <t>Costos: S/ 0 en servicios (planes gratuitos) · horas según la votación</t>
+        </is>
+      </c>
+      <c r="H1796" s="37" t="n"/>
+      <c r="I1796" s="37" t="n"/>
+      <c r="J1796" s="38" t="n"/>
+    </row>
+    <row r="1799">
+      <c r="B1799" s="18" t="inlineStr">
+        <is>
+          <t>HT-03 · Proteger el repositorio y main (historia técnica)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1800" ht="18" customHeight="1">
+      <c r="B1800" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 1 · Historia técnica</t>
+        </is>
+      </c>
+      <c r="C1800" s="20" t="n"/>
+      <c r="D1800" s="20" t="n"/>
+      <c r="E1800" s="21" t="n"/>
+      <c r="G1800" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 2 · Definición de Listo</t>
+        </is>
+      </c>
+      <c r="H1800" s="20" t="n"/>
+      <c r="I1800" s="20" t="n"/>
+      <c r="J1800" s="21" t="n"/>
+      <c r="L1800" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 3 · Definición de Terminado</t>
+        </is>
+      </c>
+      <c r="M1800" s="20" t="n"/>
+      <c r="N1800" s="20" t="n"/>
+      <c r="O1800" s="21" t="n"/>
+    </row>
+    <row r="1801" ht="28" customHeight="1">
+      <c r="B1801" s="22" t="inlineStr">
+        <is>
+          <t>Habilita a las HU de usuario: no entrega una función al usuario final</t>
+        </is>
+      </c>
+      <c r="C1801" s="8" t="n"/>
+      <c r="D1801" s="8" t="n"/>
+      <c r="E1801" s="23" t="n"/>
+      <c r="G1801" s="22" t="inlineStr">
+        <is>
+          <t>El enfoque está en la consideración del equipo de desarrollo sobre si la historia está lista para un Sprint</t>
+        </is>
+      </c>
+      <c r="H1801" s="8" t="n"/>
+      <c r="I1801" s="8" t="n"/>
+      <c r="J1801" s="23" t="n"/>
+      <c r="L1801" s="22" t="inlineStr">
+        <is>
+          <t>El enfoque está en la aceptación del cliente cuando se le entregue el producto</t>
+        </is>
+      </c>
+      <c r="M1801" s="8" t="n"/>
+      <c r="N1801" s="8" t="n"/>
+      <c r="O1801" s="23" t="n"/>
+    </row>
+    <row r="1802">
+      <c r="B1802" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="C1802" s="8" t="n"/>
+      <c r="D1802" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="E1802" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="G1802" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="H1802" s="8" t="n"/>
+      <c r="I1802" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="J1802" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="L1802" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="M1802" s="8" t="n"/>
+      <c r="N1802" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="O1802" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+    </row>
+    <row r="1803" ht="30" customHeight="1">
+      <c r="B1803" s="27" t="inlineStr">
+        <is>
+          <t>HT-03 · Proteger el repositorio y main</t>
+        </is>
+      </c>
+      <c r="C1803" s="8" t="n"/>
+      <c r="D1803" s="9" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="E1803" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+      <c r="G1803" s="27" t="inlineStr">
+        <is>
+          <t>HT-03 · Proteger el repositorio y main</t>
+        </is>
+      </c>
+      <c r="H1803" s="8" t="n"/>
+      <c r="I1803" s="9" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J1803" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+      <c r="L1803" s="27" t="inlineStr">
+        <is>
+          <t>HT-03 · Proteger el repositorio y main</t>
+        </is>
+      </c>
+      <c r="M1803" s="8" t="n"/>
+      <c r="N1803" s="9" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="O1803" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="B1804" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="C1804" s="8" t="n"/>
+      <c r="D1804" s="8" t="n"/>
+      <c r="E1804" s="23" t="n"/>
+      <c r="G1804" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="H1804" s="8" t="n"/>
+      <c r="I1804" s="8" t="n"/>
+      <c r="J1804" s="23" t="n"/>
+      <c r="L1804" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="M1804" s="8" t="n"/>
+      <c r="N1804" s="8" t="n"/>
+      <c r="O1804" s="23" t="n"/>
+    </row>
+    <row r="1805" ht="28" customHeight="1">
+      <c r="B1805" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero el repositorio privado y la rama main protegida, para que los datos del cliente no queden expuestos y nada entre sin revisión.</t>
+        </is>
+      </c>
+      <c r="C1805" s="8" t="n"/>
+      <c r="D1805" s="8" t="n"/>
+      <c r="E1805" s="23" t="n"/>
+      <c r="G1805" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero el repositorio privado y la rama main protegida, para que los datos del cliente no queden expuestos y nada entre sin revisión.</t>
+        </is>
+      </c>
+      <c r="H1805" s="8" t="n"/>
+      <c r="I1805" s="8" t="n"/>
+      <c r="J1805" s="23" t="n"/>
+      <c r="L1805" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero el repositorio privado y la rama main protegida, para que los datos del cliente no queden expuestos y nada entre sin revisión.</t>
+        </is>
+      </c>
+      <c r="M1805" s="8" t="n"/>
+      <c r="N1805" s="8" t="n"/>
+      <c r="O1805" s="23" t="n"/>
+    </row>
+    <row r="1806" ht="28" customHeight="1">
+      <c r="B1806" s="31" t="n"/>
+      <c r="C1806" s="8" t="n"/>
+      <c r="D1806" s="8" t="n"/>
+      <c r="E1806" s="23" t="n"/>
+      <c r="G1806" s="31" t="n"/>
+      <c r="H1806" s="8" t="n"/>
+      <c r="I1806" s="8" t="n"/>
+      <c r="J1806" s="23" t="n"/>
+      <c r="L1806" s="31" t="n"/>
+      <c r="M1806" s="8" t="n"/>
+      <c r="N1806" s="8" t="n"/>
+      <c r="O1806" s="23" t="n"/>
+    </row>
+    <row r="1807">
+      <c r="B1807" s="29" t="inlineStr">
+        <is>
+          <t>Ficha de la historia</t>
+        </is>
+      </c>
+      <c r="C1807" s="8" t="n"/>
+      <c r="D1807" s="8" t="n"/>
+      <c r="E1807" s="23" t="n"/>
+      <c r="G1807" s="29" t="inlineStr">
+        <is>
+          <t>Criterios de listo:</t>
+        </is>
+      </c>
+      <c r="H1807" s="8" t="n"/>
+      <c r="I1807" s="8" t="n"/>
+      <c r="J1807" s="23" t="n"/>
+      <c r="L1807" s="29" t="inlineStr">
+        <is>
+          <t>Condiciones finales (se marcan cuando el PO acepta la historia en la Review):</t>
+        </is>
+      </c>
+      <c r="M1807" s="8" t="n"/>
+      <c r="N1807" s="8" t="n"/>
+      <c r="O1807" s="23" t="n"/>
+    </row>
+    <row r="1808" ht="30" customHeight="1">
+      <c r="B1808" s="32" t="inlineStr">
+        <is>
+          <t>Tipo: Historia técnica (habilitadora)</t>
+        </is>
+      </c>
+      <c r="C1808" s="8" t="n"/>
+      <c r="D1808" s="8" t="n"/>
+      <c r="E1808" s="23" t="n"/>
+      <c r="G1808" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1808" s="34" t="inlineStr">
+        <is>
+          <t>L1 · Redactada en el formato acordado — Cumple</t>
+        </is>
+      </c>
+      <c r="I1808" s="8" t="n"/>
+      <c r="J1808" s="23" t="n"/>
+      <c r="L1808" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1808" s="34" t="inlineStr">
+        <is>
+          <t>El repositorio se ha puesto en privado y el docente se ha invitado como lector</t>
+        </is>
+      </c>
+      <c r="N1808" s="8" t="n"/>
+      <c r="O1808" s="23" t="n"/>
+    </row>
+    <row r="1809" ht="30" customHeight="1">
+      <c r="B1809" s="32" t="inlineStr">
+        <is>
+          <t>Qué destraba: T1 de la DoD y la confidencialidad de los datos de SEVENS</t>
+        </is>
+      </c>
+      <c r="C1809" s="8" t="n"/>
+      <c r="D1809" s="8" t="n"/>
+      <c r="E1809" s="23" t="n"/>
+      <c r="G1809" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1809" s="34" t="inlineStr">
+        <is>
+          <t>L2 · Nombre corto en forma de acción — Cumple</t>
+        </is>
+      </c>
+      <c r="I1809" s="8" t="n"/>
+      <c r="J1809" s="23" t="n"/>
+      <c r="L1809" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1809" s="34" t="inlineStr">
+        <is>
+          <t>Un push directo a main se ha rechazado: todo entra por PR con al menos una aprobación de otro integrante</t>
+        </is>
+      </c>
+      <c r="N1809" s="8" t="n"/>
+      <c r="O1809" s="23" t="n"/>
+    </row>
+    <row r="1810" ht="30" customHeight="1">
+      <c r="B1810" s="32" t="inlineStr">
+        <is>
+          <t>Responsable técnico: Fernando</t>
+        </is>
+      </c>
+      <c r="C1810" s="8" t="n"/>
+      <c r="D1810" s="8" t="n"/>
+      <c r="E1810" s="23" t="n"/>
+      <c r="G1810" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1810" s="34" t="inlineStr">
+        <is>
+          <t>L3 · Criterios de aceptación escritos — Cumple</t>
+        </is>
+      </c>
+      <c r="I1810" s="8" t="n"/>
+      <c r="J1810" s="23" t="n"/>
+      <c r="L1810" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1810" s="34" t="inlineStr">
+        <is>
+          <t>Se ha verificado que ningún .env ni token está en el historial del repositorio</t>
+        </is>
+      </c>
+      <c r="N1810" s="8" t="n"/>
+      <c r="O1810" s="23" t="n"/>
+    </row>
+    <row r="1811" ht="36" customHeight="1">
+      <c r="B1811" s="36" t="inlineStr">
+        <is>
+          <t>Depende de: Ninguna</t>
+        </is>
+      </c>
+      <c r="C1811" s="37" t="n"/>
+      <c r="D1811" s="37" t="n"/>
+      <c r="E1811" s="38" t="n"/>
+      <c r="G1811" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1811" s="34" t="inlineStr">
+        <is>
+          <t>L4 · Dependencias resueltas — Cumple</t>
+        </is>
+      </c>
+      <c r="I1811" s="8" t="n"/>
+      <c r="J1811" s="23" t="n"/>
+      <c r="L1811" s="36" t="inlineStr">
+        <is>
+          <t>Mitad técnica: Además, los criterios T1 a T10 de la hoja «3. Criterios DoR y DoD» que le apliquen</t>
+        </is>
+      </c>
+      <c r="M1811" s="37" t="n"/>
+      <c r="N1811" s="37" t="n"/>
+      <c r="O1811" s="38" t="n"/>
+    </row>
+    <row r="1812" ht="30" customHeight="1">
+      <c r="G1812" s="40" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1812" s="34" t="inlineStr">
+        <is>
+          <t>L5 · Estimada por los Developers — No cumple: se vota en el próximo Daily</t>
+        </is>
+      </c>
+      <c r="I1812" s="8" t="n"/>
+      <c r="J1812" s="23" t="n"/>
+    </row>
+    <row r="1813" ht="30" customHeight="1">
+      <c r="G1813" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1813" s="34" t="inlineStr">
+        <is>
+          <t>L6 · Cabe en un sprint (8 puntos o menos) — Cumple</t>
+        </is>
+      </c>
+      <c r="I1813" s="8" t="n"/>
+      <c r="J1813" s="23" t="n"/>
+    </row>
+    <row r="1814" ht="30" customHeight="1">
+      <c r="G1814" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1814" s="34" t="inlineStr">
+        <is>
+          <t>L7 · Reglas de dominio identificadas — Cumple</t>
+        </is>
+      </c>
+      <c r="I1814" s="8" t="n"/>
+      <c r="J1814" s="23" t="n"/>
+    </row>
+    <row r="1815" ht="30" customHeight="1">
+      <c r="G1815" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1815" s="34" t="inlineStr">
+        <is>
+          <t>L8 · Datos de prueba disponibles — Cumple</t>
+        </is>
+      </c>
+      <c r="I1815" s="8" t="n"/>
+      <c r="J1815" s="23" t="n"/>
+    </row>
+    <row r="1816" ht="30" customHeight="1">
+      <c r="G1816" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1816" s="34" t="inlineStr">
+        <is>
+          <t>L9 · Responsable técnico asignado — Cumple</t>
+        </is>
+      </c>
+      <c r="I1816" s="8" t="n"/>
+      <c r="J1816" s="23" t="n"/>
+    </row>
+    <row r="1817" ht="30" customHeight="1">
+      <c r="G1817" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1817" s="34" t="inlineStr">
+        <is>
+          <t>L10 · Recursos identificados — Cumple: Fernando + equipo</t>
+        </is>
+      </c>
+      <c r="I1817" s="8" t="n"/>
+      <c r="J1817" s="23" t="n"/>
+    </row>
+    <row r="1818" ht="30" customHeight="1">
+      <c r="G1818" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1818" s="34" t="inlineStr">
+        <is>
+          <t>L11 · Requisitos técnicos de programación definidos — Cumple: FastAPI, Docker y la consola del hosting</t>
+        </is>
+      </c>
+      <c r="I1818" s="8" t="n"/>
+      <c r="J1818" s="23" t="n"/>
+    </row>
+    <row r="1819" ht="30" customHeight="1">
+      <c r="G1819" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1819" s="34" t="inlineStr">
+        <is>
+          <t>L12 · Accesos de red disponibles — Cumple: GitHub</t>
+        </is>
+      </c>
+      <c r="I1819" s="8" t="n"/>
+      <c r="J1819" s="23" t="n"/>
+    </row>
+    <row r="1820" ht="36" customHeight="1">
+      <c r="G1820" s="39" t="inlineStr">
+        <is>
+          <t>Riesgos: Hoy el repositorio es público con precios y proveedores del cliente · cambiarlo antes que cualquier otra cosa</t>
+        </is>
+      </c>
+      <c r="H1820" s="8" t="n"/>
+      <c r="I1820" s="8" t="n"/>
+      <c r="J1820" s="23" t="n"/>
+    </row>
+    <row r="1821" ht="36" customHeight="1">
+      <c r="G1821" s="32" t="inlineStr">
+        <is>
+          <t>Proveedores de servicio: GitHub</t>
+        </is>
+      </c>
+      <c r="H1821" s="8" t="n"/>
+      <c r="I1821" s="8" t="n"/>
+      <c r="J1821" s="23" t="n"/>
+    </row>
+    <row r="1822" ht="36" customHeight="1">
+      <c r="G1822" s="36" t="inlineStr">
+        <is>
+          <t>Costos: S/ 0 en servicios (planes gratuitos) · horas según la votación</t>
+        </is>
+      </c>
+      <c r="H1822" s="37" t="n"/>
+      <c r="I1822" s="37" t="n"/>
+      <c r="J1822" s="38" t="n"/>
+    </row>
+    <row r="1825">
+      <c r="B1825" s="18" t="inlineStr">
+        <is>
+          <t>HT-04 · Conectar la web con la API real (historia técnica)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1826" ht="18" customHeight="1">
+      <c r="B1826" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 1 · Historia técnica</t>
+        </is>
+      </c>
+      <c r="C1826" s="20" t="n"/>
+      <c r="D1826" s="20" t="n"/>
+      <c r="E1826" s="21" t="n"/>
+      <c r="G1826" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 2 · Definición de Listo</t>
+        </is>
+      </c>
+      <c r="H1826" s="20" t="n"/>
+      <c r="I1826" s="20" t="n"/>
+      <c r="J1826" s="21" t="n"/>
+      <c r="L1826" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 3 · Definición de Terminado</t>
+        </is>
+      </c>
+      <c r="M1826" s="20" t="n"/>
+      <c r="N1826" s="20" t="n"/>
+      <c r="O1826" s="21" t="n"/>
+    </row>
+    <row r="1827" ht="28" customHeight="1">
+      <c r="B1827" s="22" t="inlineStr">
+        <is>
+          <t>Habilita a las HU de usuario: no entrega una función al usuario final</t>
+        </is>
+      </c>
+      <c r="C1827" s="8" t="n"/>
+      <c r="D1827" s="8" t="n"/>
+      <c r="E1827" s="23" t="n"/>
+      <c r="G1827" s="22" t="inlineStr">
+        <is>
+          <t>El enfoque está en la consideración del equipo de desarrollo sobre si la historia está lista para un Sprint</t>
+        </is>
+      </c>
+      <c r="H1827" s="8" t="n"/>
+      <c r="I1827" s="8" t="n"/>
+      <c r="J1827" s="23" t="n"/>
+      <c r="L1827" s="22" t="inlineStr">
+        <is>
+          <t>El enfoque está en la aceptación del cliente cuando se le entregue el producto</t>
+        </is>
+      </c>
+      <c r="M1827" s="8" t="n"/>
+      <c r="N1827" s="8" t="n"/>
+      <c r="O1827" s="23" t="n"/>
+    </row>
+    <row r="1828">
+      <c r="B1828" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="C1828" s="8" t="n"/>
+      <c r="D1828" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="E1828" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="G1828" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="H1828" s="8" t="n"/>
+      <c r="I1828" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="J1828" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="L1828" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="M1828" s="8" t="n"/>
+      <c r="N1828" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="O1828" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+    </row>
+    <row r="1829" ht="30" customHeight="1">
+      <c r="B1829" s="27" t="inlineStr">
+        <is>
+          <t>HT-04 · Conectar la web con la API real</t>
+        </is>
+      </c>
+      <c r="C1829" s="8" t="n"/>
+      <c r="D1829" s="9" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="E1829" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+      <c r="G1829" s="27" t="inlineStr">
+        <is>
+          <t>HT-04 · Conectar la web con la API real</t>
+        </is>
+      </c>
+      <c r="H1829" s="8" t="n"/>
+      <c r="I1829" s="9" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J1829" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+      <c r="L1829" s="27" t="inlineStr">
+        <is>
+          <t>HT-04 · Conectar la web con la API real</t>
+        </is>
+      </c>
+      <c r="M1829" s="8" t="n"/>
+      <c r="N1829" s="9" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="O1829" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="B1830" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="C1830" s="8" t="n"/>
+      <c r="D1830" s="8" t="n"/>
+      <c r="E1830" s="23" t="n"/>
+      <c r="G1830" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="H1830" s="8" t="n"/>
+      <c r="I1830" s="8" t="n"/>
+      <c r="J1830" s="23" t="n"/>
+      <c r="L1830" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="M1830" s="8" t="n"/>
+      <c r="N1830" s="8" t="n"/>
+      <c r="O1830" s="23" t="n"/>
+    </row>
+    <row r="1831" ht="28" customHeight="1">
+      <c r="B1831" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero un cliente HTTP único en la web que hable con la API, para conectar todas las pantallas sin rehacerlas.</t>
+        </is>
+      </c>
+      <c r="C1831" s="8" t="n"/>
+      <c r="D1831" s="8" t="n"/>
+      <c r="E1831" s="23" t="n"/>
+      <c r="G1831" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero un cliente HTTP único en la web que hable con la API, para conectar todas las pantallas sin rehacerlas.</t>
+        </is>
+      </c>
+      <c r="H1831" s="8" t="n"/>
+      <c r="I1831" s="8" t="n"/>
+      <c r="J1831" s="23" t="n"/>
+      <c r="L1831" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero un cliente HTTP único en la web que hable con la API, para conectar todas las pantallas sin rehacerlas.</t>
+        </is>
+      </c>
+      <c r="M1831" s="8" t="n"/>
+      <c r="N1831" s="8" t="n"/>
+      <c r="O1831" s="23" t="n"/>
+    </row>
+    <row r="1832" ht="28" customHeight="1">
+      <c r="B1832" s="31" t="n"/>
+      <c r="C1832" s="8" t="n"/>
+      <c r="D1832" s="8" t="n"/>
+      <c r="E1832" s="23" t="n"/>
+      <c r="G1832" s="31" t="n"/>
+      <c r="H1832" s="8" t="n"/>
+      <c r="I1832" s="8" t="n"/>
+      <c r="J1832" s="23" t="n"/>
+      <c r="L1832" s="31" t="n"/>
+      <c r="M1832" s="8" t="n"/>
+      <c r="N1832" s="8" t="n"/>
+      <c r="O1832" s="23" t="n"/>
+    </row>
+    <row r="1833">
+      <c r="B1833" s="29" t="inlineStr">
+        <is>
+          <t>Ficha de la historia</t>
+        </is>
+      </c>
+      <c r="C1833" s="8" t="n"/>
+      <c r="D1833" s="8" t="n"/>
+      <c r="E1833" s="23" t="n"/>
+      <c r="G1833" s="29" t="inlineStr">
+        <is>
+          <t>Criterios de listo:</t>
+        </is>
+      </c>
+      <c r="H1833" s="8" t="n"/>
+      <c r="I1833" s="8" t="n"/>
+      <c r="J1833" s="23" t="n"/>
+      <c r="L1833" s="29" t="inlineStr">
+        <is>
+          <t>Condiciones finales (se marcan cuando el PO acepta la historia en la Review):</t>
+        </is>
+      </c>
+      <c r="M1833" s="8" t="n"/>
+      <c r="N1833" s="8" t="n"/>
+      <c r="O1833" s="23" t="n"/>
+    </row>
+    <row r="1834" ht="30" customHeight="1">
+      <c r="B1834" s="32" t="inlineStr">
+        <is>
+          <t>Tipo: Historia técnica (habilitadora)</t>
+        </is>
+      </c>
+      <c r="C1834" s="8" t="n"/>
+      <c r="D1834" s="8" t="n"/>
+      <c r="E1834" s="23" t="n"/>
+      <c r="G1834" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1834" s="34" t="inlineStr">
+        <is>
+          <t>L1 · Redactada en el formato acordado — Cumple</t>
+        </is>
+      </c>
+      <c r="I1834" s="8" t="n"/>
+      <c r="J1834" s="23" t="n"/>
+      <c r="L1834" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1834" s="34" t="inlineStr">
+        <is>
+          <t>La web ha iniciado sesión contra la API real y ha enviado el token en cada llamada</t>
+        </is>
+      </c>
+      <c r="N1834" s="8" t="n"/>
+      <c r="O1834" s="23" t="n"/>
+    </row>
+    <row r="1835" ht="30" customHeight="1">
+      <c r="B1835" s="32" t="inlineStr">
+        <is>
+          <t>Qué destraba: Todas las tareas «Conectar con la API» de la web</t>
+        </is>
+      </c>
+      <c r="C1835" s="8" t="n"/>
+      <c r="D1835" s="8" t="n"/>
+      <c r="E1835" s="23" t="n"/>
+      <c r="G1835" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1835" s="34" t="inlineStr">
+        <is>
+          <t>L2 · Nombre corto en forma de acción — Cumple</t>
+        </is>
+      </c>
+      <c r="I1835" s="8" t="n"/>
+      <c r="J1835" s="23" t="n"/>
+      <c r="L1835" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1835" s="34" t="inlineStr">
+        <is>
+          <t>Los campos se han convertido entre snake_case y camelCase en un solo lugar</t>
+        </is>
+      </c>
+      <c r="N1835" s="8" t="n"/>
+      <c r="O1835" s="23" t="n"/>
+    </row>
+    <row r="1836" ht="30" customHeight="1">
+      <c r="B1836" s="32" t="inlineStr">
+        <is>
+          <t>Responsable técnico: Henry</t>
+        </is>
+      </c>
+      <c r="C1836" s="8" t="n"/>
+      <c r="D1836" s="8" t="n"/>
+      <c r="E1836" s="23" t="n"/>
+      <c r="G1836" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1836" s="34" t="inlineStr">
+        <is>
+          <t>L3 · Criterios de aceptación escritos — Cumple</t>
+        </is>
+      </c>
+      <c r="I1836" s="8" t="n"/>
+      <c r="J1836" s="23" t="n"/>
+      <c r="L1836" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1836" s="34" t="inlineStr">
+        <is>
+          <t>Un error {codigo, mensaje} de la API se ha mostrado igual que los errores simulados</t>
+        </is>
+      </c>
+      <c r="N1836" s="8" t="n"/>
+      <c r="O1836" s="23" t="n"/>
+    </row>
+    <row r="1837" ht="30" customHeight="1">
+      <c r="B1837" s="36" t="inlineStr">
+        <is>
+          <t>Depende de: HT-01</t>
+        </is>
+      </c>
+      <c r="C1837" s="37" t="n"/>
+      <c r="D1837" s="37" t="n"/>
+      <c r="E1837" s="38" t="n"/>
+      <c r="G1837" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1837" s="34" t="inlineStr">
+        <is>
+          <t>L4 · Dependencias resueltas — Cumple</t>
+        </is>
+      </c>
+      <c r="I1837" s="8" t="n"/>
+      <c r="J1837" s="23" t="n"/>
+      <c r="L1837" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1837" s="34" t="inlineStr">
+        <is>
+          <t>Lo que la API aún no tiene ha seguido funcionando con el cliente simulado</t>
+        </is>
+      </c>
+      <c r="N1837" s="8" t="n"/>
+      <c r="O1837" s="23" t="n"/>
+    </row>
+    <row r="1838" ht="36" customHeight="1">
+      <c r="G1838" s="40" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1838" s="34" t="inlineStr">
+        <is>
+          <t>L5 · Estimada por los Developers — No cumple: se vota en el próximo Daily</t>
+        </is>
+      </c>
+      <c r="I1838" s="8" t="n"/>
+      <c r="J1838" s="23" t="n"/>
+      <c r="L1838" s="36" t="inlineStr">
+        <is>
+          <t>Mitad técnica: Además, los criterios T1 a T10 de la hoja «3. Criterios DoR y DoD» que le apliquen</t>
+        </is>
+      </c>
+      <c r="M1838" s="37" t="n"/>
+      <c r="N1838" s="37" t="n"/>
+      <c r="O1838" s="38" t="n"/>
+    </row>
+    <row r="1839" ht="30" customHeight="1">
+      <c r="G1839" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1839" s="34" t="inlineStr">
+        <is>
+          <t>L6 · Cabe en un sprint (8 puntos o menos) — Cumple</t>
+        </is>
+      </c>
+      <c r="I1839" s="8" t="n"/>
+      <c r="J1839" s="23" t="n"/>
+    </row>
+    <row r="1840" ht="30" customHeight="1">
+      <c r="G1840" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1840" s="34" t="inlineStr">
+        <is>
+          <t>L7 · Reglas de dominio identificadas — Cumple</t>
+        </is>
+      </c>
+      <c r="I1840" s="8" t="n"/>
+      <c r="J1840" s="23" t="n"/>
+    </row>
+    <row r="1841" ht="30" customHeight="1">
+      <c r="G1841" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1841" s="34" t="inlineStr">
+        <is>
+          <t>L8 · Datos de prueba disponibles — Cumple</t>
+        </is>
+      </c>
+      <c r="I1841" s="8" t="n"/>
+      <c r="J1841" s="23" t="n"/>
+    </row>
+    <row r="1842" ht="30" customHeight="1">
+      <c r="G1842" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1842" s="34" t="inlineStr">
+        <is>
+          <t>L9 · Responsable técnico asignado — Cumple</t>
+        </is>
+      </c>
+      <c r="I1842" s="8" t="n"/>
+      <c r="J1842" s="23" t="n"/>
+    </row>
+    <row r="1843" ht="30" customHeight="1">
+      <c r="G1843" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1843" s="34" t="inlineStr">
+        <is>
+          <t>L10 · Recursos identificados — Cumple: Henry + equipo</t>
+        </is>
+      </c>
+      <c r="I1843" s="8" t="n"/>
+      <c r="J1843" s="23" t="n"/>
+    </row>
+    <row r="1844" ht="30" customHeight="1">
+      <c r="G1844" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1844" s="34" t="inlineStr">
+        <is>
+          <t>L11 · Requisitos técnicos de programación definidos — Cumple: React 18 y TypeScript (fetch)</t>
+        </is>
+      </c>
+      <c r="I1844" s="8" t="n"/>
+      <c r="J1844" s="23" t="n"/>
+    </row>
+    <row r="1845" ht="30" customHeight="1">
+      <c r="G1845" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1845" s="34" t="inlineStr">
+        <is>
+          <t>L12 · Accesos de red disponibles — Cumple: API en el ambiente de pruebas</t>
+        </is>
+      </c>
+      <c r="I1845" s="8" t="n"/>
+      <c r="J1845" s="23" t="n"/>
+    </row>
+    <row r="1846" ht="36" customHeight="1">
+      <c r="G1846" s="39" t="inlineStr">
+        <is>
+          <t>Riesgos: Diferencias de nombres entre API y web · convertir snake_case ↔ camelCase en un solo archivo</t>
+        </is>
+      </c>
+      <c r="H1846" s="8" t="n"/>
+      <c r="I1846" s="8" t="n"/>
+      <c r="J1846" s="23" t="n"/>
+    </row>
+    <row r="1847" ht="36" customHeight="1">
+      <c r="G1847" s="32" t="inlineStr">
+        <is>
+          <t>Proveedores de servicio: API en el ambiente de pruebas</t>
+        </is>
+      </c>
+      <c r="H1847" s="8" t="n"/>
+      <c r="I1847" s="8" t="n"/>
+      <c r="J1847" s="23" t="n"/>
+    </row>
+    <row r="1848" ht="36" customHeight="1">
+      <c r="G1848" s="36" t="inlineStr">
+        <is>
+          <t>Costos: S/ 0 en servicios (planes gratuitos) · horas según la votación</t>
+        </is>
+      </c>
+      <c r="H1848" s="37" t="n"/>
+      <c r="I1848" s="37" t="n"/>
+      <c r="J1848" s="38" t="n"/>
+    </row>
+    <row r="1851">
+      <c r="B1851" s="18" t="inlineStr">
+        <is>
+          <t>HT-05 · Crear la base de la app Android (historia técnica)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1852" ht="18" customHeight="1">
+      <c r="B1852" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 1 · Historia técnica</t>
+        </is>
+      </c>
+      <c r="C1852" s="20" t="n"/>
+      <c r="D1852" s="20" t="n"/>
+      <c r="E1852" s="21" t="n"/>
+      <c r="G1852" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 2 · Definición de Listo</t>
+        </is>
+      </c>
+      <c r="H1852" s="20" t="n"/>
+      <c r="I1852" s="20" t="n"/>
+      <c r="J1852" s="21" t="n"/>
+      <c r="L1852" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 3 · Definición de Terminado</t>
+        </is>
+      </c>
+      <c r="M1852" s="20" t="n"/>
+      <c r="N1852" s="20" t="n"/>
+      <c r="O1852" s="21" t="n"/>
+    </row>
+    <row r="1853" ht="28" customHeight="1">
+      <c r="B1853" s="22" t="inlineStr">
+        <is>
+          <t>Habilita a las HU de usuario: no entrega una función al usuario final</t>
+        </is>
+      </c>
+      <c r="C1853" s="8" t="n"/>
+      <c r="D1853" s="8" t="n"/>
+      <c r="E1853" s="23" t="n"/>
+      <c r="G1853" s="22" t="inlineStr">
+        <is>
+          <t>El enfoque está en la consideración del equipo de desarrollo sobre si la historia está lista para un Sprint</t>
+        </is>
+      </c>
+      <c r="H1853" s="8" t="n"/>
+      <c r="I1853" s="8" t="n"/>
+      <c r="J1853" s="23" t="n"/>
+      <c r="L1853" s="22" t="inlineStr">
+        <is>
+          <t>El enfoque está en la aceptación del cliente cuando se le entregue el producto</t>
+        </is>
+      </c>
+      <c r="M1853" s="8" t="n"/>
+      <c r="N1853" s="8" t="n"/>
+      <c r="O1853" s="23" t="n"/>
+    </row>
+    <row r="1854">
+      <c r="B1854" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="C1854" s="8" t="n"/>
+      <c r="D1854" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="E1854" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="G1854" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="H1854" s="8" t="n"/>
+      <c r="I1854" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="J1854" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="L1854" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="M1854" s="8" t="n"/>
+      <c r="N1854" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="O1854" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+    </row>
+    <row r="1855" ht="30" customHeight="1">
+      <c r="B1855" s="27" t="inlineStr">
+        <is>
+          <t>HT-05 · Crear la base de la app Android</t>
+        </is>
+      </c>
+      <c r="C1855" s="8" t="n"/>
+      <c r="D1855" s="9" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="E1855" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+      <c r="G1855" s="27" t="inlineStr">
+        <is>
+          <t>HT-05 · Crear la base de la app Android</t>
+        </is>
+      </c>
+      <c r="H1855" s="8" t="n"/>
+      <c r="I1855" s="9" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J1855" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+      <c r="L1855" s="27" t="inlineStr">
+        <is>
+          <t>HT-05 · Crear la base de la app Android</t>
+        </is>
+      </c>
+      <c r="M1855" s="8" t="n"/>
+      <c r="N1855" s="9" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="O1855" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="B1856" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="C1856" s="8" t="n"/>
+      <c r="D1856" s="8" t="n"/>
+      <c r="E1856" s="23" t="n"/>
+      <c r="G1856" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="H1856" s="8" t="n"/>
+      <c r="I1856" s="8" t="n"/>
+      <c r="J1856" s="23" t="n"/>
+      <c r="L1856" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="M1856" s="8" t="n"/>
+      <c r="N1856" s="8" t="n"/>
+      <c r="O1856" s="23" t="n"/>
+    </row>
+    <row r="1857" ht="28" customHeight="1">
+      <c r="B1857" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero el proyecto base de la app con Compose, Room, WorkManager, sesión y cliente de la API, para construir encima las pantallas del almacenero.</t>
+        </is>
+      </c>
+      <c r="C1857" s="8" t="n"/>
+      <c r="D1857" s="8" t="n"/>
+      <c r="E1857" s="23" t="n"/>
+      <c r="G1857" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero el proyecto base de la app con Compose, Room, WorkManager, sesión y cliente de la API, para construir encima las pantallas del almacenero.</t>
+        </is>
+      </c>
+      <c r="H1857" s="8" t="n"/>
+      <c r="I1857" s="8" t="n"/>
+      <c r="J1857" s="23" t="n"/>
+      <c r="L1857" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero el proyecto base de la app con Compose, Room, WorkManager, sesión y cliente de la API, para construir encima las pantallas del almacenero.</t>
+        </is>
+      </c>
+      <c r="M1857" s="8" t="n"/>
+      <c r="N1857" s="8" t="n"/>
+      <c r="O1857" s="23" t="n"/>
+    </row>
+    <row r="1858" ht="28" customHeight="1">
+      <c r="B1858" s="31" t="n"/>
+      <c r="C1858" s="8" t="n"/>
+      <c r="D1858" s="8" t="n"/>
+      <c r="E1858" s="23" t="n"/>
+      <c r="G1858" s="31" t="n"/>
+      <c r="H1858" s="8" t="n"/>
+      <c r="I1858" s="8" t="n"/>
+      <c r="J1858" s="23" t="n"/>
+      <c r="L1858" s="31" t="n"/>
+      <c r="M1858" s="8" t="n"/>
+      <c r="N1858" s="8" t="n"/>
+      <c r="O1858" s="23" t="n"/>
+    </row>
+    <row r="1859">
+      <c r="B1859" s="29" t="inlineStr">
+        <is>
+          <t>Ficha de la historia</t>
+        </is>
+      </c>
+      <c r="C1859" s="8" t="n"/>
+      <c r="D1859" s="8" t="n"/>
+      <c r="E1859" s="23" t="n"/>
+      <c r="G1859" s="29" t="inlineStr">
+        <is>
+          <t>Criterios de listo:</t>
+        </is>
+      </c>
+      <c r="H1859" s="8" t="n"/>
+      <c r="I1859" s="8" t="n"/>
+      <c r="J1859" s="23" t="n"/>
+      <c r="L1859" s="29" t="inlineStr">
+        <is>
+          <t>Condiciones finales (se marcan cuando el PO acepta la historia en la Review):</t>
+        </is>
+      </c>
+      <c r="M1859" s="8" t="n"/>
+      <c r="N1859" s="8" t="n"/>
+      <c r="O1859" s="23" t="n"/>
+    </row>
+    <row r="1860" ht="30" customHeight="1">
+      <c r="B1860" s="32" t="inlineStr">
+        <is>
+          <t>Tipo: Historia técnica (habilitadora)</t>
+        </is>
+      </c>
+      <c r="C1860" s="8" t="n"/>
+      <c r="D1860" s="8" t="n"/>
+      <c r="E1860" s="23" t="n"/>
+      <c r="G1860" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1860" s="34" t="inlineStr">
+        <is>
+          <t>L1 · Redactada en el formato acordado — Cumple</t>
+        </is>
+      </c>
+      <c r="I1860" s="8" t="n"/>
+      <c r="J1860" s="23" t="n"/>
+      <c r="L1860" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1860" s="34" t="inlineStr">
+        <is>
+          <t>La app se ha instalado en un teléfono real y ha iniciado sesión contra la API</t>
+        </is>
+      </c>
+      <c r="N1860" s="8" t="n"/>
+      <c r="O1860" s="23" t="n"/>
+    </row>
+    <row r="1861" ht="30" customHeight="1">
+      <c r="B1861" s="32" t="inlineStr">
+        <is>
+          <t>Qué destraba: Todas las HU de la app (HU-12, 15, 35, 37, 38, 40, 43, 62 y 63)</t>
+        </is>
+      </c>
+      <c r="C1861" s="8" t="n"/>
+      <c r="D1861" s="8" t="n"/>
+      <c r="E1861" s="23" t="n"/>
+      <c r="G1861" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1861" s="34" t="inlineStr">
+        <is>
+          <t>L2 · Nombre corto en forma de acción — Cumple</t>
+        </is>
+      </c>
+      <c r="I1861" s="8" t="n"/>
+      <c r="J1861" s="23" t="n"/>
+      <c r="L1861" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1861" s="34" t="inlineStr">
+        <is>
+          <t>Room ha guardado un dato local que ha sobrevivido al cierre de la app</t>
+        </is>
+      </c>
+      <c r="N1861" s="8" t="n"/>
+      <c r="O1861" s="23" t="n"/>
+    </row>
+    <row r="1862" ht="30" customHeight="1">
+      <c r="B1862" s="32" t="inlineStr">
+        <is>
+          <t>Responsable técnico: Nicolás</t>
+        </is>
+      </c>
+      <c r="C1862" s="8" t="n"/>
+      <c r="D1862" s="8" t="n"/>
+      <c r="E1862" s="23" t="n"/>
+      <c r="G1862" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1862" s="34" t="inlineStr">
+        <is>
+          <t>L3 · Criterios de aceptación escritos — Cumple</t>
+        </is>
+      </c>
+      <c r="I1862" s="8" t="n"/>
+      <c r="J1862" s="23" t="n"/>
+      <c r="L1862" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1862" s="34" t="inlineStr">
+        <is>
+          <t>WorkManager ha ejecutado un trabajo de prueba al recuperar la conexión</t>
+        </is>
+      </c>
+      <c r="N1862" s="8" t="n"/>
+      <c r="O1862" s="23" t="n"/>
+    </row>
+    <row r="1863" ht="30" customHeight="1">
+      <c r="B1863" s="36" t="inlineStr">
+        <is>
+          <t>Depende de: HT-01</t>
+        </is>
+      </c>
+      <c r="C1863" s="37" t="n"/>
+      <c r="D1863" s="37" t="n"/>
+      <c r="E1863" s="38" t="n"/>
+      <c r="G1863" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1863" s="34" t="inlineStr">
+        <is>
+          <t>L4 · Dependencias resueltas — Cumple</t>
+        </is>
+      </c>
+      <c r="I1863" s="8" t="n"/>
+      <c r="J1863" s="23" t="n"/>
+      <c r="L1863" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1863" s="34" t="inlineStr">
+        <is>
+          <t>El APK de pruebas se ha generado desde el repositorio</t>
+        </is>
+      </c>
+      <c r="N1863" s="8" t="n"/>
+      <c r="O1863" s="23" t="n"/>
+    </row>
+    <row r="1864" ht="36" customHeight="1">
+      <c r="G1864" s="40" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1864" s="34" t="inlineStr">
+        <is>
+          <t>L5 · Estimada por los Developers — No cumple: se vota en el próximo Daily</t>
+        </is>
+      </c>
+      <c r="I1864" s="8" t="n"/>
+      <c r="J1864" s="23" t="n"/>
+      <c r="L1864" s="36" t="inlineStr">
+        <is>
+          <t>Mitad técnica: Además, los criterios T1 a T10 de la hoja «3. Criterios DoR y DoD» que le apliquen</t>
+        </is>
+      </c>
+      <c r="M1864" s="37" t="n"/>
+      <c r="N1864" s="37" t="n"/>
+      <c r="O1864" s="38" t="n"/>
+    </row>
+    <row r="1865" ht="30" customHeight="1">
+      <c r="G1865" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1865" s="34" t="inlineStr">
+        <is>
+          <t>L6 · Cabe en un sprint (8 puntos o menos) — Cumple</t>
+        </is>
+      </c>
+      <c r="I1865" s="8" t="n"/>
+      <c r="J1865" s="23" t="n"/>
+    </row>
+    <row r="1866" ht="30" customHeight="1">
+      <c r="G1866" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1866" s="34" t="inlineStr">
+        <is>
+          <t>L7 · Reglas de dominio identificadas — Cumple</t>
+        </is>
+      </c>
+      <c r="I1866" s="8" t="n"/>
+      <c r="J1866" s="23" t="n"/>
+    </row>
+    <row r="1867" ht="30" customHeight="1">
+      <c r="G1867" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1867" s="34" t="inlineStr">
+        <is>
+          <t>L8 · Datos de prueba disponibles — Cumple</t>
+        </is>
+      </c>
+      <c r="I1867" s="8" t="n"/>
+      <c r="J1867" s="23" t="n"/>
+    </row>
+    <row r="1868" ht="30" customHeight="1">
+      <c r="G1868" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1868" s="34" t="inlineStr">
+        <is>
+          <t>L9 · Responsable técnico asignado — Cumple</t>
+        </is>
+      </c>
+      <c r="I1868" s="8" t="n"/>
+      <c r="J1868" s="23" t="n"/>
+    </row>
+    <row r="1869" ht="30" customHeight="1">
+      <c r="G1869" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1869" s="34" t="inlineStr">
+        <is>
+          <t>L10 · Recursos identificados — Cumple: Nicolás + equipo</t>
+        </is>
+      </c>
+      <c r="I1869" s="8" t="n"/>
+      <c r="J1869" s="23" t="n"/>
+    </row>
+    <row r="1870" ht="30" customHeight="1">
+      <c r="G1870" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1870" s="34" t="inlineStr">
+        <is>
+          <t>L11 · Requisitos técnicos de programación definidos — Cumple: Kotlin, Compose, Room y WorkManager</t>
+        </is>
+      </c>
+      <c r="I1870" s="8" t="n"/>
+      <c r="J1870" s="23" t="n"/>
+    </row>
+    <row r="1871" ht="30" customHeight="1">
+      <c r="G1871" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1871" s="34" t="inlineStr">
+        <is>
+          <t>L12 · Accesos de red disponibles — Cumple: Android Studio · teléfono de prueba · API en el ambiente de pruebas</t>
+        </is>
+      </c>
+      <c r="I1871" s="8" t="n"/>
+      <c r="J1871" s="23" t="n"/>
+    </row>
+    <row r="1872" ht="36" customHeight="1">
+      <c r="G1872" s="39" t="inlineStr">
+        <is>
+          <t>Riesgos: Configuración de Gradle que consume el sprint · partir de la plantilla oficial de Compose</t>
+        </is>
+      </c>
+      <c r="H1872" s="8" t="n"/>
+      <c r="I1872" s="8" t="n"/>
+      <c r="J1872" s="23" t="n"/>
+    </row>
+    <row r="1873" ht="36" customHeight="1">
+      <c r="G1873" s="32" t="inlineStr">
+        <is>
+          <t>Proveedores de servicio: Android Studio · teléfono de prueba · API en el ambiente de pruebas</t>
+        </is>
+      </c>
+      <c r="H1873" s="8" t="n"/>
+      <c r="I1873" s="8" t="n"/>
+      <c r="J1873" s="23" t="n"/>
+    </row>
+    <row r="1874" ht="36" customHeight="1">
+      <c r="G1874" s="36" t="inlineStr">
+        <is>
+          <t>Costos: S/ 0 en servicios (planes gratuitos) · horas según la votación</t>
+        </is>
+      </c>
+      <c r="H1874" s="37" t="n"/>
+      <c r="I1874" s="37" t="n"/>
+      <c r="J1874" s="38" t="n"/>
+    </row>
+    <row r="1877">
+      <c r="B1877" s="18" t="inlineStr">
+        <is>
+          <t>HT-06 · Publicar el contrato de la API y Postman (historia técnica)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1878" ht="18" customHeight="1">
+      <c r="B1878" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 1 · Historia técnica</t>
+        </is>
+      </c>
+      <c r="C1878" s="20" t="n"/>
+      <c r="D1878" s="20" t="n"/>
+      <c r="E1878" s="21" t="n"/>
+      <c r="G1878" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 2 · Definición de Listo</t>
+        </is>
+      </c>
+      <c r="H1878" s="20" t="n"/>
+      <c r="I1878" s="20" t="n"/>
+      <c r="J1878" s="21" t="n"/>
+      <c r="L1878" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 3 · Definición de Terminado</t>
+        </is>
+      </c>
+      <c r="M1878" s="20" t="n"/>
+      <c r="N1878" s="20" t="n"/>
+      <c r="O1878" s="21" t="n"/>
+    </row>
+    <row r="1879" ht="28" customHeight="1">
+      <c r="B1879" s="22" t="inlineStr">
+        <is>
+          <t>Habilita a las HU de usuario: no entrega una función al usuario final</t>
+        </is>
+      </c>
+      <c r="C1879" s="8" t="n"/>
+      <c r="D1879" s="8" t="n"/>
+      <c r="E1879" s="23" t="n"/>
+      <c r="G1879" s="22" t="inlineStr">
+        <is>
+          <t>El enfoque está en la consideración del equipo de desarrollo sobre si la historia está lista para un Sprint</t>
+        </is>
+      </c>
+      <c r="H1879" s="8" t="n"/>
+      <c r="I1879" s="8" t="n"/>
+      <c r="J1879" s="23" t="n"/>
+      <c r="L1879" s="22" t="inlineStr">
+        <is>
+          <t>El enfoque está en la aceptación del cliente cuando se le entregue el producto</t>
+        </is>
+      </c>
+      <c r="M1879" s="8" t="n"/>
+      <c r="N1879" s="8" t="n"/>
+      <c r="O1879" s="23" t="n"/>
+    </row>
+    <row r="1880">
+      <c r="B1880" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="C1880" s="8" t="n"/>
+      <c r="D1880" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="E1880" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="G1880" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="H1880" s="8" t="n"/>
+      <c r="I1880" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="J1880" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="L1880" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="M1880" s="8" t="n"/>
+      <c r="N1880" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="O1880" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+    </row>
+    <row r="1881" ht="30" customHeight="1">
+      <c r="B1881" s="27" t="inlineStr">
+        <is>
+          <t>HT-06 · Publicar el contrato de la API y Postman</t>
+        </is>
+      </c>
+      <c r="C1881" s="8" t="n"/>
+      <c r="D1881" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E1881" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+      <c r="G1881" s="27" t="inlineStr">
+        <is>
+          <t>HT-06 · Publicar el contrato de la API y Postman</t>
+        </is>
+      </c>
+      <c r="H1881" s="8" t="n"/>
+      <c r="I1881" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J1881" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+      <c r="L1881" s="27" t="inlineStr">
+        <is>
+          <t>HT-06 · Publicar el contrato de la API y Postman</t>
+        </is>
+      </c>
+      <c r="M1881" s="8" t="n"/>
+      <c r="N1881" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="O1881" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="B1882" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="C1882" s="8" t="n"/>
+      <c r="D1882" s="8" t="n"/>
+      <c r="E1882" s="23" t="n"/>
+      <c r="G1882" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="H1882" s="8" t="n"/>
+      <c r="I1882" s="8" t="n"/>
+      <c r="J1882" s="23" t="n"/>
+      <c r="L1882" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="M1882" s="8" t="n"/>
+      <c r="N1882" s="8" t="n"/>
+      <c r="O1882" s="23" t="n"/>
+    </row>
+    <row r="1883" ht="28" customHeight="1">
+      <c r="B1883" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero el contrato de la API publicado (OpenAPI) y una colección de Postman compartida, para probar cada endpoint igual y sin adivinar cómo llamarlo.</t>
+        </is>
+      </c>
+      <c r="C1883" s="8" t="n"/>
+      <c r="D1883" s="8" t="n"/>
+      <c r="E1883" s="23" t="n"/>
+      <c r="G1883" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero el contrato de la API publicado (OpenAPI) y una colección de Postman compartida, para probar cada endpoint igual y sin adivinar cómo llamarlo.</t>
+        </is>
+      </c>
+      <c r="H1883" s="8" t="n"/>
+      <c r="I1883" s="8" t="n"/>
+      <c r="J1883" s="23" t="n"/>
+      <c r="L1883" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero el contrato de la API publicado (OpenAPI) y una colección de Postman compartida, para probar cada endpoint igual y sin adivinar cómo llamarlo.</t>
+        </is>
+      </c>
+      <c r="M1883" s="8" t="n"/>
+      <c r="N1883" s="8" t="n"/>
+      <c r="O1883" s="23" t="n"/>
+    </row>
+    <row r="1884" ht="28" customHeight="1">
+      <c r="B1884" s="31" t="n"/>
+      <c r="C1884" s="8" t="n"/>
+      <c r="D1884" s="8" t="n"/>
+      <c r="E1884" s="23" t="n"/>
+      <c r="G1884" s="31" t="n"/>
+      <c r="H1884" s="8" t="n"/>
+      <c r="I1884" s="8" t="n"/>
+      <c r="J1884" s="23" t="n"/>
+      <c r="L1884" s="31" t="n"/>
+      <c r="M1884" s="8" t="n"/>
+      <c r="N1884" s="8" t="n"/>
+      <c r="O1884" s="23" t="n"/>
+    </row>
+    <row r="1885">
+      <c r="B1885" s="29" t="inlineStr">
+        <is>
+          <t>Ficha de la historia</t>
+        </is>
+      </c>
+      <c r="C1885" s="8" t="n"/>
+      <c r="D1885" s="8" t="n"/>
+      <c r="E1885" s="23" t="n"/>
+      <c r="G1885" s="29" t="inlineStr">
+        <is>
+          <t>Criterios de listo:</t>
+        </is>
+      </c>
+      <c r="H1885" s="8" t="n"/>
+      <c r="I1885" s="8" t="n"/>
+      <c r="J1885" s="23" t="n"/>
+      <c r="L1885" s="29" t="inlineStr">
+        <is>
+          <t>Condiciones finales (se marcan cuando el PO acepta la historia en la Review):</t>
+        </is>
+      </c>
+      <c r="M1885" s="8" t="n"/>
+      <c r="N1885" s="8" t="n"/>
+      <c r="O1885" s="23" t="n"/>
+    </row>
+    <row r="1886" ht="30" customHeight="1">
+      <c r="B1886" s="32" t="inlineStr">
+        <is>
+          <t>Tipo: Historia técnica (habilitadora)</t>
+        </is>
+      </c>
+      <c r="C1886" s="8" t="n"/>
+      <c r="D1886" s="8" t="n"/>
+      <c r="E1886" s="23" t="n"/>
+      <c r="G1886" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1886" s="34" t="inlineStr">
+        <is>
+          <t>L1 · Redactada en el formato acordado — Cumple</t>
+        </is>
+      </c>
+      <c r="I1886" s="8" t="n"/>
+      <c r="J1886" s="23" t="n"/>
+      <c r="L1886" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1886" s="34" t="inlineStr">
+        <is>
+          <t>El OpenAPI se ha publicado en el ambiente de pruebas (/docs)</t>
+        </is>
+      </c>
+      <c r="N1886" s="8" t="n"/>
+      <c r="O1886" s="23" t="n"/>
+    </row>
+    <row r="1887" ht="30" customHeight="1">
+      <c r="B1887" s="32" t="inlineStr">
+        <is>
+          <t>Qué destraba: La prueba con Postman de cada HU (modelo del docente)</t>
+        </is>
+      </c>
+      <c r="C1887" s="8" t="n"/>
+      <c r="D1887" s="8" t="n"/>
+      <c r="E1887" s="23" t="n"/>
+      <c r="G1887" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1887" s="34" t="inlineStr">
+        <is>
+          <t>L2 · Nombre corto en forma de acción — Cumple</t>
+        </is>
+      </c>
+      <c r="I1887" s="8" t="n"/>
+      <c r="J1887" s="23" t="n"/>
+      <c r="L1887" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1887" s="34" t="inlineStr">
+        <is>
+          <t>La colección de Postman se ha compartido con el equipo, con un entorno de pruebas y el login ya configurado</t>
+        </is>
+      </c>
+      <c r="N1887" s="8" t="n"/>
+      <c r="O1887" s="23" t="n"/>
+    </row>
+    <row r="1888" ht="30" customHeight="1">
+      <c r="B1888" s="32" t="inlineStr">
+        <is>
+          <t>Responsable técnico: Adiel</t>
+        </is>
+      </c>
+      <c r="C1888" s="8" t="n"/>
+      <c r="D1888" s="8" t="n"/>
+      <c r="E1888" s="23" t="n"/>
+      <c r="G1888" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1888" s="34" t="inlineStr">
+        <is>
+          <t>L3 · Criterios de aceptación escritos — Cumple</t>
+        </is>
+      </c>
+      <c r="I1888" s="8" t="n"/>
+      <c r="J1888" s="23" t="n"/>
+      <c r="L1888" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1888" s="34" t="inlineStr">
+        <is>
+          <t>Cada endpoint del Sprint 1 ha quedado con al menos un ejemplo de llamada correcta y uno de error</t>
+        </is>
+      </c>
+      <c r="N1888" s="8" t="n"/>
+      <c r="O1888" s="23" t="n"/>
+    </row>
+    <row r="1889" ht="36" customHeight="1">
+      <c r="B1889" s="36" t="inlineStr">
+        <is>
+          <t>Depende de: HT-01</t>
+        </is>
+      </c>
+      <c r="C1889" s="37" t="n"/>
+      <c r="D1889" s="37" t="n"/>
+      <c r="E1889" s="38" t="n"/>
+      <c r="G1889" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1889" s="34" t="inlineStr">
+        <is>
+          <t>L4 · Dependencias resueltas — Cumple</t>
+        </is>
+      </c>
+      <c r="I1889" s="8" t="n"/>
+      <c r="J1889" s="23" t="n"/>
+      <c r="L1889" s="36" t="inlineStr">
+        <is>
+          <t>Mitad técnica: Además, los criterios T1 a T10 de la hoja «3. Criterios DoR y DoD» que le apliquen</t>
+        </is>
+      </c>
+      <c r="M1889" s="37" t="n"/>
+      <c r="N1889" s="37" t="n"/>
+      <c r="O1889" s="38" t="n"/>
+    </row>
+    <row r="1890" ht="30" customHeight="1">
+      <c r="G1890" s="40" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1890" s="34" t="inlineStr">
+        <is>
+          <t>L5 · Estimada por los Developers — No cumple: se vota en el próximo Daily</t>
+        </is>
+      </c>
+      <c r="I1890" s="8" t="n"/>
+      <c r="J1890" s="23" t="n"/>
+    </row>
+    <row r="1891" ht="30" customHeight="1">
+      <c r="G1891" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1891" s="34" t="inlineStr">
+        <is>
+          <t>L6 · Cabe en un sprint (8 puntos o menos) — Cumple</t>
+        </is>
+      </c>
+      <c r="I1891" s="8" t="n"/>
+      <c r="J1891" s="23" t="n"/>
+    </row>
+    <row r="1892" ht="30" customHeight="1">
+      <c r="G1892" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1892" s="34" t="inlineStr">
+        <is>
+          <t>L7 · Reglas de dominio identificadas — Cumple</t>
+        </is>
+      </c>
+      <c r="I1892" s="8" t="n"/>
+      <c r="J1892" s="23" t="n"/>
+    </row>
+    <row r="1893" ht="30" customHeight="1">
+      <c r="G1893" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1893" s="34" t="inlineStr">
+        <is>
+          <t>L8 · Datos de prueba disponibles — Cumple</t>
+        </is>
+      </c>
+      <c r="I1893" s="8" t="n"/>
+      <c r="J1893" s="23" t="n"/>
+    </row>
+    <row r="1894" ht="30" customHeight="1">
+      <c r="G1894" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1894" s="34" t="inlineStr">
+        <is>
+          <t>L9 · Responsable técnico asignado — Cumple</t>
+        </is>
+      </c>
+      <c r="I1894" s="8" t="n"/>
+      <c r="J1894" s="23" t="n"/>
+    </row>
+    <row r="1895" ht="30" customHeight="1">
+      <c r="G1895" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1895" s="34" t="inlineStr">
+        <is>
+          <t>L10 · Recursos identificados — Cumple: Adiel + equipo</t>
+        </is>
+      </c>
+      <c r="I1895" s="8" t="n"/>
+      <c r="J1895" s="23" t="n"/>
+    </row>
+    <row r="1896" ht="30" customHeight="1">
+      <c r="G1896" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1896" s="34" t="inlineStr">
+        <is>
+          <t>L11 · Requisitos técnicos de programación definidos — Cumple: FastAPI, pytest y GitHub Actions</t>
+        </is>
+      </c>
+      <c r="I1896" s="8" t="n"/>
+      <c r="J1896" s="23" t="n"/>
+    </row>
+    <row r="1897" ht="30" customHeight="1">
+      <c r="G1897" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1897" s="34" t="inlineStr">
+        <is>
+          <t>L12 · Accesos de red disponibles — Cumple: Postman (plan gratuito) · Swagger de FastAPI</t>
+        </is>
+      </c>
+      <c r="I1897" s="8" t="n"/>
+      <c r="J1897" s="23" t="n"/>
+    </row>
+    <row r="1898" ht="36" customHeight="1">
+      <c r="G1898" s="39" t="inlineStr">
+        <is>
+          <t>Riesgos: Colección desactualizada · generarla desde el OpenAPI de FastAPI</t>
+        </is>
+      </c>
+      <c r="H1898" s="8" t="n"/>
+      <c r="I1898" s="8" t="n"/>
+      <c r="J1898" s="23" t="n"/>
+    </row>
+    <row r="1899" ht="36" customHeight="1">
+      <c r="G1899" s="32" t="inlineStr">
+        <is>
+          <t>Proveedores de servicio: Postman (plan gratuito) · Swagger de FastAPI</t>
+        </is>
+      </c>
+      <c r="H1899" s="8" t="n"/>
+      <c r="I1899" s="8" t="n"/>
+      <c r="J1899" s="23" t="n"/>
+    </row>
+    <row r="1900" ht="36" customHeight="1">
+      <c r="G1900" s="36" t="inlineStr">
+        <is>
+          <t>Costos: S/ 0 en servicios (planes gratuitos) · horas según la votación</t>
+        </is>
+      </c>
+      <c r="H1900" s="37" t="n"/>
+      <c r="I1900" s="37" t="n"/>
+      <c r="J1900" s="38" t="n"/>
+    </row>
+    <row r="1903">
+      <c r="B1903" s="18" t="inlineStr">
+        <is>
+          <t>HT-07 · Cargar los datos de prueba reales (historia técnica)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1904" ht="18" customHeight="1">
+      <c r="B1904" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 1 · Historia técnica</t>
+        </is>
+      </c>
+      <c r="C1904" s="20" t="n"/>
+      <c r="D1904" s="20" t="n"/>
+      <c r="E1904" s="21" t="n"/>
+      <c r="G1904" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 2 · Definición de Listo</t>
+        </is>
+      </c>
+      <c r="H1904" s="20" t="n"/>
+      <c r="I1904" s="20" t="n"/>
+      <c r="J1904" s="21" t="n"/>
+      <c r="L1904" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 3 · Definición de Terminado</t>
+        </is>
+      </c>
+      <c r="M1904" s="20" t="n"/>
+      <c r="N1904" s="20" t="n"/>
+      <c r="O1904" s="21" t="n"/>
+    </row>
+    <row r="1905" ht="28" customHeight="1">
+      <c r="B1905" s="22" t="inlineStr">
+        <is>
+          <t>Habilita a las HU de usuario: no entrega una función al usuario final</t>
+        </is>
+      </c>
+      <c r="C1905" s="8" t="n"/>
+      <c r="D1905" s="8" t="n"/>
+      <c r="E1905" s="23" t="n"/>
+      <c r="G1905" s="22" t="inlineStr">
+        <is>
+          <t>El enfoque está en la consideración del equipo de desarrollo sobre si la historia está lista para un Sprint</t>
+        </is>
+      </c>
+      <c r="H1905" s="8" t="n"/>
+      <c r="I1905" s="8" t="n"/>
+      <c r="J1905" s="23" t="n"/>
+      <c r="L1905" s="22" t="inlineStr">
+        <is>
+          <t>El enfoque está en la aceptación del cliente cuando se le entregue el producto</t>
+        </is>
+      </c>
+      <c r="M1905" s="8" t="n"/>
+      <c r="N1905" s="8" t="n"/>
+      <c r="O1905" s="23" t="n"/>
+    </row>
+    <row r="1906">
+      <c r="B1906" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="C1906" s="8" t="n"/>
+      <c r="D1906" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="E1906" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="G1906" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="H1906" s="8" t="n"/>
+      <c r="I1906" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="J1906" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="L1906" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="M1906" s="8" t="n"/>
+      <c r="N1906" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="O1906" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+    </row>
+    <row r="1907" ht="30" customHeight="1">
+      <c r="B1907" s="27" t="inlineStr">
+        <is>
+          <t>HT-07 · Cargar los datos de prueba reales</t>
+        </is>
+      </c>
+      <c r="C1907" s="8" t="n"/>
+      <c r="D1907" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E1907" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+      <c r="G1907" s="27" t="inlineStr">
+        <is>
+          <t>HT-07 · Cargar los datos de prueba reales</t>
+        </is>
+      </c>
+      <c r="H1907" s="8" t="n"/>
+      <c r="I1907" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J1907" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+      <c r="L1907" s="27" t="inlineStr">
+        <is>
+          <t>HT-07 · Cargar los datos de prueba reales</t>
+        </is>
+      </c>
+      <c r="M1907" s="8" t="n"/>
+      <c r="N1907" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="O1907" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="B1908" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="C1908" s="8" t="n"/>
+      <c r="D1908" s="8" t="n"/>
+      <c r="E1908" s="23" t="n"/>
+      <c r="G1908" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="H1908" s="8" t="n"/>
+      <c r="I1908" s="8" t="n"/>
+      <c r="J1908" s="23" t="n"/>
+      <c r="L1908" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="M1908" s="8" t="n"/>
+      <c r="N1908" s="8" t="n"/>
+      <c r="O1908" s="23" t="n"/>
+    </row>
+    <row r="1909" ht="28" customHeight="1">
+      <c r="B1909" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero la base de pruebas cargada con los datos reales del cliente, para que ninguna HU se pruebe con datos inventados.</t>
+        </is>
+      </c>
+      <c r="C1909" s="8" t="n"/>
+      <c r="D1909" s="8" t="n"/>
+      <c r="E1909" s="23" t="n"/>
+      <c r="G1909" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero la base de pruebas cargada con los datos reales del cliente, para que ninguna HU se pruebe con datos inventados.</t>
+        </is>
+      </c>
+      <c r="H1909" s="8" t="n"/>
+      <c r="I1909" s="8" t="n"/>
+      <c r="J1909" s="23" t="n"/>
+      <c r="L1909" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero la base de pruebas cargada con los datos reales del cliente, para que ninguna HU se pruebe con datos inventados.</t>
+        </is>
+      </c>
+      <c r="M1909" s="8" t="n"/>
+      <c r="N1909" s="8" t="n"/>
+      <c r="O1909" s="23" t="n"/>
+    </row>
+    <row r="1910" ht="28" customHeight="1">
+      <c r="B1910" s="31" t="n"/>
+      <c r="C1910" s="8" t="n"/>
+      <c r="D1910" s="8" t="n"/>
+      <c r="E1910" s="23" t="n"/>
+      <c r="G1910" s="31" t="n"/>
+      <c r="H1910" s="8" t="n"/>
+      <c r="I1910" s="8" t="n"/>
+      <c r="J1910" s="23" t="n"/>
+      <c r="L1910" s="31" t="n"/>
+      <c r="M1910" s="8" t="n"/>
+      <c r="N1910" s="8" t="n"/>
+      <c r="O1910" s="23" t="n"/>
+    </row>
+    <row r="1911">
+      <c r="B1911" s="29" t="inlineStr">
+        <is>
+          <t>Ficha de la historia</t>
+        </is>
+      </c>
+      <c r="C1911" s="8" t="n"/>
+      <c r="D1911" s="8" t="n"/>
+      <c r="E1911" s="23" t="n"/>
+      <c r="G1911" s="29" t="inlineStr">
+        <is>
+          <t>Criterios de listo:</t>
+        </is>
+      </c>
+      <c r="H1911" s="8" t="n"/>
+      <c r="I1911" s="8" t="n"/>
+      <c r="J1911" s="23" t="n"/>
+      <c r="L1911" s="29" t="inlineStr">
+        <is>
+          <t>Condiciones finales (se marcan cuando el PO acepta la historia en la Review):</t>
+        </is>
+      </c>
+      <c r="M1911" s="8" t="n"/>
+      <c r="N1911" s="8" t="n"/>
+      <c r="O1911" s="23" t="n"/>
+    </row>
+    <row r="1912" ht="30" customHeight="1">
+      <c r="B1912" s="32" t="inlineStr">
+        <is>
+          <t>Tipo: Historia técnica (habilitadora)</t>
+        </is>
+      </c>
+      <c r="C1912" s="8" t="n"/>
+      <c r="D1912" s="8" t="n"/>
+      <c r="E1912" s="23" t="n"/>
+      <c r="G1912" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1912" s="34" t="inlineStr">
+        <is>
+          <t>L1 · Redactada en el formato acordado — Cumple</t>
+        </is>
+      </c>
+      <c r="I1912" s="8" t="n"/>
+      <c r="J1912" s="23" t="n"/>
+      <c r="L1912" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1912" s="34" t="inlineStr">
+        <is>
+          <t>Se han cargado los 626 proveedores y el catálogo de insumos del cliente</t>
+        </is>
+      </c>
+      <c r="N1912" s="8" t="n"/>
+      <c r="O1912" s="23" t="n"/>
+    </row>
+    <row r="1913" ht="30" customHeight="1">
+      <c r="B1913" s="32" t="inlineStr">
+        <is>
+          <t>Qué destraba: L8 de la DoR y las pruebas de importación</t>
+        </is>
+      </c>
+      <c r="C1913" s="8" t="n"/>
+      <c r="D1913" s="8" t="n"/>
+      <c r="E1913" s="23" t="n"/>
+      <c r="G1913" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1913" s="34" t="inlineStr">
+        <is>
+          <t>L2 · Nombre corto en forma de acción — Cumple</t>
+        </is>
+      </c>
+      <c r="I1913" s="8" t="n"/>
+      <c r="J1913" s="23" t="n"/>
+      <c r="L1913" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1913" s="34" t="inlineStr">
+        <is>
+          <t>Se ha creado la obra Multifamiliar Flores con su relación de insumos del S10</t>
+        </is>
+      </c>
+      <c r="N1913" s="8" t="n"/>
+      <c r="O1913" s="23" t="n"/>
+    </row>
+    <row r="1914" ht="30" customHeight="1">
+      <c r="B1914" s="32" t="inlineStr">
+        <is>
+          <t>Responsable técnico: Adiel</t>
+        </is>
+      </c>
+      <c r="C1914" s="8" t="n"/>
+      <c r="D1914" s="8" t="n"/>
+      <c r="E1914" s="23" t="n"/>
+      <c r="G1914" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1914" s="34" t="inlineStr">
+        <is>
+          <t>L3 · Criterios de aceptación escritos — Cumple</t>
+        </is>
+      </c>
+      <c r="I1914" s="8" t="n"/>
+      <c r="J1914" s="23" t="n"/>
+      <c r="L1914" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1914" s="34" t="inlineStr">
+        <is>
+          <t>Una segunda carga no ha duplicado ningún registro</t>
+        </is>
+      </c>
+      <c r="N1914" s="8" t="n"/>
+      <c r="O1914" s="23" t="n"/>
+    </row>
+    <row r="1915" ht="36" customHeight="1">
+      <c r="B1915" s="36" t="inlineStr">
+        <is>
+          <t>Depende de: HT-01</t>
+        </is>
+      </c>
+      <c r="C1915" s="37" t="n"/>
+      <c r="D1915" s="37" t="n"/>
+      <c r="E1915" s="38" t="n"/>
+      <c r="G1915" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1915" s="34" t="inlineStr">
+        <is>
+          <t>L4 · Dependencias resueltas — Cumple</t>
+        </is>
+      </c>
+      <c r="I1915" s="8" t="n"/>
+      <c r="J1915" s="23" t="n"/>
+      <c r="L1915" s="36" t="inlineStr">
+        <is>
+          <t>Mitad técnica: Además, los criterios T1 a T10 de la hoja «3. Criterios DoR y DoD» que le apliquen</t>
+        </is>
+      </c>
+      <c r="M1915" s="37" t="n"/>
+      <c r="N1915" s="37" t="n"/>
+      <c r="O1915" s="38" t="n"/>
+    </row>
+    <row r="1916" ht="30" customHeight="1">
+      <c r="G1916" s="40" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1916" s="34" t="inlineStr">
+        <is>
+          <t>L5 · Estimada por los Developers — No cumple: se vota en el próximo Daily</t>
+        </is>
+      </c>
+      <c r="I1916" s="8" t="n"/>
+      <c r="J1916" s="23" t="n"/>
+    </row>
+    <row r="1917" ht="30" customHeight="1">
+      <c r="G1917" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1917" s="34" t="inlineStr">
+        <is>
+          <t>L6 · Cabe en un sprint (8 puntos o menos) — Cumple</t>
+        </is>
+      </c>
+      <c r="I1917" s="8" t="n"/>
+      <c r="J1917" s="23" t="n"/>
+    </row>
+    <row r="1918" ht="30" customHeight="1">
+      <c r="G1918" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1918" s="34" t="inlineStr">
+        <is>
+          <t>L7 · Reglas de dominio identificadas — Cumple</t>
+        </is>
+      </c>
+      <c r="I1918" s="8" t="n"/>
+      <c r="J1918" s="23" t="n"/>
+    </row>
+    <row r="1919" ht="30" customHeight="1">
+      <c r="G1919" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1919" s="34" t="inlineStr">
+        <is>
+          <t>L8 · Datos de prueba disponibles — Cumple</t>
+        </is>
+      </c>
+      <c r="I1919" s="8" t="n"/>
+      <c r="J1919" s="23" t="n"/>
+    </row>
+    <row r="1920" ht="30" customHeight="1">
+      <c r="G1920" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1920" s="34" t="inlineStr">
+        <is>
+          <t>L9 · Responsable técnico asignado — Cumple</t>
+        </is>
+      </c>
+      <c r="I1920" s="8" t="n"/>
+      <c r="J1920" s="23" t="n"/>
+    </row>
+    <row r="1921" ht="30" customHeight="1">
+      <c r="G1921" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1921" s="34" t="inlineStr">
+        <is>
+          <t>L10 · Recursos identificados — Cumple: Adiel + equipo</t>
+        </is>
+      </c>
+      <c r="I1921" s="8" t="n"/>
+      <c r="J1921" s="23" t="n"/>
+    </row>
+    <row r="1922" ht="30" customHeight="1">
+      <c r="G1922" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1922" s="34" t="inlineStr">
+        <is>
+          <t>L11 · Requisitos técnicos de programación definidos — Cumple: FastAPI, pytest y GitHub Actions</t>
+        </is>
+      </c>
+      <c r="I1922" s="8" t="n"/>
+      <c r="J1922" s="23" t="n"/>
+    </row>
+    <row r="1923" ht="30" customHeight="1">
+      <c r="G1923" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1923" s="34" t="inlineStr">
+        <is>
+          <t>L12 · Accesos de red disponibles — Cumple: PostgreSQL de pruebas · archivos del cliente (S10, proveedores, catálogo)</t>
+        </is>
+      </c>
+      <c r="I1923" s="8" t="n"/>
+      <c r="J1923" s="23" t="n"/>
+    </row>
+    <row r="1924" ht="36" customHeight="1">
+      <c r="G1924" s="39" t="inlineStr">
+        <is>
+          <t>Riesgos: Cargar dos veces y duplicar · cargadores idempotentes con --dry-run</t>
+        </is>
+      </c>
+      <c r="H1924" s="8" t="n"/>
+      <c r="I1924" s="8" t="n"/>
+      <c r="J1924" s="23" t="n"/>
+    </row>
+    <row r="1925" ht="36" customHeight="1">
+      <c r="G1925" s="32" t="inlineStr">
+        <is>
+          <t>Proveedores de servicio: PostgreSQL de pruebas · archivos del cliente (S10, proveedores, catálogo)</t>
+        </is>
+      </c>
+      <c r="H1925" s="8" t="n"/>
+      <c r="I1925" s="8" t="n"/>
+      <c r="J1925" s="23" t="n"/>
+    </row>
+    <row r="1926" ht="36" customHeight="1">
+      <c r="G1926" s="36" t="inlineStr">
+        <is>
+          <t>Costos: S/ 0 en servicios (planes gratuitos) · horas según la votación</t>
+        </is>
+      </c>
+      <c r="H1926" s="37" t="n"/>
+      <c r="I1926" s="37" t="n"/>
+      <c r="J1926" s="38" t="n"/>
+    </row>
+    <row r="1929">
+      <c r="B1929" s="18" t="inlineStr">
+        <is>
+          <t>HT-08 · Autenticar a los servicios entre sí (historia técnica)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930" ht="18" customHeight="1">
+      <c r="B1930" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 1 · Historia técnica</t>
+        </is>
+      </c>
+      <c r="C1930" s="20" t="n"/>
+      <c r="D1930" s="20" t="n"/>
+      <c r="E1930" s="21" t="n"/>
+      <c r="G1930" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 2 · Definición de Listo</t>
+        </is>
+      </c>
+      <c r="H1930" s="20" t="n"/>
+      <c r="I1930" s="20" t="n"/>
+      <c r="J1930" s="21" t="n"/>
+      <c r="L1930" s="19" t="inlineStr">
+        <is>
+          <t>TARJETA 3 · Definición de Terminado</t>
+        </is>
+      </c>
+      <c r="M1930" s="20" t="n"/>
+      <c r="N1930" s="20" t="n"/>
+      <c r="O1930" s="21" t="n"/>
+    </row>
+    <row r="1931" ht="28" customHeight="1">
+      <c r="B1931" s="22" t="inlineStr">
+        <is>
+          <t>Habilita a las HU de usuario: no entrega una función al usuario final</t>
+        </is>
+      </c>
+      <c r="C1931" s="8" t="n"/>
+      <c r="D1931" s="8" t="n"/>
+      <c r="E1931" s="23" t="n"/>
+      <c r="G1931" s="22" t="inlineStr">
+        <is>
+          <t>El enfoque está en la consideración del equipo de desarrollo sobre si la historia está lista para un Sprint</t>
+        </is>
+      </c>
+      <c r="H1931" s="8" t="n"/>
+      <c r="I1931" s="8" t="n"/>
+      <c r="J1931" s="23" t="n"/>
+      <c r="L1931" s="22" t="inlineStr">
+        <is>
+          <t>El enfoque está en la aceptación del cliente cuando se le entregue el producto</t>
+        </is>
+      </c>
+      <c r="M1931" s="8" t="n"/>
+      <c r="N1931" s="8" t="n"/>
+      <c r="O1931" s="23" t="n"/>
+    </row>
+    <row r="1932">
+      <c r="B1932" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="C1932" s="8" t="n"/>
+      <c r="D1932" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="E1932" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="G1932" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="H1932" s="8" t="n"/>
+      <c r="I1932" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="J1932" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="L1932" s="24" t="inlineStr">
+        <is>
+          <t>Historia de usuario</t>
+        </is>
+      </c>
+      <c r="M1932" s="8" t="n"/>
+      <c r="N1932" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="O1932" s="26" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+    </row>
+    <row r="1933" ht="30" customHeight="1">
+      <c r="B1933" s="27" t="inlineStr">
+        <is>
+          <t>HT-08 · Autenticar a los servicios entre sí</t>
+        </is>
+      </c>
+      <c r="C1933" s="8" t="n"/>
+      <c r="D1933" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E1933" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+      <c r="G1933" s="27" t="inlineStr">
+        <is>
+          <t>HT-08 · Autenticar a los servicios entre sí</t>
+        </is>
+      </c>
+      <c r="H1933" s="8" t="n"/>
+      <c r="I1933" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J1933" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+      <c r="L1933" s="27" t="inlineStr">
+        <is>
+          <t>HT-08 · Autenticar a los servicios entre sí</t>
+        </is>
+      </c>
+      <c r="M1933" s="8" t="n"/>
+      <c r="N1933" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="O1933" s="28" t="inlineStr">
+        <is>
+          <t>Por votar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="B1934" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="C1934" s="8" t="n"/>
+      <c r="D1934" s="8" t="n"/>
+      <c r="E1934" s="23" t="n"/>
+      <c r="G1934" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="H1934" s="8" t="n"/>
+      <c r="I1934" s="8" t="n"/>
+      <c r="J1934" s="23" t="n"/>
+      <c r="L1934" s="29" t="inlineStr">
+        <is>
+          <t>Descripción:</t>
+        </is>
+      </c>
+      <c r="M1934" s="8" t="n"/>
+      <c r="N1934" s="8" t="n"/>
+      <c r="O1934" s="23" t="n"/>
+    </row>
+    <row r="1935" ht="28" customHeight="1">
+      <c r="B1935" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero que Integraciones y Notificaciones solo atiendan a la API con un token de servicio, para que nadie gaste las consultas de Factiliza ni envíe avisos falsos.</t>
+        </is>
+      </c>
+      <c r="C1935" s="8" t="n"/>
+      <c r="D1935" s="8" t="n"/>
+      <c r="E1935" s="23" t="n"/>
+      <c r="G1935" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero que Integraciones y Notificaciones solo atiendan a la API con un token de servicio, para que nadie gaste las consultas de Factiliza ni envíe avisos falsos.</t>
+        </is>
+      </c>
+      <c r="H1935" s="8" t="n"/>
+      <c r="I1935" s="8" t="n"/>
+      <c r="J1935" s="23" t="n"/>
+      <c r="L1935" s="30" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero que Integraciones y Notificaciones solo atiendan a la API con un token de servicio, para que nadie gaste las consultas de Factiliza ni envíe avisos falsos.</t>
+        </is>
+      </c>
+      <c r="M1935" s="8" t="n"/>
+      <c r="N1935" s="8" t="n"/>
+      <c r="O1935" s="23" t="n"/>
+    </row>
+    <row r="1936" ht="28" customHeight="1">
+      <c r="B1936" s="31" t="n"/>
+      <c r="C1936" s="8" t="n"/>
+      <c r="D1936" s="8" t="n"/>
+      <c r="E1936" s="23" t="n"/>
+      <c r="G1936" s="31" t="n"/>
+      <c r="H1936" s="8" t="n"/>
+      <c r="I1936" s="8" t="n"/>
+      <c r="J1936" s="23" t="n"/>
+      <c r="L1936" s="31" t="n"/>
+      <c r="M1936" s="8" t="n"/>
+      <c r="N1936" s="8" t="n"/>
+      <c r="O1936" s="23" t="n"/>
+    </row>
+    <row r="1937">
+      <c r="B1937" s="29" t="inlineStr">
+        <is>
+          <t>Ficha de la historia</t>
+        </is>
+      </c>
+      <c r="C1937" s="8" t="n"/>
+      <c r="D1937" s="8" t="n"/>
+      <c r="E1937" s="23" t="n"/>
+      <c r="G1937" s="29" t="inlineStr">
+        <is>
+          <t>Criterios de listo:</t>
+        </is>
+      </c>
+      <c r="H1937" s="8" t="n"/>
+      <c r="I1937" s="8" t="n"/>
+      <c r="J1937" s="23" t="n"/>
+      <c r="L1937" s="29" t="inlineStr">
+        <is>
+          <t>Condiciones finales (se marcan cuando el PO acepta la historia en la Review):</t>
+        </is>
+      </c>
+      <c r="M1937" s="8" t="n"/>
+      <c r="N1937" s="8" t="n"/>
+      <c r="O1937" s="23" t="n"/>
+    </row>
+    <row r="1938" ht="30" customHeight="1">
+      <c r="B1938" s="32" t="inlineStr">
+        <is>
+          <t>Tipo: Historia técnica (habilitadora)</t>
+        </is>
+      </c>
+      <c r="C1938" s="8" t="n"/>
+      <c r="D1938" s="8" t="n"/>
+      <c r="E1938" s="23" t="n"/>
+      <c r="G1938" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1938" s="34" t="inlineStr">
+        <is>
+          <t>L1 · Redactada en el formato acordado — Cumple</t>
+        </is>
+      </c>
+      <c r="I1938" s="8" t="n"/>
+      <c r="J1938" s="23" t="n"/>
+      <c r="L1938" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1938" s="34" t="inlineStr">
+        <is>
+          <t>Una llamada a Integraciones sin el token de servicio se ha rechazado con 401</t>
+        </is>
+      </c>
+      <c r="N1938" s="8" t="n"/>
+      <c r="O1938" s="23" t="n"/>
+    </row>
+    <row r="1939" ht="30" customHeight="1">
+      <c r="B1939" s="32" t="inlineStr">
+        <is>
+          <t>Qué destraba: La seguridad de las integraciones (incidencia del 22/10)</t>
+        </is>
+      </c>
+      <c r="C1939" s="8" t="n"/>
+      <c r="D1939" s="8" t="n"/>
+      <c r="E1939" s="23" t="n"/>
+      <c r="G1939" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1939" s="34" t="inlineStr">
+        <is>
+          <t>L2 · Nombre corto en forma de acción — Cumple</t>
+        </is>
+      </c>
+      <c r="I1939" s="8" t="n"/>
+      <c r="J1939" s="23" t="n"/>
+      <c r="L1939" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1939" s="34" t="inlineStr">
+        <is>
+          <t>La API ha llamado a Integraciones y a Notificaciones con su token desde docker compose</t>
+        </is>
+      </c>
+      <c r="N1939" s="8" t="n"/>
+      <c r="O1939" s="23" t="n"/>
+    </row>
+    <row r="1940" ht="30" customHeight="1">
+      <c r="B1940" s="32" t="inlineStr">
+        <is>
+          <t>Responsable técnico: Fernando</t>
+        </is>
+      </c>
+      <c r="C1940" s="8" t="n"/>
+      <c r="D1940" s="8" t="n"/>
+      <c r="E1940" s="23" t="n"/>
+      <c r="G1940" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1940" s="34" t="inlineStr">
+        <is>
+          <t>L3 · Criterios de aceptación escritos — Cumple</t>
+        </is>
+      </c>
+      <c r="I1940" s="8" t="n"/>
+      <c r="J1940" s="23" t="n"/>
+      <c r="L1940" s="35" t="inlineStr">
+        <is>
+          <t>(    )</t>
+        </is>
+      </c>
+      <c r="M1940" s="34" t="inlineStr">
+        <is>
+          <t>El token se ha guardado como variable de entorno, nunca en el código</t>
+        </is>
+      </c>
+      <c r="N1940" s="8" t="n"/>
+      <c r="O1940" s="23" t="n"/>
+    </row>
+    <row r="1941" ht="36" customHeight="1">
+      <c r="B1941" s="36" t="inlineStr">
+        <is>
+          <t>Depende de: HT-01</t>
+        </is>
+      </c>
+      <c r="C1941" s="37" t="n"/>
+      <c r="D1941" s="37" t="n"/>
+      <c r="E1941" s="38" t="n"/>
+      <c r="G1941" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1941" s="34" t="inlineStr">
+        <is>
+          <t>L4 · Dependencias resueltas — Cumple</t>
+        </is>
+      </c>
+      <c r="I1941" s="8" t="n"/>
+      <c r="J1941" s="23" t="n"/>
+      <c r="L1941" s="36" t="inlineStr">
+        <is>
+          <t>Mitad técnica: Además, los criterios T1 a T10 de la hoja «3. Criterios DoR y DoD» que le apliquen</t>
+        </is>
+      </c>
+      <c r="M1941" s="37" t="n"/>
+      <c r="N1941" s="37" t="n"/>
+      <c r="O1941" s="38" t="n"/>
+    </row>
+    <row r="1942" ht="30" customHeight="1">
+      <c r="G1942" s="40" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1942" s="34" t="inlineStr">
+        <is>
+          <t>L5 · Estimada por los Developers — No cumple: se vota en el próximo Daily</t>
+        </is>
+      </c>
+      <c r="I1942" s="8" t="n"/>
+      <c r="J1942" s="23" t="n"/>
+    </row>
+    <row r="1943" ht="30" customHeight="1">
+      <c r="G1943" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1943" s="34" t="inlineStr">
+        <is>
+          <t>L6 · Cabe en un sprint (8 puntos o menos) — Cumple</t>
+        </is>
+      </c>
+      <c r="I1943" s="8" t="n"/>
+      <c r="J1943" s="23" t="n"/>
+    </row>
+    <row r="1944" ht="30" customHeight="1">
+      <c r="G1944" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1944" s="34" t="inlineStr">
+        <is>
+          <t>L7 · Reglas de dominio identificadas — Cumple</t>
+        </is>
+      </c>
+      <c r="I1944" s="8" t="n"/>
+      <c r="J1944" s="23" t="n"/>
+    </row>
+    <row r="1945" ht="30" customHeight="1">
+      <c r="G1945" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1945" s="34" t="inlineStr">
+        <is>
+          <t>L8 · Datos de prueba disponibles — Cumple</t>
+        </is>
+      </c>
+      <c r="I1945" s="8" t="n"/>
+      <c r="J1945" s="23" t="n"/>
+    </row>
+    <row r="1946" ht="30" customHeight="1">
+      <c r="G1946" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1946" s="34" t="inlineStr">
+        <is>
+          <t>L9 · Responsable técnico asignado — Cumple</t>
+        </is>
+      </c>
+      <c r="I1946" s="8" t="n"/>
+      <c r="J1946" s="23" t="n"/>
+    </row>
+    <row r="1947" ht="30" customHeight="1">
+      <c r="G1947" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1947" s="34" t="inlineStr">
+        <is>
+          <t>L10 · Recursos identificados — Cumple: Fernando + equipo</t>
+        </is>
+      </c>
+      <c r="I1947" s="8" t="n"/>
+      <c r="J1947" s="23" t="n"/>
+    </row>
+    <row r="1948" ht="30" customHeight="1">
+      <c r="G1948" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1948" s="34" t="inlineStr">
+        <is>
+          <t>L11 · Requisitos técnicos de programación definidos — Cumple: FastAPI, Docker y la consola del hosting</t>
+        </is>
+      </c>
+      <c r="I1948" s="8" t="n"/>
+      <c r="J1948" s="23" t="n"/>
+    </row>
+    <row r="1949" ht="30" customHeight="1">
+      <c r="G1949" s="33" t="inlineStr">
+        <is>
+          <t>( x )</t>
+        </is>
+      </c>
+      <c r="H1949" s="34" t="inlineStr">
+        <is>
+          <t>L12 · Accesos de red disponibles — Cumple: Microservicios Integraciones y Notificaciones · Factiliza</t>
+        </is>
+      </c>
+      <c r="I1949" s="8" t="n"/>
+      <c r="J1949" s="23" t="n"/>
+    </row>
+    <row r="1950" ht="36" customHeight="1">
+      <c r="G1950" s="39" t="inlineStr">
+        <is>
+          <t>Riesgos: Token expuesto en el frontend · solo la API lo conoce</t>
+        </is>
+      </c>
+      <c r="H1950" s="8" t="n"/>
+      <c r="I1950" s="8" t="n"/>
+      <c r="J1950" s="23" t="n"/>
+    </row>
+    <row r="1951" ht="36" customHeight="1">
+      <c r="G1951" s="32" t="inlineStr">
+        <is>
+          <t>Proveedores de servicio: Microservicios Integraciones y Notificaciones · Factiliza</t>
+        </is>
+      </c>
+      <c r="H1951" s="8" t="n"/>
+      <c r="I1951" s="8" t="n"/>
+      <c r="J1951" s="23" t="n"/>
+    </row>
+    <row r="1952" ht="36" customHeight="1">
+      <c r="G1952" s="36" t="inlineStr">
+        <is>
+          <t>Costos: S/ 0 en servicios (planes gratuitos) · horas según la votación</t>
+        </is>
+      </c>
+      <c r="H1952" s="37" t="n"/>
+      <c r="I1952" s="37" t="n"/>
+      <c r="J1952" s="38" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="2969">
+  <mergeCells count="3324">
     <mergeCell ref="L1725:M1725"/>
+    <mergeCell ref="B1886:E1886"/>
+    <mergeCell ref="B1861:E1861"/>
     <mergeCell ref="G1232:J1232"/>
+    <mergeCell ref="H1784:J1784"/>
     <mergeCell ref="B68:E68"/>
+    <mergeCell ref="G1778:J1778"/>
     <mergeCell ref="L1124:O1124"/>
     <mergeCell ref="L947:O948"/>
     <mergeCell ref="H1479:J1479"/>
     <mergeCell ref="L1308:M1308"/>
+    <mergeCell ref="L1883:O1884"/>
+    <mergeCell ref="B1915:E1915"/>
     <mergeCell ref="H747:J747"/>
     <mergeCell ref="B789:C789"/>
     <mergeCell ref="B374:E374"/>
@@ -41298,8 +45689,10 @@
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="H1474:J1474"/>
     <mergeCell ref="H75:J75"/>
+    <mergeCell ref="L1878:O1878"/>
     <mergeCell ref="L997:M997"/>
     <mergeCell ref="L91:O91"/>
+    <mergeCell ref="H1808:J1808"/>
     <mergeCell ref="H749:J749"/>
     <mergeCell ref="G892:H892"/>
     <mergeCell ref="H409:J409"/>
@@ -41310,6 +45703,7 @@
     <mergeCell ref="H1136:J1136"/>
     <mergeCell ref="B215:E215"/>
     <mergeCell ref="M1393:O1393"/>
+    <mergeCell ref="H1810:J1810"/>
     <mergeCell ref="B243:C243"/>
     <mergeCell ref="G139:H139"/>
     <mergeCell ref="H1347:J1347"/>
@@ -41320,11 +45714,13 @@
     <mergeCell ref="M509:O509"/>
     <mergeCell ref="B1308:C1308"/>
     <mergeCell ref="H1505:J1505"/>
+    <mergeCell ref="B1783:E1783"/>
     <mergeCell ref="B244:E244"/>
     <mergeCell ref="B819:E819"/>
     <mergeCell ref="B1574:E1574"/>
     <mergeCell ref="G184:J184"/>
     <mergeCell ref="L1177:O1177"/>
+    <mergeCell ref="B1785:E1785"/>
     <mergeCell ref="G1404:J1404"/>
     <mergeCell ref="L117:O117"/>
     <mergeCell ref="B557:E558"/>
@@ -41346,6 +45742,7 @@
     <mergeCell ref="B1155:E1156"/>
     <mergeCell ref="H1652:J1652"/>
     <mergeCell ref="G1405:J1405"/>
+    <mergeCell ref="H1792:J1792"/>
     <mergeCell ref="G1703:J1703"/>
     <mergeCell ref="H1189:J1189"/>
     <mergeCell ref="M1290:O1290"/>
@@ -41356,6 +45753,7 @@
     <mergeCell ref="M562:O562"/>
     <mergeCell ref="H1218:J1218"/>
     <mergeCell ref="H463:J463"/>
+    <mergeCell ref="B1776:C1776"/>
     <mergeCell ref="H1525:J1525"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="L890:O890"/>
@@ -41366,8 +45764,12 @@
     <mergeCell ref="G660:J660"/>
     <mergeCell ref="B140:E140"/>
     <mergeCell ref="G241:J241"/>
+    <mergeCell ref="G1857:J1858"/>
     <mergeCell ref="L137:O137"/>
     <mergeCell ref="H1735:J1735"/>
+    <mergeCell ref="B1777:C1777"/>
+    <mergeCell ref="B1804:E1804"/>
+    <mergeCell ref="L1864:O1864"/>
     <mergeCell ref="G1306:J1306"/>
     <mergeCell ref="H490:J490"/>
     <mergeCell ref="G1327:J1327"/>
@@ -41375,9 +45777,12 @@
     <mergeCell ref="G572:J572"/>
     <mergeCell ref="B1499:E1499"/>
     <mergeCell ref="L166:O166"/>
+    <mergeCell ref="L1830:O1830"/>
     <mergeCell ref="H902:J902"/>
+    <mergeCell ref="B1802:C1802"/>
     <mergeCell ref="H1576:J1576"/>
     <mergeCell ref="G574:J574"/>
+    <mergeCell ref="L1859:O1859"/>
     <mergeCell ref="B918:C918"/>
     <mergeCell ref="H904:J904"/>
     <mergeCell ref="M275:O275"/>
@@ -41394,6 +45799,7 @@
     <mergeCell ref="B614:E614"/>
     <mergeCell ref="L1541:O1541"/>
     <mergeCell ref="B527:E527"/>
+    <mergeCell ref="G1774:J1774"/>
     <mergeCell ref="G715:J715"/>
     <mergeCell ref="B1254:E1254"/>
     <mergeCell ref="H203:J203"/>
@@ -41401,6 +45807,8 @@
     <mergeCell ref="L1285:O1286"/>
     <mergeCell ref="G1171:J1171"/>
     <mergeCell ref="G1469:J1469"/>
+    <mergeCell ref="B1859:E1859"/>
+    <mergeCell ref="H1892:J1892"/>
     <mergeCell ref="M301:O301"/>
     <mergeCell ref="B1131:E1131"/>
     <mergeCell ref="L946:O946"/>
@@ -41412,17 +45820,21 @@
     <mergeCell ref="G287:J287"/>
     <mergeCell ref="L1280:O1280"/>
     <mergeCell ref="H71:J71"/>
+    <mergeCell ref="G1775:J1775"/>
     <mergeCell ref="M303:O303"/>
     <mergeCell ref="G1014:J1014"/>
+    <mergeCell ref="G1769:J1769"/>
     <mergeCell ref="B762:C762"/>
     <mergeCell ref="H405:J405"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="H536:J536"/>
     <mergeCell ref="L214:O214"/>
+    <mergeCell ref="H1887:J1887"/>
     <mergeCell ref="H1132:J1132"/>
     <mergeCell ref="H231:J231"/>
     <mergeCell ref="L60:M60"/>
     <mergeCell ref="H407:J407"/>
+    <mergeCell ref="G1800:J1800"/>
     <mergeCell ref="G13:J13"/>
     <mergeCell ref="M304:O304"/>
     <mergeCell ref="H1134:J1134"/>
@@ -41430,14 +45842,18 @@
     <mergeCell ref="G314:J314"/>
     <mergeCell ref="B1570:E1570"/>
     <mergeCell ref="H1292:J1292"/>
+    <mergeCell ref="L1905:O1905"/>
     <mergeCell ref="L875:O875"/>
+    <mergeCell ref="L1934:O1934"/>
     <mergeCell ref="G164:H164"/>
     <mergeCell ref="G217:H217"/>
     <mergeCell ref="G313:J313"/>
     <mergeCell ref="B659:C659"/>
     <mergeCell ref="B510:E510"/>
     <mergeCell ref="B1265:E1265"/>
+    <mergeCell ref="G1795:J1795"/>
     <mergeCell ref="G1040:J1040"/>
+    <mergeCell ref="L1930:O1930"/>
     <mergeCell ref="B838:E838"/>
     <mergeCell ref="B1730:E1730"/>
     <mergeCell ref="G1076:J1076"/>
@@ -41450,13 +45866,17 @@
     <mergeCell ref="L1727:O1728"/>
     <mergeCell ref="B85:E85"/>
     <mergeCell ref="M690:O690"/>
+    <mergeCell ref="H1921:J1921"/>
     <mergeCell ref="H1185:J1185"/>
     <mergeCell ref="H1160:J1160"/>
     <mergeCell ref="B1567:E1567"/>
     <mergeCell ref="B1569:C1569"/>
     <mergeCell ref="H128:J128"/>
+    <mergeCell ref="L1931:O1931"/>
     <mergeCell ref="H435:J435"/>
+    <mergeCell ref="B1784:E1784"/>
     <mergeCell ref="G190:H190"/>
+    <mergeCell ref="H1948:J1948"/>
     <mergeCell ref="M352:O352"/>
     <mergeCell ref="B685:C685"/>
     <mergeCell ref="H1162:J1162"/>
@@ -41470,6 +45890,7 @@
     <mergeCell ref="G455:J455"/>
     <mergeCell ref="B530:E530"/>
     <mergeCell ref="B872:E872"/>
+    <mergeCell ref="G1846:J1846"/>
     <mergeCell ref="B111:E111"/>
     <mergeCell ref="H275:J275"/>
     <mergeCell ref="G815:H815"/>
@@ -41516,6 +45937,7 @@
     <mergeCell ref="H1529:J1529"/>
     <mergeCell ref="B1671:E1671"/>
     <mergeCell ref="B1672:C1672"/>
+    <mergeCell ref="M1759:O1759"/>
     <mergeCell ref="H1687:J1687"/>
     <mergeCell ref="L146:O146"/>
     <mergeCell ref="G1440:J1440"/>
@@ -41557,6 +45979,7 @@
     <mergeCell ref="H641:J641"/>
     <mergeCell ref="B1701:E1702"/>
     <mergeCell ref="L657:O657"/>
+    <mergeCell ref="G1882:J1882"/>
     <mergeCell ref="G1670:J1670"/>
     <mergeCell ref="H518:J518"/>
     <mergeCell ref="G611:J611"/>
@@ -41567,9 +45990,11 @@
     <mergeCell ref="B815:C815"/>
     <mergeCell ref="G1067:J1067"/>
     <mergeCell ref="H1245:J1245"/>
+    <mergeCell ref="H1919:J1919"/>
     <mergeCell ref="L1255:O1255"/>
     <mergeCell ref="H1158:J1158"/>
     <mergeCell ref="H126:J126"/>
+    <mergeCell ref="M1836:O1836"/>
     <mergeCell ref="G269:H269"/>
     <mergeCell ref="G756:J756"/>
     <mergeCell ref="B353:E353"/>
@@ -41581,6 +46006,7 @@
     <mergeCell ref="H1187:J1187"/>
     <mergeCell ref="B1596:E1596"/>
     <mergeCell ref="L683:O683"/>
+    <mergeCell ref="H1914:J1914"/>
     <mergeCell ref="B196:E196"/>
     <mergeCell ref="G322:J322"/>
     <mergeCell ref="G1519:J1520"/>
@@ -41590,6 +46016,7 @@
     <mergeCell ref="H571:J571"/>
     <mergeCell ref="G1079:J1079"/>
     <mergeCell ref="L1317:O1317"/>
+    <mergeCell ref="M1862:O1862"/>
     <mergeCell ref="G1514:J1514"/>
     <mergeCell ref="B661:E662"/>
     <mergeCell ref="H144:J144"/>
@@ -41618,6 +46045,7 @@
     <mergeCell ref="L267:O267"/>
     <mergeCell ref="G1207:J1208"/>
     <mergeCell ref="G1534:J1534"/>
+    <mergeCell ref="B1880:C1880"/>
     <mergeCell ref="B120:E120"/>
     <mergeCell ref="H328:J328"/>
     <mergeCell ref="G500:J500"/>
@@ -41630,6 +46058,7 @@
     <mergeCell ref="B1005:E1005"/>
     <mergeCell ref="G764:J764"/>
     <mergeCell ref="H1685:J1685"/>
+    <mergeCell ref="G1828:H1828"/>
     <mergeCell ref="H1345:J1345"/>
     <mergeCell ref="B1339:E1339"/>
     <mergeCell ref="G1098:J1098"/>
@@ -41643,7 +46072,9 @@
     <mergeCell ref="H953:J953"/>
     <mergeCell ref="H928:J928"/>
     <mergeCell ref="G192:J192"/>
+    <mergeCell ref="B1906:C1906"/>
     <mergeCell ref="M1445:O1445"/>
+    <mergeCell ref="G1829:H1829"/>
     <mergeCell ref="H1680:J1680"/>
     <mergeCell ref="B295:C295"/>
     <mergeCell ref="H1340:J1340"/>
@@ -41656,6 +46087,7 @@
     <mergeCell ref="G553:J553"/>
     <mergeCell ref="B1232:E1232"/>
     <mergeCell ref="M1470:O1470"/>
+    <mergeCell ref="B1778:E1778"/>
     <mergeCell ref="B719:E719"/>
     <mergeCell ref="L477:M477"/>
     <mergeCell ref="G1124:J1124"/>
@@ -41669,6 +46101,7 @@
     <mergeCell ref="G1151:J1151"/>
     <mergeCell ref="M560:O560"/>
     <mergeCell ref="G548:J548"/>
+    <mergeCell ref="G1878:J1878"/>
     <mergeCell ref="L453:O454"/>
     <mergeCell ref="B508:E508"/>
     <mergeCell ref="L1389:O1390"/>
@@ -41687,6 +46120,7 @@
     <mergeCell ref="G1177:J1177"/>
     <mergeCell ref="H25:J25"/>
     <mergeCell ref="H511:J511"/>
+    <mergeCell ref="G1904:J1904"/>
     <mergeCell ref="B192:E192"/>
     <mergeCell ref="H669:J669"/>
     <mergeCell ref="B1105:E1105"/>
@@ -41705,13 +46139,16 @@
     <mergeCell ref="L36:O36"/>
     <mergeCell ref="M459:O459"/>
     <mergeCell ref="G111:J111"/>
+    <mergeCell ref="B1854:C1854"/>
     <mergeCell ref="L641:O641"/>
     <mergeCell ref="M1186:O1186"/>
     <mergeCell ref="G1180:J1180"/>
     <mergeCell ref="B61:C61"/>
     <mergeCell ref="G1595:H1595"/>
+    <mergeCell ref="B1834:E1834"/>
     <mergeCell ref="L216:M216"/>
     <mergeCell ref="L1395:O1395"/>
+    <mergeCell ref="L1911:O1911"/>
     <mergeCell ref="H956:J956"/>
     <mergeCell ref="H1298:J1298"/>
     <mergeCell ref="B1705:E1705"/>
@@ -41726,6 +46163,7 @@
     <mergeCell ref="L945:M945"/>
     <mergeCell ref="B975:E975"/>
     <mergeCell ref="B660:E660"/>
+    <mergeCell ref="B1857:E1858"/>
     <mergeCell ref="G137:J137"/>
     <mergeCell ref="L692:O692"/>
     <mergeCell ref="G1619:J1619"/>
@@ -41734,6 +46172,7 @@
     <mergeCell ref="B249:E249"/>
     <mergeCell ref="L1568:M1568"/>
     <mergeCell ref="H413:J413"/>
+    <mergeCell ref="G1830:J1830"/>
     <mergeCell ref="H982:J982"/>
     <mergeCell ref="G1363:J1364"/>
     <mergeCell ref="B1725:C1725"/>
@@ -41742,6 +46181,7 @@
     <mergeCell ref="B1003:E1003"/>
     <mergeCell ref="H1011:J1011"/>
     <mergeCell ref="H1036:J1036"/>
+    <mergeCell ref="L1755:O1755"/>
     <mergeCell ref="H250:J250"/>
     <mergeCell ref="L1021:O1021"/>
     <mergeCell ref="L266:O266"/>
@@ -41754,9 +46194,12 @@
     <mergeCell ref="H619:J619"/>
     <mergeCell ref="L658:M658"/>
     <mergeCell ref="G1100:H1100"/>
+    <mergeCell ref="H1765:J1765"/>
+    <mergeCell ref="G1855:H1855"/>
     <mergeCell ref="G1249:J1249"/>
     <mergeCell ref="L89:O90"/>
     <mergeCell ref="H308:J308"/>
+    <mergeCell ref="B1774:E1774"/>
     <mergeCell ref="G1698:H1698"/>
     <mergeCell ref="G911:J911"/>
     <mergeCell ref="L1466:O1466"/>
@@ -41769,6 +46212,7 @@
     <mergeCell ref="H1064:J1064"/>
     <mergeCell ref="H309:J309"/>
     <mergeCell ref="B716:E716"/>
+    <mergeCell ref="B1775:E1775"/>
     <mergeCell ref="G62:J62"/>
     <mergeCell ref="H643:J643"/>
     <mergeCell ref="B1050:E1050"/>
@@ -41782,6 +46226,7 @@
     <mergeCell ref="M1498:O1498"/>
     <mergeCell ref="L433:O433"/>
     <mergeCell ref="H638:J638"/>
+    <mergeCell ref="G1934:J1934"/>
     <mergeCell ref="B1047:E1047"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="L581:M581"/>
@@ -41790,6 +46235,7 @@
     <mergeCell ref="M223:O223"/>
     <mergeCell ref="L760:O760"/>
     <mergeCell ref="B1076:E1076"/>
+    <mergeCell ref="L1853:O1853"/>
     <mergeCell ref="G245:J246"/>
     <mergeCell ref="B744:E744"/>
     <mergeCell ref="H777:J777"/>
@@ -41801,17 +46247,22 @@
     <mergeCell ref="H1504:J1504"/>
     <mergeCell ref="L305:O305"/>
     <mergeCell ref="B615:E615"/>
+    <mergeCell ref="H1838:J1838"/>
     <mergeCell ref="H779:J779"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="G1176:J1176"/>
     <mergeCell ref="G843:J844"/>
     <mergeCell ref="H18:J18"/>
+    <mergeCell ref="G1931:J1931"/>
     <mergeCell ref="G990:J990"/>
     <mergeCell ref="H1288:J1288"/>
+    <mergeCell ref="M1939:O1939"/>
     <mergeCell ref="G1568:H1568"/>
     <mergeCell ref="M1211:O1211"/>
+    <mergeCell ref="H1840:J1840"/>
     <mergeCell ref="H622:J622"/>
     <mergeCell ref="B760:E760"/>
+    <mergeCell ref="M1938:O1938"/>
     <mergeCell ref="H1296:J1296"/>
     <mergeCell ref="G1439:H1439"/>
     <mergeCell ref="M1213:O1213"/>
@@ -41820,6 +46271,7 @@
     <mergeCell ref="H353:J353"/>
     <mergeCell ref="G894:J894"/>
     <mergeCell ref="L58:O58"/>
+    <mergeCell ref="M1940:O1940"/>
     <mergeCell ref="B457:E457"/>
     <mergeCell ref="L970:M970"/>
     <mergeCell ref="G1465:H1465"/>
@@ -41828,9 +46280,12 @@
     <mergeCell ref="G1644:J1644"/>
     <mergeCell ref="L1540:O1540"/>
     <mergeCell ref="G8:H8"/>
+    <mergeCell ref="L1838:O1838"/>
+    <mergeCell ref="G1951:J1951"/>
     <mergeCell ref="G687:J688"/>
     <mergeCell ref="G1490:H1490"/>
     <mergeCell ref="H1007:J1007"/>
+    <mergeCell ref="H1893:J1893"/>
     <mergeCell ref="H1138:J1138"/>
     <mergeCell ref="H798:J798"/>
     <mergeCell ref="G891:J891"/>
@@ -41859,6 +46314,7 @@
     <mergeCell ref="L1437:O1437"/>
     <mergeCell ref="G609:J610"/>
     <mergeCell ref="L1621:M1621"/>
+    <mergeCell ref="B1905:E1905"/>
     <mergeCell ref="G1365:J1365"/>
     <mergeCell ref="H851:J851"/>
     <mergeCell ref="M952:O952"/>
@@ -41868,6 +46324,7 @@
     <mergeCell ref="G1205:H1205"/>
     <mergeCell ref="G450:H450"/>
     <mergeCell ref="H722:J722"/>
+    <mergeCell ref="H1912:J1912"/>
     <mergeCell ref="H853:J853"/>
     <mergeCell ref="M979:O979"/>
     <mergeCell ref="H119:J119"/>
@@ -41879,6 +46336,7 @@
     <mergeCell ref="H1660:J1660"/>
     <mergeCell ref="H1451:J1451"/>
     <mergeCell ref="L247:O247"/>
+    <mergeCell ref="B1887:E1887"/>
     <mergeCell ref="B1284:E1284"/>
     <mergeCell ref="G630:J630"/>
     <mergeCell ref="L1027:O1027"/>
@@ -41890,14 +46348,17 @@
     <mergeCell ref="B1597:E1598"/>
     <mergeCell ref="G657:J657"/>
     <mergeCell ref="G1716:J1716"/>
+    <mergeCell ref="B1882:E1882"/>
     <mergeCell ref="B1670:E1670"/>
     <mergeCell ref="M1732:O1732"/>
+    <mergeCell ref="B1801:E1801"/>
     <mergeCell ref="H775:J775"/>
     <mergeCell ref="H750:J750"/>
     <mergeCell ref="G1051:J1052"/>
     <mergeCell ref="G1718:J1718"/>
     <mergeCell ref="M667:O667"/>
     <mergeCell ref="M1603:O1603"/>
+    <mergeCell ref="H1836:J1836"/>
     <mergeCell ref="H1081:J1081"/>
     <mergeCell ref="G165:H165"/>
     <mergeCell ref="H1373:J1373"/>
@@ -41911,6 +46372,7 @@
     <mergeCell ref="G1742:J1742"/>
     <mergeCell ref="G683:J683"/>
     <mergeCell ref="G859:J859"/>
+    <mergeCell ref="B1811:E1811"/>
     <mergeCell ref="H778:J778"/>
     <mergeCell ref="B583:E584"/>
     <mergeCell ref="G1077:J1078"/>
@@ -41919,6 +46381,7 @@
     <mergeCell ref="B787:E787"/>
     <mergeCell ref="B32:E32"/>
     <mergeCell ref="L294:M294"/>
+    <mergeCell ref="H1862:J1862"/>
     <mergeCell ref="H803:J803"/>
     <mergeCell ref="B1514:E1514"/>
     <mergeCell ref="G247:J247"/>
@@ -41930,6 +46393,7 @@
     <mergeCell ref="M1316:O1316"/>
     <mergeCell ref="H674:J674"/>
     <mergeCell ref="B1385:E1385"/>
+    <mergeCell ref="H1864:J1864"/>
     <mergeCell ref="L174:O174"/>
     <mergeCell ref="H794:J794"/>
     <mergeCell ref="H77:J77"/>
@@ -41952,21 +46416,28 @@
     <mergeCell ref="B927:E927"/>
     <mergeCell ref="B166:E166"/>
     <mergeCell ref="B1207:E1208"/>
+    <mergeCell ref="G1883:J1884"/>
     <mergeCell ref="L163:O163"/>
     <mergeCell ref="G1457:J1457"/>
     <mergeCell ref="G702:J702"/>
+    <mergeCell ref="H1761:J1761"/>
     <mergeCell ref="L191:M191"/>
     <mergeCell ref="B352:E352"/>
     <mergeCell ref="H1575:J1575"/>
     <mergeCell ref="B479:E480"/>
+    <mergeCell ref="H1763:J1763"/>
     <mergeCell ref="G704:J704"/>
+    <mergeCell ref="L1856:O1856"/>
+    <mergeCell ref="G1906:H1906"/>
     <mergeCell ref="L1128:O1128"/>
     <mergeCell ref="H1577:J1577"/>
     <mergeCell ref="H822:J822"/>
     <mergeCell ref="B501:E501"/>
     <mergeCell ref="L323:O324"/>
     <mergeCell ref="H359:J359"/>
+    <mergeCell ref="L1885:O1885"/>
     <mergeCell ref="B944:C944"/>
+    <mergeCell ref="H1788:J1788"/>
     <mergeCell ref="B169:E169"/>
     <mergeCell ref="G270:J270"/>
     <mergeCell ref="B347:C347"/>
@@ -41974,6 +46445,8 @@
     <mergeCell ref="G1467:J1468"/>
     <mergeCell ref="L527:O527"/>
     <mergeCell ref="M950:O950"/>
+    <mergeCell ref="G1909:J1910"/>
+    <mergeCell ref="B1829:C1829"/>
     <mergeCell ref="H388:J388"/>
     <mergeCell ref="B526:E526"/>
     <mergeCell ref="L373:M373"/>
@@ -41998,35 +46471,43 @@
     <mergeCell ref="L1306:O1306"/>
     <mergeCell ref="L1604:O1604"/>
     <mergeCell ref="G453:J454"/>
+    <mergeCell ref="B1914:E1914"/>
     <mergeCell ref="L88:O88"/>
     <mergeCell ref="M329:O329"/>
     <mergeCell ref="H746:J746"/>
     <mergeCell ref="B788:C788"/>
     <mergeCell ref="B1159:E1159"/>
+    <mergeCell ref="L1909:O1910"/>
     <mergeCell ref="L1570:O1570"/>
     <mergeCell ref="H1473:J1473"/>
     <mergeCell ref="H441:J441"/>
+    <mergeCell ref="L1904:O1904"/>
     <mergeCell ref="L845:O845"/>
     <mergeCell ref="G1384:J1384"/>
     <mergeCell ref="L86:M86"/>
     <mergeCell ref="G503:H503"/>
     <mergeCell ref="M665:O665"/>
+    <mergeCell ref="L1750:M1750"/>
     <mergeCell ref="H1475:J1475"/>
     <mergeCell ref="G1230:H1230"/>
     <mergeCell ref="H1502:J1502"/>
     <mergeCell ref="B1154:E1154"/>
+    <mergeCell ref="B1911:E1911"/>
     <mergeCell ref="M1392:O1392"/>
     <mergeCell ref="B241:E241"/>
     <mergeCell ref="M664:O664"/>
     <mergeCell ref="L1332:O1332"/>
+    <mergeCell ref="B1940:E1940"/>
     <mergeCell ref="B1185:E1185"/>
     <mergeCell ref="G1102:J1102"/>
+    <mergeCell ref="B1912:E1912"/>
     <mergeCell ref="G788:H788"/>
     <mergeCell ref="L271:O272"/>
     <mergeCell ref="L871:O871"/>
     <mergeCell ref="B1187:E1187"/>
     <mergeCell ref="G36:J36"/>
     <mergeCell ref="H459:J459"/>
+    <mergeCell ref="L1753:O1754"/>
     <mergeCell ref="H617:J617"/>
     <mergeCell ref="B1599:E1599"/>
     <mergeCell ref="G1700:J1700"/>
@@ -42037,21 +46518,27 @@
     <mergeCell ref="M1418:O1418"/>
     <mergeCell ref="H1344:J1344"/>
     <mergeCell ref="H285:J285"/>
+    <mergeCell ref="H1860:J1860"/>
     <mergeCell ref="G349:J350"/>
     <mergeCell ref="H461:J461"/>
     <mergeCell ref="G216:H216"/>
+    <mergeCell ref="L1803:M1803"/>
     <mergeCell ref="B1337:E1338"/>
+    <mergeCell ref="H1949:J1949"/>
     <mergeCell ref="H1555:J1555"/>
     <mergeCell ref="H1188:J1188"/>
     <mergeCell ref="H460:J460"/>
     <mergeCell ref="G1099:J1099"/>
+    <mergeCell ref="H1942:J1942"/>
     <mergeCell ref="H883:J883"/>
     <mergeCell ref="G814:H814"/>
     <mergeCell ref="L297:O298"/>
     <mergeCell ref="G945:H945"/>
     <mergeCell ref="G970:H970"/>
     <mergeCell ref="H1217:J1217"/>
+    <mergeCell ref="B1935:E1936"/>
     <mergeCell ref="B898:E898"/>
+    <mergeCell ref="L1779:O1780"/>
     <mergeCell ref="B137:E137"/>
     <mergeCell ref="H673:J673"/>
     <mergeCell ref="B1625:E1625"/>
@@ -42065,10 +46552,12 @@
     <mergeCell ref="G998:J998"/>
     <mergeCell ref="G1150:J1150"/>
     <mergeCell ref="G817:J818"/>
+    <mergeCell ref="H1871:J1871"/>
     <mergeCell ref="L1074:M1074"/>
     <mergeCell ref="L1516:M1516"/>
     <mergeCell ref="H1662:J1662"/>
     <mergeCell ref="M1342:O1342"/>
+    <mergeCell ref="G1755:J1755"/>
     <mergeCell ref="L917:O917"/>
     <mergeCell ref="H304:J304"/>
     <mergeCell ref="G867:H867"/>
@@ -42083,12 +46572,14 @@
     <mergeCell ref="L1696:O1696"/>
     <mergeCell ref="B953:E953"/>
     <mergeCell ref="H1113:J1113"/>
+    <mergeCell ref="H1868:J1868"/>
     <mergeCell ref="B613:E613"/>
     <mergeCell ref="L739:O740"/>
     <mergeCell ref="B1549:E1549"/>
     <mergeCell ref="M1030:O1030"/>
     <mergeCell ref="B1340:E1340"/>
     <mergeCell ref="G1466:J1466"/>
+    <mergeCell ref="B1856:E1856"/>
     <mergeCell ref="B946:E946"/>
     <mergeCell ref="B69:E69"/>
     <mergeCell ref="L943:O943"/>
@@ -42096,6 +46587,7 @@
     <mergeCell ref="B1551:E1551"/>
     <mergeCell ref="B823:E823"/>
     <mergeCell ref="H1715:J1715"/>
+    <mergeCell ref="G1779:J1780"/>
     <mergeCell ref="M300:O300"/>
     <mergeCell ref="H226:J226"/>
     <mergeCell ref="B1126:C1126"/>
@@ -42109,6 +46601,7 @@
     <mergeCell ref="L511:O511"/>
     <mergeCell ref="M1056:O1056"/>
     <mergeCell ref="H1498:J1498"/>
+    <mergeCell ref="B1855:C1855"/>
     <mergeCell ref="H99:J99"/>
     <mergeCell ref="H1289:J1289"/>
     <mergeCell ref="B666:E666"/>
@@ -42138,6 +46631,7 @@
     <mergeCell ref="M171:O171"/>
     <mergeCell ref="B240:E240"/>
     <mergeCell ref="B1176:E1176"/>
+    <mergeCell ref="G1827:J1827"/>
     <mergeCell ref="H125:J125"/>
     <mergeCell ref="H256:J256"/>
     <mergeCell ref="G1093:J1093"/>
@@ -42146,19 +46640,24 @@
     <mergeCell ref="B1722:E1722"/>
     <mergeCell ref="H852:J852"/>
     <mergeCell ref="M173:O173"/>
+    <mergeCell ref="H1945:J1945"/>
     <mergeCell ref="L868:O868"/>
     <mergeCell ref="M769:O769"/>
     <mergeCell ref="B1568:C1568"/>
     <mergeCell ref="H127:J127"/>
     <mergeCell ref="B563:E563"/>
+    <mergeCell ref="H1938:J1938"/>
     <mergeCell ref="H879:J879"/>
     <mergeCell ref="G65:J65"/>
     <mergeCell ref="H854:J854"/>
     <mergeCell ref="B1439:C1439"/>
     <mergeCell ref="B1290:E1290"/>
+    <mergeCell ref="G1822:J1822"/>
     <mergeCell ref="H1213:J1213"/>
     <mergeCell ref="L709:O709"/>
+    <mergeCell ref="H1940:J1940"/>
     <mergeCell ref="G365:J365"/>
+    <mergeCell ref="G1853:J1853"/>
     <mergeCell ref="B1651:E1651"/>
     <mergeCell ref="G1119:J1119"/>
     <mergeCell ref="B1571:E1572"/>
@@ -42174,6 +46673,7 @@
     <mergeCell ref="H1239:J1239"/>
     <mergeCell ref="G1726:J1726"/>
     <mergeCell ref="B891:E891"/>
+    <mergeCell ref="G1848:J1848"/>
     <mergeCell ref="H592:J592"/>
     <mergeCell ref="B737:C737"/>
     <mergeCell ref="H1241:J1241"/>
@@ -42222,12 +46722,14 @@
     <mergeCell ref="B1362:E1362"/>
     <mergeCell ref="M327:O327"/>
     <mergeCell ref="B451:C451"/>
+    <mergeCell ref="M1809:O1809"/>
     <mergeCell ref="M1054:O1054"/>
     <mergeCell ref="B1391:E1391"/>
     <mergeCell ref="B630:E630"/>
     <mergeCell ref="G1281:J1281"/>
     <mergeCell ref="G547:J547"/>
     <mergeCell ref="G1492:J1492"/>
+    <mergeCell ref="G1796:J1796"/>
     <mergeCell ref="H41:J41"/>
     <mergeCell ref="L139:M139"/>
     <mergeCell ref="H1610:J1610"/>
@@ -42255,6 +46757,7 @@
     <mergeCell ref="L1127:M1127"/>
     <mergeCell ref="G478:J478"/>
     <mergeCell ref="B1288:E1288"/>
+    <mergeCell ref="L1854:M1854"/>
     <mergeCell ref="M41:O41"/>
     <mergeCell ref="B1446:E1446"/>
     <mergeCell ref="B345:E345"/>
@@ -42280,6 +46783,7 @@
     <mergeCell ref="H563:J563"/>
     <mergeCell ref="H1455:J1455"/>
     <mergeCell ref="L1724:M1724"/>
+    <mergeCell ref="L1857:O1858"/>
     <mergeCell ref="M795:O795"/>
     <mergeCell ref="H721:J721"/>
     <mergeCell ref="B1621:C1621"/>
@@ -42298,6 +46802,7 @@
     <mergeCell ref="B406:E406"/>
     <mergeCell ref="G507:J507"/>
     <mergeCell ref="G1224:J1224"/>
+    <mergeCell ref="B1757:E1757"/>
     <mergeCell ref="B1002:E1002"/>
     <mergeCell ref="G1389:J1390"/>
     <mergeCell ref="B277:E277"/>
@@ -42310,6 +46815,8 @@
     <mergeCell ref="G832:J832"/>
     <mergeCell ref="B1004:E1004"/>
     <mergeCell ref="H1377:J1377"/>
+    <mergeCell ref="B1759:E1759"/>
+    <mergeCell ref="L1781:O1781"/>
     <mergeCell ref="H1168:J1168"/>
     <mergeCell ref="L292:O292"/>
     <mergeCell ref="B1467:E1468"/>
@@ -42320,6 +46827,7 @@
     <mergeCell ref="H1220:J1220"/>
     <mergeCell ref="M1600:O1600"/>
     <mergeCell ref="G1588:J1588"/>
+    <mergeCell ref="H1766:J1766"/>
     <mergeCell ref="B117:E117"/>
     <mergeCell ref="H1548:J1548"/>
     <mergeCell ref="L115:O116"/>
@@ -42335,6 +46843,7 @@
     <mergeCell ref="G1259:J1260"/>
     <mergeCell ref="M536:O536"/>
     <mergeCell ref="B1470:E1470"/>
+    <mergeCell ref="L1807:O1807"/>
     <mergeCell ref="G972:J972"/>
     <mergeCell ref="L1073:O1073"/>
     <mergeCell ref="L318:O318"/>
@@ -42348,6 +46857,7 @@
     <mergeCell ref="G546:J546"/>
     <mergeCell ref="H665:J665"/>
     <mergeCell ref="B294:C294"/>
+    <mergeCell ref="G1750:H1750"/>
     <mergeCell ref="B1230:C1230"/>
     <mergeCell ref="H1392:J1392"/>
     <mergeCell ref="H360:J360"/>
@@ -42358,6 +46868,7 @@
     <mergeCell ref="B892:C892"/>
     <mergeCell ref="B768:E768"/>
     <mergeCell ref="H666:J666"/>
+    <mergeCell ref="B1830:E1830"/>
     <mergeCell ref="B1102:E1102"/>
     <mergeCell ref="B43:E43"/>
     <mergeCell ref="G579:J579"/>
@@ -42366,6 +46877,7 @@
     <mergeCell ref="G573:J573"/>
     <mergeCell ref="G871:J871"/>
     <mergeCell ref="B797:E797"/>
+    <mergeCell ref="G1753:J1754"/>
     <mergeCell ref="G1300:J1300"/>
     <mergeCell ref="L33:O33"/>
     <mergeCell ref="H691:J691"/>
@@ -42399,6 +46911,7 @@
     <mergeCell ref="G890:J890"/>
     <mergeCell ref="L849:O849"/>
     <mergeCell ref="L1594:M1594"/>
+    <mergeCell ref="B1755:E1755"/>
     <mergeCell ref="H1164:J1164"/>
     <mergeCell ref="L842:O842"/>
     <mergeCell ref="M510:O510"/>
@@ -42410,14 +46923,19 @@
     <mergeCell ref="B658:C658"/>
     <mergeCell ref="L1022:M1022"/>
     <mergeCell ref="L1020:O1020"/>
+    <mergeCell ref="H1762:J1762"/>
+    <mergeCell ref="M1863:O1863"/>
     <mergeCell ref="B88:E88"/>
     <mergeCell ref="H1037:J1037"/>
     <mergeCell ref="L866:M866"/>
     <mergeCell ref="H1159:J1159"/>
     <mergeCell ref="G819:J819"/>
+    <mergeCell ref="H1764:J1764"/>
+    <mergeCell ref="H1791:J1791"/>
     <mergeCell ref="L114:O114"/>
     <mergeCell ref="G739:J740"/>
     <mergeCell ref="L1620:M1620"/>
+    <mergeCell ref="L1751:M1751"/>
     <mergeCell ref="M1262:O1262"/>
     <mergeCell ref="H1190:J1190"/>
     <mergeCell ref="G943:J943"/>
@@ -42431,20 +46949,26 @@
     <mergeCell ref="H458:J458"/>
     <mergeCell ref="B110:E110"/>
     <mergeCell ref="L141:O142"/>
+    <mergeCell ref="H1818:J1818"/>
     <mergeCell ref="H1063:J1063"/>
     <mergeCell ref="G476:H476"/>
     <mergeCell ref="B715:E715"/>
     <mergeCell ref="H1221:J1221"/>
     <mergeCell ref="L1623:O1624"/>
+    <mergeCell ref="H1790:J1790"/>
+    <mergeCell ref="H1817:J1817"/>
     <mergeCell ref="B1620:C1620"/>
     <mergeCell ref="H301:J301"/>
     <mergeCell ref="M1707:O1707"/>
     <mergeCell ref="L737:M737"/>
+    <mergeCell ref="H1844:J1844"/>
     <mergeCell ref="L1673:M1673"/>
+    <mergeCell ref="H1819:J1819"/>
     <mergeCell ref="H1058:J1058"/>
     <mergeCell ref="H303:J303"/>
     <mergeCell ref="B869:E870"/>
     <mergeCell ref="L1464:M1464"/>
+    <mergeCell ref="G1881:H1881"/>
     <mergeCell ref="G656:J656"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B136:E136"/>
@@ -42452,14 +46976,17 @@
     <mergeCell ref="L1335:M1335"/>
     <mergeCell ref="L167:O168"/>
     <mergeCell ref="G53:J53"/>
+    <mergeCell ref="G1899:J1899"/>
     <mergeCell ref="B1496:E1496"/>
     <mergeCell ref="B741:E741"/>
     <mergeCell ref="L1518:O1518"/>
+    <mergeCell ref="B1800:E1800"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="M276:O276"/>
     <mergeCell ref="B1623:E1624"/>
     <mergeCell ref="G1717:J1717"/>
     <mergeCell ref="H1116:J1116"/>
+    <mergeCell ref="B1827:E1827"/>
     <mergeCell ref="H776:J776"/>
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="G114:J114"/>
@@ -42468,7 +46995,9 @@
     <mergeCell ref="H173:J173"/>
     <mergeCell ref="L1084:O1084"/>
     <mergeCell ref="H1503:J1503"/>
+    <mergeCell ref="H1837:J1837"/>
     <mergeCell ref="B1491:C1491"/>
+    <mergeCell ref="G1930:J1930"/>
     <mergeCell ref="G143:J143"/>
     <mergeCell ref="H1714:J1714"/>
     <mergeCell ref="B167:E168"/>
@@ -42479,12 +47008,15 @@
     <mergeCell ref="L1544:O1544"/>
     <mergeCell ref="H690:J690"/>
     <mergeCell ref="L633:M633"/>
+    <mergeCell ref="B1853:E1853"/>
     <mergeCell ref="G1612:J1612"/>
     <mergeCell ref="M302:O302"/>
+    <mergeCell ref="G1770:J1770"/>
     <mergeCell ref="G1015:J1015"/>
     <mergeCell ref="G1307:J1307"/>
     <mergeCell ref="B665:E665"/>
     <mergeCell ref="H1446:J1446"/>
+    <mergeCell ref="H1888:J1888"/>
     <mergeCell ref="B1540:E1540"/>
     <mergeCell ref="B1515:E1515"/>
     <mergeCell ref="G582:J582"/>
@@ -42492,6 +47024,7 @@
     <mergeCell ref="L1547:O1547"/>
     <mergeCell ref="B1726:E1726"/>
     <mergeCell ref="H67:J67"/>
+    <mergeCell ref="H1890:J1890"/>
     <mergeCell ref="L813:O813"/>
     <mergeCell ref="H103:J103"/>
     <mergeCell ref="H672:J672"/>
@@ -42506,6 +47039,7 @@
     <mergeCell ref="H701:J701"/>
     <mergeCell ref="B839:E839"/>
     <mergeCell ref="B84:E84"/>
+    <mergeCell ref="H1891:J1891"/>
     <mergeCell ref="L1101:M1101"/>
     <mergeCell ref="L346:M346"/>
     <mergeCell ref="M172:O172"/>
@@ -42513,6 +47047,7 @@
     <mergeCell ref="G763:H763"/>
     <mergeCell ref="G1027:J1027"/>
     <mergeCell ref="B1566:E1566"/>
+    <mergeCell ref="L1828:M1828"/>
     <mergeCell ref="G1483:J1483"/>
     <mergeCell ref="L217:M217"/>
     <mergeCell ref="B1437:E1437"/>
@@ -42526,6 +47061,7 @@
     <mergeCell ref="G1493:J1494"/>
     <mergeCell ref="H456:J456"/>
     <mergeCell ref="H431:J431"/>
+    <mergeCell ref="H1813:J1813"/>
     <mergeCell ref="B381:E381"/>
     <mergeCell ref="H414:J414"/>
     <mergeCell ref="H1604:J1604"/>
@@ -42533,6 +47069,7 @@
     <mergeCell ref="H545:J545"/>
     <mergeCell ref="G1697:J1697"/>
     <mergeCell ref="G1543:H1543"/>
+    <mergeCell ref="H1815:J1815"/>
     <mergeCell ref="H1054:J1054"/>
     <mergeCell ref="M1705:O1705"/>
     <mergeCell ref="M977:O977"/>
@@ -42550,6 +47087,7 @@
     <mergeCell ref="H1499:J1499"/>
     <mergeCell ref="M1731:O1731"/>
     <mergeCell ref="B94:E94"/>
+    <mergeCell ref="M1758:O1758"/>
     <mergeCell ref="G1410:J1410"/>
     <mergeCell ref="L87:M87"/>
     <mergeCell ref="M120:O120"/>
@@ -42561,6 +47099,7 @@
     <mergeCell ref="H1528:J1528"/>
     <mergeCell ref="G1596:J1596"/>
     <mergeCell ref="H1659:J1659"/>
+    <mergeCell ref="B1937:E1937"/>
     <mergeCell ref="L765:O766"/>
     <mergeCell ref="H925:J925"/>
     <mergeCell ref="H48:J48"/>
@@ -42569,7 +47108,9 @@
     <mergeCell ref="G505:J506"/>
     <mergeCell ref="H14:J14"/>
     <mergeCell ref="B1211:E1211"/>
+    <mergeCell ref="G1854:H1854"/>
     <mergeCell ref="G682:J682"/>
+    <mergeCell ref="B1938:E1938"/>
     <mergeCell ref="B269:C269"/>
     <mergeCell ref="B145:E145"/>
     <mergeCell ref="L897:O897"/>
@@ -42607,6 +47148,8 @@
     <mergeCell ref="B163:E163"/>
     <mergeCell ref="M1341:O1341"/>
     <mergeCell ref="G1725:H1725"/>
+    <mergeCell ref="G1794:J1794"/>
+    <mergeCell ref="H1889:J1889"/>
     <mergeCell ref="B173:E173"/>
     <mergeCell ref="H1426:J1426"/>
     <mergeCell ref="G401:J402"/>
@@ -42620,6 +47163,7 @@
     <mergeCell ref="G63:J64"/>
     <mergeCell ref="G390:J390"/>
     <mergeCell ref="L1100:M1100"/>
+    <mergeCell ref="G1781:J1781"/>
     <mergeCell ref="M613:O613"/>
     <mergeCell ref="G997:H997"/>
     <mergeCell ref="H514:J514"/>
@@ -42638,16 +47182,20 @@
     <mergeCell ref="L1287:O1287"/>
     <mergeCell ref="L824:O824"/>
     <mergeCell ref="M614:O614"/>
+    <mergeCell ref="B1828:C1828"/>
     <mergeCell ref="B1415:E1416"/>
     <mergeCell ref="H1602:J1602"/>
     <mergeCell ref="B35:C35"/>
+    <mergeCell ref="H1894:J1894"/>
     <mergeCell ref="H1139:J1139"/>
     <mergeCell ref="G325:J325"/>
     <mergeCell ref="B1259:E1260"/>
     <mergeCell ref="G1378:J1378"/>
     <mergeCell ref="B1575:E1575"/>
+    <mergeCell ref="L1881:M1881"/>
     <mergeCell ref="L1126:M1126"/>
     <mergeCell ref="G1509:J1509"/>
+    <mergeCell ref="G1807:J1807"/>
     <mergeCell ref="L243:M243"/>
     <mergeCell ref="G318:J318"/>
     <mergeCell ref="L969:O969"/>
@@ -42673,10 +47221,13 @@
     <mergeCell ref="B1280:E1280"/>
     <mergeCell ref="H229:J229"/>
     <mergeCell ref="H1165:J1165"/>
+    <mergeCell ref="B1750:C1750"/>
     <mergeCell ref="L537:O537"/>
     <mergeCell ref="M1082:O1082"/>
+    <mergeCell ref="B1881:C1881"/>
     <mergeCell ref="H440:J440"/>
     <mergeCell ref="H1630:J1630"/>
+    <mergeCell ref="M1756:O1756"/>
     <mergeCell ref="H1167:J1167"/>
     <mergeCell ref="H439:J439"/>
     <mergeCell ref="B997:C997"/>
@@ -42684,6 +47235,7 @@
     <mergeCell ref="H1501:J1501"/>
     <mergeCell ref="B375:E376"/>
     <mergeCell ref="M1003:O1003"/>
+    <mergeCell ref="L1752:O1752"/>
     <mergeCell ref="G162:J162"/>
     <mergeCell ref="B579:E579"/>
     <mergeCell ref="G338:J338"/>
@@ -42705,9 +47257,11 @@
     <mergeCell ref="H1341:J1341"/>
     <mergeCell ref="H282:J282"/>
     <mergeCell ref="G1094:J1094"/>
+    <mergeCell ref="B1904:E1904"/>
     <mergeCell ref="L894:O894"/>
     <mergeCell ref="H1552:J1552"/>
     <mergeCell ref="B1594:C1594"/>
+    <mergeCell ref="G1821:J1821"/>
     <mergeCell ref="H153:J153"/>
     <mergeCell ref="H1343:J1343"/>
     <mergeCell ref="L169:O169"/>
@@ -42721,6 +47275,7 @@
     <mergeCell ref="B1595:C1595"/>
     <mergeCell ref="L8:M8"/>
     <mergeCell ref="B292:E292"/>
+    <mergeCell ref="G1879:J1879"/>
     <mergeCell ref="H1236:J1236"/>
     <mergeCell ref="M1472:O1472"/>
     <mergeCell ref="H179:J179"/>
@@ -42728,7 +47283,10 @@
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="L195:O195"/>
     <mergeCell ref="G392:J392"/>
+    <mergeCell ref="L1805:O1806"/>
     <mergeCell ref="L1677:O1677"/>
+    <mergeCell ref="G1752:J1752"/>
+    <mergeCell ref="G1874:J1874"/>
     <mergeCell ref="H1265:J1265"/>
     <mergeCell ref="H510:J510"/>
     <mergeCell ref="B917:E917"/>
@@ -42740,11 +47298,15 @@
     <mergeCell ref="H1267:J1267"/>
     <mergeCell ref="H512:J512"/>
     <mergeCell ref="G1022:H1022"/>
+    <mergeCell ref="H1863:J1863"/>
     <mergeCell ref="H49:J49"/>
     <mergeCell ref="H207:J207"/>
     <mergeCell ref="G866:H866"/>
+    <mergeCell ref="G1905:J1905"/>
+    <mergeCell ref="L1831:O1832"/>
     <mergeCell ref="B739:E740"/>
     <mergeCell ref="B189:E189"/>
+    <mergeCell ref="G1751:H1751"/>
     <mergeCell ref="G996:H996"/>
     <mergeCell ref="H1268:J1268"/>
     <mergeCell ref="G106:J106"/>
@@ -42771,6 +47333,7 @@
     <mergeCell ref="H227:J227"/>
     <mergeCell ref="G737:H737"/>
     <mergeCell ref="G1677:J1677"/>
+    <mergeCell ref="H1918:J1918"/>
     <mergeCell ref="H1709:J1709"/>
     <mergeCell ref="G1464:H1464"/>
     <mergeCell ref="H981:J981"/>
@@ -42790,6 +47353,8 @@
     <mergeCell ref="B3:O3"/>
     <mergeCell ref="L559:O559"/>
     <mergeCell ref="B875:E875"/>
+    <mergeCell ref="L1749:O1749"/>
+    <mergeCell ref="B1934:E1934"/>
     <mergeCell ref="B1421:E1421"/>
     <mergeCell ref="H278:J278"/>
     <mergeCell ref="H253:J253"/>
@@ -42800,6 +47365,7 @@
     <mergeCell ref="G1649:J1650"/>
     <mergeCell ref="L1593:O1593"/>
     <mergeCell ref="M1106:O1106"/>
+    <mergeCell ref="B1930:E1930"/>
     <mergeCell ref="B1473:E1473"/>
     <mergeCell ref="G1092:J1092"/>
     <mergeCell ref="H1637:J1637"/>
@@ -42837,6 +47403,7 @@
     <mergeCell ref="B1317:E1317"/>
     <mergeCell ref="H589:J589"/>
     <mergeCell ref="L920:O920"/>
+    <mergeCell ref="G1847:J1847"/>
     <mergeCell ref="M821:O821"/>
     <mergeCell ref="H1238:J1238"/>
     <mergeCell ref="B1647:C1647"/>
@@ -42864,7 +47431,9 @@
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="B1493:E1494"/>
     <mergeCell ref="H196:J196"/>
+    <mergeCell ref="M1783:O1783"/>
     <mergeCell ref="L1701:O1702"/>
+    <mergeCell ref="G1885:J1885"/>
     <mergeCell ref="B607:C607"/>
     <mergeCell ref="H618:J618"/>
     <mergeCell ref="B1543:C1543"/>
@@ -42881,8 +47450,10 @@
     <mergeCell ref="B1205:C1205"/>
     <mergeCell ref="B1056:E1056"/>
     <mergeCell ref="L1569:M1569"/>
+    <mergeCell ref="L1833:O1833"/>
     <mergeCell ref="H979:J979"/>
     <mergeCell ref="G1489:J1489"/>
+    <mergeCell ref="B1932:C1932"/>
     <mergeCell ref="H1706:J1706"/>
     <mergeCell ref="G886:J886"/>
     <mergeCell ref="G131:J131"/>
@@ -42906,6 +47477,7 @@
     <mergeCell ref="L43:O43"/>
     <mergeCell ref="M588:O588"/>
     <mergeCell ref="H1005:J1005"/>
+    <mergeCell ref="H1760:J1760"/>
     <mergeCell ref="B657:E657"/>
     <mergeCell ref="B42:E42"/>
     <mergeCell ref="B1127:C1127"/>
@@ -42917,6 +47489,7 @@
     <mergeCell ref="M924:O924"/>
     <mergeCell ref="B682:E682"/>
     <mergeCell ref="H1734:J1734"/>
+    <mergeCell ref="M1860:O1860"/>
     <mergeCell ref="L1135:O1135"/>
     <mergeCell ref="B1436:E1436"/>
     <mergeCell ref="L374:O374"/>
@@ -42931,12 +47504,14 @@
     <mergeCell ref="H718:J718"/>
     <mergeCell ref="H849:J849"/>
     <mergeCell ref="L1129:O1130"/>
+    <mergeCell ref="L1760:O1760"/>
     <mergeCell ref="H1663:J1663"/>
     <mergeCell ref="H1323:J1323"/>
     <mergeCell ref="H1445:J1445"/>
     <mergeCell ref="H929:J929"/>
     <mergeCell ref="B971:C971"/>
     <mergeCell ref="H1481:J1481"/>
+    <mergeCell ref="G1872:J1872"/>
     <mergeCell ref="H720:J720"/>
     <mergeCell ref="H1656:J1656"/>
     <mergeCell ref="H1316:J1316"/>
@@ -42946,8 +47521,10 @@
     <mergeCell ref="M93:O93"/>
     <mergeCell ref="G477:H477"/>
     <mergeCell ref="B814:C814"/>
+    <mergeCell ref="L1933:M1933"/>
     <mergeCell ref="G504:J504"/>
     <mergeCell ref="M820:O820"/>
+    <mergeCell ref="B1885:E1885"/>
     <mergeCell ref="B1151:E1151"/>
     <mergeCell ref="B274:E274"/>
     <mergeCell ref="B396:E396"/>
@@ -42960,6 +47537,7 @@
     <mergeCell ref="G1258:J1258"/>
     <mergeCell ref="L1359:O1359"/>
     <mergeCell ref="B267:E267"/>
+    <mergeCell ref="B1883:E1884"/>
     <mergeCell ref="H1376:J1376"/>
     <mergeCell ref="H621:J621"/>
     <mergeCell ref="B113:C113"/>
@@ -42970,16 +47548,21 @@
     <mergeCell ref="L1048:M1048"/>
     <mergeCell ref="G1287:J1287"/>
     <mergeCell ref="M874:O874"/>
+    <mergeCell ref="G1856:J1856"/>
+    <mergeCell ref="B1782:E1782"/>
     <mergeCell ref="H1369:J1369"/>
     <mergeCell ref="H310:J310"/>
     <mergeCell ref="H614:J614"/>
     <mergeCell ref="M1601:O1601"/>
     <mergeCell ref="H644:J644"/>
+    <mergeCell ref="H1834:J1834"/>
     <mergeCell ref="B325:E325"/>
     <mergeCell ref="L1646:M1646"/>
     <mergeCell ref="H1371:J1371"/>
     <mergeCell ref="H616:J616"/>
     <mergeCell ref="G1126:H1126"/>
+    <mergeCell ref="L1777:M1777"/>
+    <mergeCell ref="B1909:E1910"/>
     <mergeCell ref="G969:J969"/>
     <mergeCell ref="B327:E327"/>
     <mergeCell ref="G208:J208"/>
@@ -42992,9 +47575,11 @@
     <mergeCell ref="L738:O738"/>
     <mergeCell ref="B1054:E1054"/>
     <mergeCell ref="B1081:E1081"/>
+    <mergeCell ref="B1809:E1809"/>
     <mergeCell ref="G1313:J1313"/>
     <mergeCell ref="L1072:O1072"/>
     <mergeCell ref="G552:J552"/>
+    <mergeCell ref="B1808:E1808"/>
     <mergeCell ref="H1089:J1089"/>
     <mergeCell ref="H334:J334"/>
     <mergeCell ref="L767:O767"/>
@@ -43002,10 +47587,14 @@
     <mergeCell ref="B1083:E1083"/>
     <mergeCell ref="H486:J486"/>
     <mergeCell ref="G1613:J1613"/>
+    <mergeCell ref="B1810:E1810"/>
+    <mergeCell ref="G1911:J1911"/>
     <mergeCell ref="H1082:J1082"/>
+    <mergeCell ref="L1826:O1826"/>
     <mergeCell ref="M1314:O1314"/>
     <mergeCell ref="H363:J363"/>
     <mergeCell ref="B502:C502"/>
+    <mergeCell ref="H1845:J1845"/>
     <mergeCell ref="H1090:J1090"/>
     <mergeCell ref="G1183:J1183"/>
     <mergeCell ref="H1084:J1084"/>
@@ -43031,6 +47620,7 @@
     <mergeCell ref="L916:O916"/>
     <mergeCell ref="L188:O188"/>
     <mergeCell ref="L1214:O1214"/>
+    <mergeCell ref="L1852:O1852"/>
     <mergeCell ref="L65:O65"/>
     <mergeCell ref="H389:J389"/>
     <mergeCell ref="B796:E796"/>
@@ -43052,6 +47642,7 @@
     <mergeCell ref="H357:J357"/>
     <mergeCell ref="M483:O483"/>
     <mergeCell ref="H42:J42"/>
+    <mergeCell ref="L1889:O1889"/>
     <mergeCell ref="B793:E793"/>
     <mergeCell ref="M274:O274"/>
     <mergeCell ref="H716:J716"/>
@@ -43060,7 +47651,9 @@
     <mergeCell ref="L659:M659"/>
     <mergeCell ref="H411:J411"/>
     <mergeCell ref="H1741:J1741"/>
+    <mergeCell ref="B1879:E1879"/>
     <mergeCell ref="B67:E67"/>
+    <mergeCell ref="G1803:H1803"/>
     <mergeCell ref="G712:J712"/>
     <mergeCell ref="H1314:J1314"/>
     <mergeCell ref="B1698:C1698"/>
@@ -43074,6 +47667,7 @@
     <mergeCell ref="B970:C970"/>
     <mergeCell ref="B1576:E1576"/>
     <mergeCell ref="L1573:O1573"/>
+    <mergeCell ref="B1752:E1752"/>
     <mergeCell ref="L1567:O1567"/>
     <mergeCell ref="L839:O839"/>
     <mergeCell ref="L84:O84"/>
@@ -43090,12 +47684,14 @@
     <mergeCell ref="H744:J744"/>
     <mergeCell ref="H404:J404"/>
     <mergeCell ref="H727:J727"/>
+    <mergeCell ref="H1917:J1917"/>
     <mergeCell ref="M198:O198"/>
     <mergeCell ref="G789:H789"/>
     <mergeCell ref="B60:C60"/>
     <mergeCell ref="G1516:H1516"/>
     <mergeCell ref="H1342:J1342"/>
     <mergeCell ref="B996:C996"/>
+    <mergeCell ref="B1751:C1751"/>
     <mergeCell ref="B867:C867"/>
     <mergeCell ref="G39:J39"/>
     <mergeCell ref="L140:O140"/>
@@ -43115,13 +47711,17 @@
     <mergeCell ref="B407:E407"/>
     <mergeCell ref="L771:O771"/>
     <mergeCell ref="G1723:J1723"/>
+    <mergeCell ref="H1939:J1939"/>
     <mergeCell ref="H1184:J1184"/>
     <mergeCell ref="L10:O10"/>
     <mergeCell ref="H152:J152"/>
     <mergeCell ref="G937:J937"/>
     <mergeCell ref="G1569:H1569"/>
+    <mergeCell ref="H1816:J1816"/>
+    <mergeCell ref="H1841:J1841"/>
     <mergeCell ref="B1464:C1464"/>
     <mergeCell ref="B894:E894"/>
+    <mergeCell ref="H1843:J1843"/>
     <mergeCell ref="L1672:M1672"/>
     <mergeCell ref="B580:C580"/>
     <mergeCell ref="B711:C711"/>
@@ -43138,16 +47738,20 @@
     <mergeCell ref="G52:J52"/>
     <mergeCell ref="L449:O449"/>
     <mergeCell ref="H597:J597"/>
+    <mergeCell ref="G1749:J1749"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="G1024:J1024"/>
     <mergeCell ref="B1649:E1650"/>
+    <mergeCell ref="H1867:J1867"/>
     <mergeCell ref="H170:J170"/>
     <mergeCell ref="G1593:J1593"/>
     <mergeCell ref="G865:J865"/>
+    <mergeCell ref="M1757:O1757"/>
     <mergeCell ref="G1411:J1411"/>
     <mergeCell ref="H387:J387"/>
     <mergeCell ref="L478:O478"/>
     <mergeCell ref="L1053:O1053"/>
+    <mergeCell ref="H1869:J1869"/>
     <mergeCell ref="H172:J172"/>
     <mergeCell ref="H1114:J1114"/>
     <mergeCell ref="G1257:H1257"/>
@@ -43164,12 +47768,14 @@
     <mergeCell ref="B633:C633"/>
     <mergeCell ref="H382:J382"/>
     <mergeCell ref="L1543:M1543"/>
+    <mergeCell ref="H1870:J1870"/>
     <mergeCell ref="M1629:O1629"/>
     <mergeCell ref="G708:J708"/>
     <mergeCell ref="B1675:E1676"/>
     <mergeCell ref="B146:E146"/>
     <mergeCell ref="G1462:J1462"/>
     <mergeCell ref="G585:J585"/>
+    <mergeCell ref="B1852:E1852"/>
     <mergeCell ref="B820:E820"/>
     <mergeCell ref="B65:E65"/>
     <mergeCell ref="L1386:M1386"/>
@@ -43196,6 +47802,7 @@
     <mergeCell ref="L1233:O1234"/>
     <mergeCell ref="H97:J97"/>
     <mergeCell ref="B533:E533"/>
+    <mergeCell ref="B1863:E1863"/>
     <mergeCell ref="H824:J824"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="L136:O136"/>
@@ -43210,13 +47817,17 @@
     <mergeCell ref="B534:E534"/>
     <mergeCell ref="B745:E745"/>
     <mergeCell ref="G765:J766"/>
+    <mergeCell ref="H1941:J1941"/>
     <mergeCell ref="L1259:O1260"/>
     <mergeCell ref="H542:J542"/>
     <mergeCell ref="B536:E536"/>
     <mergeCell ref="H1478:J1478"/>
+    <mergeCell ref="L1882:O1882"/>
     <mergeCell ref="L1463:O1463"/>
+    <mergeCell ref="H1812:J1812"/>
     <mergeCell ref="H753:J753"/>
     <mergeCell ref="H535:J535"/>
+    <mergeCell ref="H1943:J1943"/>
     <mergeCell ref="L398:M398"/>
     <mergeCell ref="L425:M425"/>
     <mergeCell ref="H1480:J1480"/>
@@ -43226,6 +47837,7 @@
     <mergeCell ref="L1152:M1152"/>
     <mergeCell ref="G1542:H1542"/>
     <mergeCell ref="M978:O978"/>
+    <mergeCell ref="H1814:J1814"/>
     <mergeCell ref="G1053:J1053"/>
     <mergeCell ref="B429:E429"/>
     <mergeCell ref="G791:J792"/>
@@ -43233,6 +47845,8 @@
     <mergeCell ref="B247:E247"/>
     <mergeCell ref="G1536:J1536"/>
     <mergeCell ref="L578:O578"/>
+    <mergeCell ref="H1809:J1809"/>
+    <mergeCell ref="L1908:O1908"/>
     <mergeCell ref="L121:O121"/>
     <mergeCell ref="B431:E431"/>
     <mergeCell ref="H464:J464"/>
@@ -43241,7 +47855,9 @@
     <mergeCell ref="L273:O273"/>
     <mergeCell ref="L424:M424"/>
     <mergeCell ref="G348:J348"/>
+    <mergeCell ref="L1937:O1937"/>
     <mergeCell ref="L1178:M1178"/>
+    <mergeCell ref="B1907:C1907"/>
     <mergeCell ref="H466:J466"/>
     <mergeCell ref="L295:M295"/>
     <mergeCell ref="L579:O579"/>
@@ -43270,6 +47886,7 @@
     <mergeCell ref="L1235:O1235"/>
     <mergeCell ref="L1229:O1229"/>
     <mergeCell ref="H1553:J1553"/>
+    <mergeCell ref="M1810:O1810"/>
     <mergeCell ref="M1055:O1055"/>
     <mergeCell ref="G1129:J1130"/>
     <mergeCell ref="H493:J493"/>
@@ -43283,6 +47900,7 @@
     <mergeCell ref="G557:J558"/>
     <mergeCell ref="B477:C477"/>
     <mergeCell ref="G1178:H1178"/>
+    <mergeCell ref="G1933:H1933"/>
     <mergeCell ref="H1581:J1581"/>
     <mergeCell ref="G1724:H1724"/>
     <mergeCell ref="G761:J761"/>
@@ -43295,6 +47913,7 @@
     <mergeCell ref="G1155:J1156"/>
     <mergeCell ref="G1664:J1664"/>
     <mergeCell ref="L1703:O1703"/>
+    <mergeCell ref="G1900:J1900"/>
     <mergeCell ref="B1258:E1258"/>
     <mergeCell ref="G1359:J1359"/>
     <mergeCell ref="M768:O768"/>
@@ -43308,9 +47927,12 @@
     <mergeCell ref="H1609:J1609"/>
     <mergeCell ref="M1368:O1368"/>
     <mergeCell ref="H1294:J1294"/>
+    <mergeCell ref="G1777:H1777"/>
+    <mergeCell ref="G1804:J1804"/>
     <mergeCell ref="G893:H893"/>
     <mergeCell ref="H719:J719"/>
     <mergeCell ref="B373:C373"/>
+    <mergeCell ref="L1880:M1880"/>
     <mergeCell ref="G999:J1000"/>
     <mergeCell ref="G271:J272"/>
     <mergeCell ref="B1732:E1732"/>
@@ -43334,14 +47956,20 @@
     <mergeCell ref="H1322:J1322"/>
     <mergeCell ref="H561:J561"/>
     <mergeCell ref="B1152:C1152"/>
+    <mergeCell ref="B1758:E1758"/>
     <mergeCell ref="L999:O1000"/>
     <mergeCell ref="M1420:O1420"/>
     <mergeCell ref="G606:H606"/>
     <mergeCell ref="B86:C86"/>
     <mergeCell ref="G1131:J1131"/>
+    <mergeCell ref="H1920:J1920"/>
     <mergeCell ref="G370:J370"/>
+    <mergeCell ref="M1837:O1837"/>
     <mergeCell ref="L1049:M1049"/>
+    <mergeCell ref="L1775:O1775"/>
     <mergeCell ref="L427:O428"/>
+    <mergeCell ref="H1947:J1947"/>
+    <mergeCell ref="L1776:M1776"/>
     <mergeCell ref="G793:J793"/>
     <mergeCell ref="G167:J168"/>
     <mergeCell ref="G1431:J1431"/>
@@ -43363,12 +47991,15 @@
     <mergeCell ref="L1648:O1648"/>
     <mergeCell ref="H1035:J1035"/>
     <mergeCell ref="H1551:J1551"/>
+    <mergeCell ref="B1753:E1754"/>
     <mergeCell ref="H274:J274"/>
     <mergeCell ref="L164:M164"/>
+    <mergeCell ref="M1888:O1888"/>
     <mergeCell ref="H1246:J1246"/>
     <mergeCell ref="H491:J491"/>
     <mergeCell ref="G1308:H1308"/>
     <mergeCell ref="G1361:H1361"/>
+    <mergeCell ref="B1803:C1803"/>
     <mergeCell ref="B712:E712"/>
     <mergeCell ref="L762:M762"/>
     <mergeCell ref="B589:E589"/>
@@ -43392,12 +48023,14 @@
     <mergeCell ref="G84:J84"/>
     <mergeCell ref="B1229:E1229"/>
     <mergeCell ref="B197:E197"/>
+    <mergeCell ref="B1779:E1780"/>
     <mergeCell ref="G1146:J1146"/>
     <mergeCell ref="B1343:E1343"/>
     <mergeCell ref="H930:J930"/>
     <mergeCell ref="B924:E924"/>
     <mergeCell ref="H1088:J1088"/>
     <mergeCell ref="M847:O847"/>
+    <mergeCell ref="G1873:J1873"/>
     <mergeCell ref="H1264:J1264"/>
     <mergeCell ref="H509:J509"/>
     <mergeCell ref="G427:J428"/>
@@ -43443,6 +48076,8 @@
     <mergeCell ref="G130:J130"/>
     <mergeCell ref="B1082:E1082"/>
     <mergeCell ref="L1595:M1595"/>
+    <mergeCell ref="B1756:E1756"/>
+    <mergeCell ref="H1916:J1916"/>
     <mergeCell ref="H857:J857"/>
     <mergeCell ref="B995:E995"/>
     <mergeCell ref="H1191:J1191"/>
@@ -43451,18 +48086,22 @@
     <mergeCell ref="L556:O556"/>
     <mergeCell ref="G1673:H1673"/>
     <mergeCell ref="B1024:E1024"/>
+    <mergeCell ref="M1835:O1835"/>
     <mergeCell ref="B1593:E1593"/>
     <mergeCell ref="B1411:E1411"/>
+    <mergeCell ref="L1748:O1748"/>
     <mergeCell ref="G895:J896"/>
     <mergeCell ref="M378:O378"/>
     <mergeCell ref="B1257:C1257"/>
     <mergeCell ref="L1443:O1443"/>
+    <mergeCell ref="H1759:J1759"/>
     <mergeCell ref="L682:O682"/>
     <mergeCell ref="H1031:J1031"/>
     <mergeCell ref="H276:J276"/>
     <mergeCell ref="M1263:O1263"/>
     <mergeCell ref="M508:O508"/>
     <mergeCell ref="H1636:J1636"/>
+    <mergeCell ref="H1758:J1758"/>
     <mergeCell ref="H726:J726"/>
     <mergeCell ref="L555:M555"/>
     <mergeCell ref="H1033:J1033"/>
@@ -43470,14 +48109,18 @@
     <mergeCell ref="B1469:E1469"/>
     <mergeCell ref="H1629:J1629"/>
     <mergeCell ref="H570:J570"/>
+    <mergeCell ref="M1886:O1886"/>
     <mergeCell ref="G54:J54"/>
+    <mergeCell ref="H1787:J1787"/>
     <mergeCell ref="B251:E251"/>
+    <mergeCell ref="M1861:O1861"/>
     <mergeCell ref="G632:H632"/>
     <mergeCell ref="L400:O400"/>
     <mergeCell ref="H1631:J1631"/>
     <mergeCell ref="G1386:H1386"/>
     <mergeCell ref="B505:E506"/>
     <mergeCell ref="G1517:H1517"/>
+    <mergeCell ref="H1789:J1789"/>
     <mergeCell ref="H1028:J1028"/>
     <mergeCell ref="G214:J214"/>
     <mergeCell ref="L95:O95"/>
@@ -43486,6 +48129,7 @@
     <mergeCell ref="L1670:O1670"/>
     <mergeCell ref="B709:E709"/>
     <mergeCell ref="G468:J468"/>
+    <mergeCell ref="L1801:O1801"/>
     <mergeCell ref="L713:O714"/>
     <mergeCell ref="B1472:E1472"/>
     <mergeCell ref="H1059:J1059"/>
@@ -43499,11 +48143,13 @@
     <mergeCell ref="B582:E582"/>
     <mergeCell ref="M1187:O1187"/>
     <mergeCell ref="M432:O432"/>
+    <mergeCell ref="G1898:J1898"/>
     <mergeCell ref="M92:O92"/>
     <mergeCell ref="L426:O426"/>
     <mergeCell ref="H327:J327"/>
     <mergeCell ref="H1657:J1657"/>
     <mergeCell ref="H1682:J1682"/>
+    <mergeCell ref="M1914:O1914"/>
     <mergeCell ref="M1574:O1574"/>
     <mergeCell ref="H1684:J1684"/>
     <mergeCell ref="G652:J652"/>
@@ -43523,12 +48169,14 @@
     <mergeCell ref="B608:E608"/>
     <mergeCell ref="L1385:O1385"/>
     <mergeCell ref="L630:O630"/>
+    <mergeCell ref="G1924:J1924"/>
     <mergeCell ref="H772:J772"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="G444:J444"/>
     <mergeCell ref="L325:O325"/>
     <mergeCell ref="B765:E766"/>
     <mergeCell ref="L1231:M1231"/>
+    <mergeCell ref="G1926:J1926"/>
     <mergeCell ref="H774:J774"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="M145:O145"/>
@@ -43556,6 +48204,8 @@
     <mergeCell ref="L1098:O1098"/>
     <mergeCell ref="H485:J485"/>
     <mergeCell ref="M1630:O1630"/>
+    <mergeCell ref="G1908:J1908"/>
+    <mergeCell ref="G1768:J1768"/>
     <mergeCell ref="L501:O501"/>
     <mergeCell ref="L502:M502"/>
     <mergeCell ref="L944:M944"/>
@@ -43563,9 +48213,13 @@
     <mergeCell ref="B354:E354"/>
     <mergeCell ref="L1228:O1228"/>
     <mergeCell ref="B348:E348"/>
+    <mergeCell ref="H1886:J1886"/>
     <mergeCell ref="L345:O345"/>
     <mergeCell ref="G1639:J1639"/>
     <mergeCell ref="G884:J884"/>
+    <mergeCell ref="B1836:E1836"/>
+    <mergeCell ref="G1937:J1937"/>
+    <mergeCell ref="L1829:M1829"/>
     <mergeCell ref="H1002:J1002"/>
     <mergeCell ref="B1707:E1707"/>
     <mergeCell ref="H539:J539"/>
@@ -43582,6 +48236,7 @@
     <mergeCell ref="B1135:E1135"/>
     <mergeCell ref="B380:E380"/>
     <mergeCell ref="L371:O371"/>
+    <mergeCell ref="B1862:E1862"/>
     <mergeCell ref="G806:J806"/>
     <mergeCell ref="B1733:E1733"/>
     <mergeCell ref="G299:J299"/>
@@ -43598,6 +48253,7 @@
     <mergeCell ref="G599:J599"/>
     <mergeCell ref="G897:J897"/>
     <mergeCell ref="G1535:J1535"/>
+    <mergeCell ref="L1915:O1915"/>
     <mergeCell ref="G138:H138"/>
     <mergeCell ref="B377:E377"/>
     <mergeCell ref="L1154:O1154"/>
@@ -43605,6 +48261,7 @@
     <mergeCell ref="H594:J594"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="H1444:J1444"/>
+    <mergeCell ref="H1767:J1767"/>
     <mergeCell ref="H412:J412"/>
     <mergeCell ref="B242:C242"/>
     <mergeCell ref="H1655:J1655"/>
@@ -43615,11 +48272,14 @@
     <mergeCell ref="M1730:O1730"/>
     <mergeCell ref="B95:E95"/>
     <mergeCell ref="G221:J221"/>
+    <mergeCell ref="L1932:M1932"/>
     <mergeCell ref="G650:J650"/>
+    <mergeCell ref="L1941:O1941"/>
     <mergeCell ref="L1180:O1180"/>
     <mergeCell ref="G1255:J1255"/>
     <mergeCell ref="H768:J768"/>
     <mergeCell ref="G521:J521"/>
+    <mergeCell ref="L1785:O1785"/>
     <mergeCell ref="B693:E693"/>
     <mergeCell ref="L1337:O1338"/>
     <mergeCell ref="B1367:E1367"/>
@@ -43633,6 +48293,7 @@
     <mergeCell ref="H465:J465"/>
     <mergeCell ref="M224:O224"/>
     <mergeCell ref="G1250:J1250"/>
+    <mergeCell ref="L1935:O1936"/>
     <mergeCell ref="M118:O118"/>
     <mergeCell ref="H1368:J1368"/>
     <mergeCell ref="B1022:C1022"/>
@@ -43657,6 +48318,7 @@
     <mergeCell ref="B321:C321"/>
     <mergeCell ref="B319:E319"/>
     <mergeCell ref="H483:J483"/>
+    <mergeCell ref="B1807:E1807"/>
     <mergeCell ref="B1048:C1048"/>
     <mergeCell ref="B1046:E1046"/>
     <mergeCell ref="H1210:J1210"/>
@@ -43666,6 +48328,7 @@
     <mergeCell ref="H72:J72"/>
     <mergeCell ref="H1427:J1427"/>
     <mergeCell ref="H1421:J1421"/>
+    <mergeCell ref="H1842:J1842"/>
     <mergeCell ref="H326:J326"/>
     <mergeCell ref="H484:J484"/>
     <mergeCell ref="G994:J994"/>
@@ -43684,33 +48347,41 @@
     <mergeCell ref="G262:J262"/>
     <mergeCell ref="L1551:O1551"/>
     <mergeCell ref="B459:E459"/>
+    <mergeCell ref="H1756:J1756"/>
     <mergeCell ref="L62:O62"/>
     <mergeCell ref="B1133:E1133"/>
     <mergeCell ref="G989:J989"/>
     <mergeCell ref="L1699:M1699"/>
     <mergeCell ref="B1729:E1729"/>
     <mergeCell ref="G1050:J1050"/>
+    <mergeCell ref="B1860:E1860"/>
     <mergeCell ref="G1016:J1016"/>
     <mergeCell ref="B795:E795"/>
     <mergeCell ref="B162:E162"/>
     <mergeCell ref="L921:O922"/>
     <mergeCell ref="B1731:E1731"/>
+    <mergeCell ref="H1895:J1895"/>
     <mergeCell ref="H1140:J1140"/>
+    <mergeCell ref="B1889:E1889"/>
     <mergeCell ref="B1522:E1522"/>
     <mergeCell ref="G1648:J1648"/>
     <mergeCell ref="B763:C763"/>
     <mergeCell ref="L1125:O1125"/>
     <mergeCell ref="M638:O638"/>
+    <mergeCell ref="H1897:J1897"/>
     <mergeCell ref="H1142:J1142"/>
+    <mergeCell ref="L1879:O1879"/>
     <mergeCell ref="B485:E485"/>
     <mergeCell ref="H408:J408"/>
     <mergeCell ref="H383:J383"/>
     <mergeCell ref="M640:O640"/>
     <mergeCell ref="B1361:C1361"/>
+    <mergeCell ref="H1896:J1896"/>
     <mergeCell ref="H1135:J1135"/>
     <mergeCell ref="M1367:O1367"/>
     <mergeCell ref="L245:O246"/>
     <mergeCell ref="H410:J410"/>
+    <mergeCell ref="B1878:E1878"/>
     <mergeCell ref="B846:E846"/>
     <mergeCell ref="B91:E91"/>
     <mergeCell ref="B821:E821"/>
@@ -43729,6 +48400,7 @@
     <mergeCell ref="B689:E689"/>
     <mergeCell ref="H1166:J1166"/>
     <mergeCell ref="B1444:E1444"/>
+    <mergeCell ref="H1923:J1923"/>
     <mergeCell ref="H92:J92"/>
     <mergeCell ref="H434:J434"/>
     <mergeCell ref="B476:C476"/>
@@ -43744,6 +48416,7 @@
     <mergeCell ref="B849:E849"/>
     <mergeCell ref="H436:J436"/>
     <mergeCell ref="L1439:M1439"/>
+    <mergeCell ref="G1805:J1806"/>
     <mergeCell ref="G189:J189"/>
     <mergeCell ref="M353:O353"/>
     <mergeCell ref="H1163:J1163"/>
@@ -43765,6 +48438,7 @@
     <mergeCell ref="B114:E114"/>
     <mergeCell ref="L891:O891"/>
     <mergeCell ref="L1441:O1442"/>
+    <mergeCell ref="G1831:J1832"/>
     <mergeCell ref="B771:E771"/>
     <mergeCell ref="B404:E404"/>
     <mergeCell ref="L1645:O1645"/>
@@ -43788,12 +48462,15 @@
     <mergeCell ref="G556:J556"/>
     <mergeCell ref="L1365:O1365"/>
     <mergeCell ref="L604:O604"/>
+    <mergeCell ref="H1835:J1835"/>
     <mergeCell ref="G266:J266"/>
     <mergeCell ref="G260:J260"/>
     <mergeCell ref="H805:J805"/>
+    <mergeCell ref="G1748:J1748"/>
     <mergeCell ref="B895:E896"/>
     <mergeCell ref="G1145:J1145"/>
     <mergeCell ref="G1443:J1443"/>
+    <mergeCell ref="H1866:J1866"/>
     <mergeCell ref="B1518:E1518"/>
     <mergeCell ref="L605:O605"/>
     <mergeCell ref="H1263:J1263"/>
@@ -43805,6 +48482,7 @@
     <mergeCell ref="H352:J352"/>
     <mergeCell ref="H379:J379"/>
     <mergeCell ref="B786:E786"/>
+    <mergeCell ref="H1861:J1861"/>
     <mergeCell ref="H1106:J1106"/>
     <mergeCell ref="H47:J47"/>
     <mergeCell ref="B632:C632"/>
@@ -43815,6 +48493,7 @@
     <mergeCell ref="H76:J76"/>
     <mergeCell ref="B214:E214"/>
     <mergeCell ref="B1544:E1544"/>
+    <mergeCell ref="G1801:J1801"/>
     <mergeCell ref="G713:J714"/>
     <mergeCell ref="B1239:E1239"/>
     <mergeCell ref="B484:E484"/>
@@ -43837,14 +48516,17 @@
     <mergeCell ref="H1574:J1574"/>
     <mergeCell ref="H1195:J1195"/>
     <mergeCell ref="H94:J94"/>
+    <mergeCell ref="H1922:J1922"/>
     <mergeCell ref="M1681:O1681"/>
     <mergeCell ref="H1607:J1607"/>
     <mergeCell ref="H821:J821"/>
     <mergeCell ref="L1592:O1592"/>
     <mergeCell ref="B198:E198"/>
     <mergeCell ref="L711:M711"/>
+    <mergeCell ref="H1793:J1793"/>
     <mergeCell ref="G734:J734"/>
     <mergeCell ref="G1181:J1182"/>
+    <mergeCell ref="B1931:E1931"/>
     <mergeCell ref="B1101:C1101"/>
     <mergeCell ref="B346:C346"/>
     <mergeCell ref="B952:E952"/>
@@ -43855,8 +48537,10 @@
     <mergeCell ref="G1385:J1385"/>
     <mergeCell ref="G1311:J1312"/>
     <mergeCell ref="M794:O794"/>
+    <mergeCell ref="G1820:J1820"/>
     <mergeCell ref="L1309:M1309"/>
     <mergeCell ref="G27:J27"/>
+    <mergeCell ref="M1834:O1834"/>
     <mergeCell ref="B199:E199"/>
     <mergeCell ref="G1691:J1691"/>
     <mergeCell ref="H145:J145"/>
@@ -43870,6 +48554,7 @@
     <mergeCell ref="H147:J147"/>
     <mergeCell ref="H961:J961"/>
     <mergeCell ref="H1477:J1477"/>
+    <mergeCell ref="B1913:E1913"/>
     <mergeCell ref="H1635:J1635"/>
     <mergeCell ref="M1394:O1394"/>
     <mergeCell ref="B372:C372"/>
@@ -43881,9 +48566,11 @@
     <mergeCell ref="H1506:J1506"/>
     <mergeCell ref="B1644:E1644"/>
     <mergeCell ref="B399:C399"/>
+    <mergeCell ref="L1906:M1906"/>
     <mergeCell ref="H903:J903"/>
     <mergeCell ref="H148:J148"/>
     <mergeCell ref="G1646:H1646"/>
+    <mergeCell ref="B1908:E1908"/>
     <mergeCell ref="G816:J816"/>
     <mergeCell ref="B1441:E1442"/>
     <mergeCell ref="G501:J501"/>
@@ -43896,12 +48583,15 @@
     <mergeCell ref="B586:E586"/>
     <mergeCell ref="L1467:O1468"/>
     <mergeCell ref="B1645:E1645"/>
+    <mergeCell ref="L1907:M1907"/>
+    <mergeCell ref="G1833:J1833"/>
     <mergeCell ref="B1313:E1313"/>
     <mergeCell ref="G1072:J1072"/>
     <mergeCell ref="G1414:J1414"/>
     <mergeCell ref="M823:O823"/>
     <mergeCell ref="L583:O584"/>
     <mergeCell ref="L450:M450"/>
+    <mergeCell ref="B1939:E1939"/>
     <mergeCell ref="B1184:E1184"/>
     <mergeCell ref="G1571:J1572"/>
     <mergeCell ref="B425:C425"/>
@@ -43918,16 +48608,20 @@
     <mergeCell ref="L1179:M1179"/>
     <mergeCell ref="H1350:J1350"/>
     <mergeCell ref="L451:M451"/>
+    <mergeCell ref="H1946:J1946"/>
     <mergeCell ref="G371:J371"/>
     <mergeCell ref="H588:J588"/>
+    <mergeCell ref="L1802:M1802"/>
     <mergeCell ref="H647:J647"/>
     <mergeCell ref="G1432:J1432"/>
     <mergeCell ref="B299:E299"/>
     <mergeCell ref="B1629:E1629"/>
     <mergeCell ref="G1597:J1598"/>
     <mergeCell ref="L1232:O1232"/>
+    <mergeCell ref="B1781:E1781"/>
     <mergeCell ref="H613:J613"/>
     <mergeCell ref="L719:O719"/>
+    <mergeCell ref="L1778:O1778"/>
     <mergeCell ref="L1384:O1384"/>
     <mergeCell ref="L507:O507"/>
     <mergeCell ref="L1051:O1052"/>
@@ -43940,9 +48634,11 @@
     <mergeCell ref="G1154:J1154"/>
     <mergeCell ref="L500:O500"/>
     <mergeCell ref="H615:J615"/>
+    <mergeCell ref="B1933:C1933"/>
     <mergeCell ref="H1272:J1272"/>
     <mergeCell ref="H517:J517"/>
     <mergeCell ref="B899:E899"/>
+    <mergeCell ref="M1808:O1808"/>
     <mergeCell ref="L892:M892"/>
     <mergeCell ref="G1334:H1334"/>
     <mergeCell ref="M15:O15"/>
@@ -43953,6 +48649,7 @@
     <mergeCell ref="G243:H243"/>
     <mergeCell ref="H1730:J1730"/>
     <mergeCell ref="H1273:J1273"/>
+    <mergeCell ref="G1932:H1932"/>
     <mergeCell ref="B1051:E1052"/>
     <mergeCell ref="M744:O744"/>
     <mergeCell ref="G1599:J1599"/>
@@ -43974,6 +48671,7 @@
     <mergeCell ref="H205:J205"/>
     <mergeCell ref="H1420:J1420"/>
     <mergeCell ref="L39:O39"/>
+    <mergeCell ref="G1935:J1936"/>
     <mergeCell ref="L215:O215"/>
     <mergeCell ref="H1712:J1712"/>
     <mergeCell ref="G754:J754"/>
@@ -43990,9 +48688,11 @@
     <mergeCell ref="H986:J986"/>
     <mergeCell ref="G1198:J1198"/>
     <mergeCell ref="G443:J443"/>
+    <mergeCell ref="G1776:H1776"/>
     <mergeCell ref="M457:O457"/>
     <mergeCell ref="L998:O998"/>
     <mergeCell ref="G1048:H1048"/>
+    <mergeCell ref="G1925:J1925"/>
     <mergeCell ref="B968:E968"/>
     <mergeCell ref="G479:J480"/>
     <mergeCell ref="B978:E978"/>
@@ -44007,6 +48707,8 @@
     <mergeCell ref="B969:E969"/>
     <mergeCell ref="G169:J169"/>
     <mergeCell ref="H1740:J1740"/>
+    <mergeCell ref="B1941:E1941"/>
+    <mergeCell ref="G1802:H1802"/>
     <mergeCell ref="H1319:J1319"/>
     <mergeCell ref="B552:E552"/>
     <mergeCell ref="M1236:O1236"/>
@@ -44016,17 +48718,21 @@
     <mergeCell ref="H1346:J1346"/>
     <mergeCell ref="H612:J612"/>
     <mergeCell ref="G1128:J1128"/>
+    <mergeCell ref="G1826:J1826"/>
     <mergeCell ref="B691:E691"/>
+    <mergeCell ref="H1944:J1944"/>
     <mergeCell ref="G1699:H1699"/>
     <mergeCell ref="B270:E270"/>
     <mergeCell ref="G527:J527"/>
     <mergeCell ref="H586:J586"/>
     <mergeCell ref="H1370:J1370"/>
+    <mergeCell ref="L1774:O1774"/>
     <mergeCell ref="G1254:J1254"/>
     <mergeCell ref="G921:J922"/>
     <mergeCell ref="G1430:J1430"/>
     <mergeCell ref="B1654:E1654"/>
     <mergeCell ref="L1469:O1469"/>
+    <mergeCell ref="G1859:J1859"/>
     <mergeCell ref="H1372:J1372"/>
     <mergeCell ref="L708:O708"/>
     <mergeCell ref="H1032:J1032"/>
@@ -44036,6 +48742,7 @@
     <mergeCell ref="H909:J909"/>
     <mergeCell ref="M1289:O1289"/>
     <mergeCell ref="B1358:E1358"/>
+    <mergeCell ref="G1852:J1852"/>
     <mergeCell ref="L585:O585"/>
     <mergeCell ref="H1243:J1243"/>
     <mergeCell ref="B866:C866"/>
@@ -44043,23 +48750,29 @@
     <mergeCell ref="M405:O405"/>
     <mergeCell ref="H640:J640"/>
     <mergeCell ref="B1622:E1622"/>
+    <mergeCell ref="M1887:O1887"/>
     <mergeCell ref="M1132:O1132"/>
     <mergeCell ref="H1367:J1367"/>
     <mergeCell ref="B1681:E1681"/>
+    <mergeCell ref="L1800:O1800"/>
     <mergeCell ref="L13:O13"/>
     <mergeCell ref="G1412:H1412"/>
     <mergeCell ref="G240:J240"/>
     <mergeCell ref="G1570:J1570"/>
+    <mergeCell ref="L1827:O1827"/>
     <mergeCell ref="B735:E735"/>
+    <mergeCell ref="L1855:M1855"/>
     <mergeCell ref="B1384:E1384"/>
     <mergeCell ref="H1085:J1085"/>
     <mergeCell ref="H330:J330"/>
     <mergeCell ref="G838:J838"/>
     <mergeCell ref="B1648:E1648"/>
+    <mergeCell ref="M1913:O1913"/>
     <mergeCell ref="G235:J235"/>
     <mergeCell ref="G684:H684"/>
     <mergeCell ref="H201:J201"/>
     <mergeCell ref="H1087:J1087"/>
+    <mergeCell ref="B1805:E1806"/>
     <mergeCell ref="H1683:J1683"/>
     <mergeCell ref="M1160:O1160"/>
     <mergeCell ref="H1086:J1086"/>
@@ -44080,12 +48793,16 @@
     <mergeCell ref="B1395:E1395"/>
     <mergeCell ref="L1726:O1726"/>
     <mergeCell ref="B634:E634"/>
+    <mergeCell ref="B1831:E1832"/>
+    <mergeCell ref="G1950:J1950"/>
     <mergeCell ref="G136:J136"/>
     <mergeCell ref="L815:M815"/>
     <mergeCell ref="L351:O351"/>
     <mergeCell ref="L193:O194"/>
     <mergeCell ref="L1542:M1542"/>
+    <mergeCell ref="B1826:E1826"/>
     <mergeCell ref="G1197:J1197"/>
+    <mergeCell ref="G1952:J1952"/>
     <mergeCell ref="G555:H555"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="G1495:J1495"/>
@@ -44100,6 +48817,7 @@
     <mergeCell ref="H1317:J1317"/>
     <mergeCell ref="L995:O995"/>
     <mergeCell ref="H40:J40"/>
+    <mergeCell ref="H1913:J1913"/>
     <mergeCell ref="H1012:J1012"/>
     <mergeCell ref="B1150:E1150"/>
     <mergeCell ref="B817:E818"/>
@@ -44109,10 +48827,12 @@
     <mergeCell ref="B266:E266"/>
     <mergeCell ref="L528:M528"/>
     <mergeCell ref="G183:J183"/>
+    <mergeCell ref="B1748:E1748"/>
     <mergeCell ref="B1291:E1291"/>
     <mergeCell ref="G1671:J1671"/>
     <mergeCell ref="G1665:J1665"/>
     <mergeCell ref="G910:J910"/>
+    <mergeCell ref="B1837:E1837"/>
     <mergeCell ref="L110:O110"/>
     <mergeCell ref="L381:O381"/>
     <mergeCell ref="B864:E864"/>
@@ -44121,6 +48841,7 @@
     <mergeCell ref="G605:J605"/>
     <mergeCell ref="L715:O715"/>
     <mergeCell ref="G912:J912"/>
+    <mergeCell ref="B1749:E1749"/>
     <mergeCell ref="G451:H451"/>
     <mergeCell ref="G449:J449"/>
     <mergeCell ref="B690:E690"/>
@@ -44128,13 +48849,17 @@
     <mergeCell ref="G1508:J1508"/>
     <mergeCell ref="G1666:J1666"/>
     <mergeCell ref="H1030:J1030"/>
+    <mergeCell ref="H1757:J1757"/>
     <mergeCell ref="H725:J725"/>
     <mergeCell ref="L554:M554"/>
+    <mergeCell ref="H1915:J1915"/>
     <mergeCell ref="G209:J209"/>
     <mergeCell ref="H1452:J1452"/>
     <mergeCell ref="L397:O397"/>
     <mergeCell ref="G936:J936"/>
     <mergeCell ref="B1282:C1282"/>
+    <mergeCell ref="B1888:E1888"/>
+    <mergeCell ref="H1786:J1786"/>
     <mergeCell ref="G1541:J1541"/>
     <mergeCell ref="H1454:J1454"/>
     <mergeCell ref="L1283:M1283"/>
@@ -44145,10 +48870,12 @@
     <mergeCell ref="B531:E532"/>
     <mergeCell ref="G475:J475"/>
     <mergeCell ref="M639:O639"/>
+    <mergeCell ref="H1811:J1811"/>
     <mergeCell ref="H1056:J1056"/>
     <mergeCell ref="B1463:E1463"/>
     <mergeCell ref="B708:E708"/>
     <mergeCell ref="L557:O558"/>
+    <mergeCell ref="H1783:J1783"/>
     <mergeCell ref="G1561:J1561"/>
     <mergeCell ref="H751:J751"/>
     <mergeCell ref="B1158:E1158"/>
@@ -44160,8 +48887,10 @@
     <mergeCell ref="L761:O761"/>
     <mergeCell ref="L6:O6"/>
     <mergeCell ref="M1184:O1184"/>
+    <mergeCell ref="H1785:J1785"/>
     <mergeCell ref="M431:O431"/>
     <mergeCell ref="G351:J351"/>
+    <mergeCell ref="H1839:J1839"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="M1185:O1185"/>
     <mergeCell ref="G1592:J1592"/>
@@ -44170,6 +48899,7 @@
     <mergeCell ref="B734:E734"/>
     <mergeCell ref="B1489:E1489"/>
     <mergeCell ref="B1057:E1057"/>
+    <mergeCell ref="M1912:O1912"/>
     <mergeCell ref="G1438:H1438"/>
     <mergeCell ref="H955:J955"/>
     <mergeCell ref="G651:J651"/>
@@ -44178,17 +48908,21 @@
     <mergeCell ref="B1311:E1312"/>
     <mergeCell ref="H769:J769"/>
     <mergeCell ref="L481:O481"/>
+    <mergeCell ref="L1811:O1811"/>
     <mergeCell ref="L18:O18"/>
     <mergeCell ref="L322:O322"/>
     <mergeCell ref="G1274:J1274"/>
     <mergeCell ref="B1393:E1393"/>
     <mergeCell ref="L1519:O1520"/>
     <mergeCell ref="H796:J796"/>
+    <mergeCell ref="L1804:O1804"/>
     <mergeCell ref="B790:E790"/>
     <mergeCell ref="B1359:E1359"/>
+    <mergeCell ref="H1865:J1865"/>
     <mergeCell ref="L1079:O1079"/>
     <mergeCell ref="G1276:J1276"/>
     <mergeCell ref="G1618:J1618"/>
+    <mergeCell ref="M1782:O1782"/>
     <mergeCell ref="M899:O899"/>
     <mergeCell ref="M144:O144"/>
     <mergeCell ref="B1023:C1023"/>
@@ -44196,6 +48930,7 @@
     <mergeCell ref="B1388:E1388"/>
     <mergeCell ref="H1112:J1112"/>
     <mergeCell ref="H797:J797"/>
+    <mergeCell ref="M1784:O1784"/>
     <mergeCell ref="M1029:O1029"/>
     <mergeCell ref="L321:M321"/>
     <mergeCell ref="H668:J668"/>
@@ -44214,8 +48949,11 @@
     <mergeCell ref="B1106:E1106"/>
     <mergeCell ref="B351:E351"/>
     <mergeCell ref="B1228:E1228"/>
+    <mergeCell ref="G1880:H1880"/>
+    <mergeCell ref="G1907:H1907"/>
     <mergeCell ref="G1152:H1152"/>
     <mergeCell ref="H96:J96"/>
+    <mergeCell ref="B1833:E1833"/>
     <mergeCell ref="B1072:E1072"/>
     <mergeCell ref="B1414:E1414"/>
     <mergeCell ref="L1436:O1436"/>
@@ -44226,6 +48964,7 @@
     <mergeCell ref="G1638:J1638"/>
     <mergeCell ref="H1428:J1428"/>
     <mergeCell ref="L764:O764"/>
+    <mergeCell ref="B1835:E1835"/>
     <mergeCell ref="H667:J667"/>
     <mergeCell ref="H1580:J1580"/>
     <mergeCell ref="H825:J825"/>
@@ -44248,13 +48987,14 @@
     <mergeCell ref="M1680:O1680"/>
     <mergeCell ref="G295:H295"/>
     <mergeCell ref="M1340:O1340"/>
+    <mergeCell ref="H1782:J1782"/>
     <mergeCell ref="B1098:E1098"/>
     <mergeCell ref="B1134:E1134"/>
     <mergeCell ref="B379:E379"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" scale="52" fitToHeight="0" fitToWidth="1"/>
-  <rowBreaks count="66" manualBreakCount="66">
+  <rowBreaks count="74" manualBreakCount="74">
     <brk id="29" min="0" max="16383" man="1"/>
     <brk id="55" min="0" max="16383" man="1"/>
     <brk id="81" min="0" max="16383" man="1"/>
@@ -44321,6 +49061,14 @@
     <brk id="1667" min="0" max="16383" man="1"/>
     <brk id="1693" min="0" max="16383" man="1"/>
     <brk id="1719" min="0" max="16383" man="1"/>
+    <brk id="1745" min="0" max="16383" man="1"/>
+    <brk id="1771" min="0" max="16383" man="1"/>
+    <brk id="1797" min="0" max="16383" man="1"/>
+    <brk id="1823" min="0" max="16383" man="1"/>
+    <brk id="1849" min="0" max="16383" man="1"/>
+    <brk id="1875" min="0" max="16383" man="1"/>
+    <brk id="1901" min="0" max="16383" man="1"/>
+    <brk id="1927" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -44355,7 +49103,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>DEFINICIÓN DE LISTO (Definition of Ready)</t>
         </is>
@@ -44590,7 +49338,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="40" t="inlineStr">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>DEFINICIÓN DE TERMINADO (Definition of Done)</t>
         </is>
@@ -44810,7 +49558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E40"/>
+  <dimension ref="B2:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -44835,14 +49583,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>1. OBJETIVO DEL PRIMER SPRINT</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>Product owner: El objetivo del primer sprint es poder controlar los recursos de la obra: desde lo que pide el S10 hasta lo que se compra, se consume y cuesta.</t>
         </is>
@@ -44850,7 +49598,7 @@
     </row>
     <row r="7" ht="24" customHeight="1"/>
     <row r="9">
-      <c r="B9" s="41" t="inlineStr">
+      <c r="B9" s="42" t="inlineStr">
         <is>
           <t>2. LISTA DE HU QUE CUMPLEN CON EL OBJETIVO</t>
         </is>
@@ -44882,12 +49630,12 @@
       <c r="B11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="43" t="inlineStr">
+      <c r="C11" s="44" t="inlineStr">
         <is>
           <t>Loguear usuario</t>
         </is>
       </c>
-      <c r="D11" s="44" t="inlineStr">
+      <c r="D11" s="45" t="inlineStr">
         <is>
           <t>HU-12</t>
         </is>
@@ -44900,12 +49648,12 @@
       <c r="B12" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="43" t="inlineStr">
+      <c r="C12" s="44" t="inlineStr">
         <is>
           <t>Asignar roles</t>
         </is>
       </c>
-      <c r="D12" s="44" t="inlineStr">
+      <c r="D12" s="45" t="inlineStr">
         <is>
           <t>HU-13</t>
         </is>
@@ -44918,12 +49666,12 @@
       <c r="B13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="43" t="inlineStr">
+      <c r="C13" s="44" t="inlineStr">
         <is>
           <t>Asignar usuarios a obras</t>
         </is>
       </c>
-      <c r="D13" s="44" t="inlineStr">
+      <c r="D13" s="45" t="inlineStr">
         <is>
           <t>HU-14</t>
         </is>
@@ -44936,12 +49684,12 @@
       <c r="B14" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="43" t="inlineStr">
+      <c r="C14" s="44" t="inlineStr">
         <is>
           <t>Autorizar celular de la obra</t>
         </is>
       </c>
-      <c r="D14" s="44" t="inlineStr">
+      <c r="D14" s="45" t="inlineStr">
         <is>
           <t>HU-15</t>
         </is>
@@ -44954,12 +49702,12 @@
       <c r="B15" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="43" t="inlineStr">
+      <c r="C15" s="44" t="inlineStr">
         <is>
           <t>Crear proyecto</t>
         </is>
       </c>
-      <c r="D15" s="44" t="inlineStr">
+      <c r="D15" s="45" t="inlineStr">
         <is>
           <t>HU-01</t>
         </is>
@@ -44972,12 +49720,12 @@
       <c r="B16" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="C16" s="43" t="inlineStr">
+      <c r="C16" s="44" t="inlineStr">
         <is>
           <t>Reportar la obra en semanas</t>
         </is>
       </c>
-      <c r="D16" s="44" t="inlineStr">
+      <c r="D16" s="45" t="inlineStr">
         <is>
           <t>HU-03</t>
         </is>
@@ -44990,12 +49738,12 @@
       <c r="B17" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="C17" s="43" t="inlineStr">
+      <c r="C17" s="44" t="inlineStr">
         <is>
           <t>Importar catálogo de insumos del S10</t>
         </is>
       </c>
-      <c r="D17" s="44" t="inlineStr">
+      <c r="D17" s="45" t="inlineStr">
         <is>
           <t>HU-07</t>
         </is>
@@ -45008,12 +49756,12 @@
       <c r="B18" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="43" t="inlineStr">
+      <c r="C18" s="44" t="inlineStr">
         <is>
           <t>Registrar insumos</t>
         </is>
       </c>
-      <c r="D18" s="44" t="inlineStr">
+      <c r="D18" s="45" t="inlineStr">
         <is>
           <t>HU-08</t>
         </is>
@@ -45026,12 +49774,12 @@
       <c r="B19" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="C19" s="43" t="inlineStr">
+      <c r="C19" s="44" t="inlineStr">
         <is>
           <t>Importar precios unitarios</t>
         </is>
       </c>
-      <c r="D19" s="44" t="inlineStr">
+      <c r="D19" s="45" t="inlineStr">
         <is>
           <t>HU-16</t>
         </is>
@@ -45044,12 +49792,12 @@
       <c r="B20" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="C20" s="43" t="inlineStr">
+      <c r="C20" s="44" t="inlineStr">
         <is>
           <t>Convertir unidades (kg a varillas)</t>
         </is>
       </c>
-      <c r="D20" s="44" t="inlineStr">
+      <c r="D20" s="45" t="inlineStr">
         <is>
           <t>HU-17</t>
         </is>
@@ -45062,12 +49810,12 @@
       <c r="B21" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="C21" s="43" t="inlineStr">
+      <c r="C21" s="44" t="inlineStr">
         <is>
           <t>Importar requerimiento de la obra</t>
         </is>
       </c>
-      <c r="D21" s="44" t="inlineStr">
+      <c r="D21" s="45" t="inlineStr">
         <is>
           <t>HU-19</t>
         </is>
@@ -45080,12 +49828,12 @@
       <c r="B22" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="C22" s="43" t="inlineStr">
+      <c r="C22" s="44" t="inlineStr">
         <is>
           <t>Definir punto de reposición</t>
         </is>
       </c>
-      <c r="D22" s="44" t="inlineStr">
+      <c r="D22" s="45" t="inlineStr">
         <is>
           <t>HU-25</t>
         </is>
@@ -45098,12 +49846,12 @@
       <c r="B23" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="C23" s="43" t="inlineStr">
+      <c r="C23" s="44" t="inlineStr">
         <is>
           <t>Avisar cuándo reponer</t>
         </is>
       </c>
-      <c r="D23" s="44" t="inlineStr">
+      <c r="D23" s="45" t="inlineStr">
         <is>
           <t>HU-26</t>
         </is>
@@ -45116,12 +49864,12 @@
       <c r="B24" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="C24" s="43" t="inlineStr">
+      <c r="C24" s="44" t="inlineStr">
         <is>
           <t>Sugerir cuánto comprar</t>
         </is>
       </c>
-      <c r="D24" s="44" t="inlineStr">
+      <c r="D24" s="45" t="inlineStr">
         <is>
           <t>HU-27</t>
         </is>
@@ -45134,12 +49882,12 @@
       <c r="B25" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="C25" s="43" t="inlineStr">
+      <c r="C25" s="44" t="inlineStr">
         <is>
           <t>Consultar cuánto se compró y consumió</t>
         </is>
       </c>
-      <c r="D25" s="44" t="inlineStr">
+      <c r="D25" s="45" t="inlineStr">
         <is>
           <t>HU-23</t>
         </is>
@@ -45152,12 +49900,12 @@
       <c r="B26" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="C26" s="43" t="inlineStr">
+      <c r="C26" s="44" t="inlineStr">
         <is>
           <t>Consultar cuánto falta comprar</t>
         </is>
       </c>
-      <c r="D26" s="44" t="inlineStr">
+      <c r="D26" s="45" t="inlineStr">
         <is>
           <t>HU-24</t>
         </is>
@@ -45170,12 +49918,12 @@
       <c r="B27" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="C27" s="43" t="inlineStr">
+      <c r="C27" s="44" t="inlineStr">
         <is>
           <t>Consultar proveedores</t>
         </is>
       </c>
-      <c r="D27" s="44" t="inlineStr">
+      <c r="D27" s="45" t="inlineStr">
         <is>
           <t>HU-29</t>
         </is>
@@ -45188,12 +49936,12 @@
       <c r="B28" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="C28" s="43" t="inlineStr">
+      <c r="C28" s="44" t="inlineStr">
         <is>
           <t>Registrar proveedores</t>
         </is>
       </c>
-      <c r="D28" s="44" t="inlineStr">
+      <c r="D28" s="45" t="inlineStr">
         <is>
           <t>HU-30</t>
         </is>
@@ -45206,12 +49954,12 @@
       <c r="B29" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="C29" s="43" t="inlineStr">
+      <c r="C29" s="44" t="inlineStr">
         <is>
           <t>Registrar compras</t>
         </is>
       </c>
-      <c r="D29" s="44" t="inlineStr">
+      <c r="D29" s="45" t="inlineStr">
         <is>
           <t>HU-32</t>
         </is>
@@ -45224,12 +49972,12 @@
       <c r="B30" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="C30" s="43" t="inlineStr">
+      <c r="C30" s="44" t="inlineStr">
         <is>
           <t>Recibir compras</t>
         </is>
       </c>
-      <c r="D30" s="44" t="inlineStr">
+      <c r="D30" s="45" t="inlineStr">
         <is>
           <t>HU-35</t>
         </is>
@@ -45242,12 +49990,12 @@
       <c r="B31" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="C31" s="43" t="inlineStr">
+      <c r="C31" s="44" t="inlineStr">
         <is>
           <t>Registrar salidas de material</t>
         </is>
       </c>
-      <c r="D31" s="44" t="inlineStr">
+      <c r="D31" s="45" t="inlineStr">
         <is>
           <t>HU-40</t>
         </is>
@@ -45260,12 +50008,12 @@
       <c r="B32" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="C32" s="43" t="inlineStr">
+      <c r="C32" s="44" t="inlineStr">
         <is>
           <t>Registrar sin señal</t>
         </is>
       </c>
-      <c r="D32" s="44" t="inlineStr">
+      <c r="D32" s="45" t="inlineStr">
         <is>
           <t>HU-37</t>
         </is>
@@ -45278,12 +50026,12 @@
       <c r="B33" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="C33" s="43" t="inlineStr">
+      <c r="C33" s="44" t="inlineStr">
         <is>
           <t>Sincronizar pendientes</t>
         </is>
       </c>
-      <c r="D33" s="44" t="inlineStr">
+      <c r="D33" s="45" t="inlineStr">
         <is>
           <t>HU-38</t>
         </is>
@@ -45296,12 +50044,12 @@
       <c r="B34" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="C34" s="43" t="inlineStr">
+      <c r="C34" s="44" t="inlineStr">
         <is>
           <t>Consultar stock</t>
         </is>
       </c>
-      <c r="D34" s="44" t="inlineStr">
+      <c r="D34" s="45" t="inlineStr">
         <is>
           <t>HU-43</t>
         </is>
@@ -45314,12 +50062,12 @@
       <c r="B35" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="C35" s="43" t="inlineStr">
+      <c r="C35" s="44" t="inlineStr">
         <is>
           <t>Corregir movimientos</t>
         </is>
       </c>
-      <c r="D35" s="44" t="inlineStr">
+      <c r="D35" s="45" t="inlineStr">
         <is>
           <t>HU-45</t>
         </is>
@@ -45332,12 +50080,12 @@
       <c r="B36" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="C36" s="43" t="inlineStr">
+      <c r="C36" s="44" t="inlineStr">
         <is>
           <t>Valorizar salidas</t>
         </is>
       </c>
-      <c r="D36" s="44" t="inlineStr">
+      <c r="D36" s="45" t="inlineStr">
         <is>
           <t>HU-55</t>
         </is>
@@ -45350,12 +50098,12 @@
       <c r="B37" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="C37" s="43" t="inlineStr">
+      <c r="C37" s="44" t="inlineStr">
         <is>
           <t>Comparar consumo vs. lo planificado</t>
         </is>
       </c>
-      <c r="D37" s="44" t="inlineStr">
+      <c r="D37" s="45" t="inlineStr">
         <is>
           <t>HU-57</t>
         </is>
@@ -45368,12 +50116,12 @@
       <c r="B38" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="C38" s="43" t="inlineStr">
+      <c r="C38" s="44" t="inlineStr">
         <is>
           <t>Registrar trabajadores</t>
         </is>
       </c>
-      <c r="D38" s="44" t="inlineStr">
+      <c r="D38" s="45" t="inlineStr">
         <is>
           <t>HU-62</t>
         </is>
@@ -45386,12 +50134,12 @@
       <c r="B39" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="C39" s="43" t="inlineStr">
+      <c r="C39" s="44" t="inlineStr">
         <is>
           <t>Tomar asistencia</t>
         </is>
       </c>
-      <c r="D39" s="44" t="inlineStr">
+      <c r="D39" s="45" t="inlineStr">
         <is>
           <t>HU-63</t>
         </is>
@@ -45415,15 +50163,686 @@
         <v/>
       </c>
     </row>
+    <row r="42">
+      <c r="B42" s="42" t="inlineStr">
+        <is>
+          <t>3. HISTORIAS TÉCNICAS QUE HABILITAN EL OBJETIVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>N.°</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Historia técnica</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Puntos</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="44" t="inlineStr">
+        <is>
+          <t>Desplegar el ambiente de pruebas</t>
+        </is>
+      </c>
+      <c r="D44" s="45" t="inlineStr">
+        <is>
+          <t>HT-01</t>
+        </is>
+      </c>
+      <c r="E44" s="45" t="inlineStr">
+        <is>
+          <t>por votar</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" s="44" t="inlineStr">
+        <is>
+          <t>Configurar la integración continua</t>
+        </is>
+      </c>
+      <c r="D45" s="45" t="inlineStr">
+        <is>
+          <t>HT-02</t>
+        </is>
+      </c>
+      <c r="E45" s="45" t="inlineStr">
+        <is>
+          <t>por votar</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" s="44" t="inlineStr">
+        <is>
+          <t>Proteger el repositorio y main</t>
+        </is>
+      </c>
+      <c r="D46" s="45" t="inlineStr">
+        <is>
+          <t>HT-03</t>
+        </is>
+      </c>
+      <c r="E46" s="45" t="inlineStr">
+        <is>
+          <t>por votar</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" s="44" t="inlineStr">
+        <is>
+          <t>Conectar la web con la API real</t>
+        </is>
+      </c>
+      <c r="D47" s="45" t="inlineStr">
+        <is>
+          <t>HT-04</t>
+        </is>
+      </c>
+      <c r="E47" s="45" t="inlineStr">
+        <is>
+          <t>por votar</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C48" s="44" t="inlineStr">
+        <is>
+          <t>Crear la base de la app Android</t>
+        </is>
+      </c>
+      <c r="D48" s="45" t="inlineStr">
+        <is>
+          <t>HT-05</t>
+        </is>
+      </c>
+      <c r="E48" s="45" t="inlineStr">
+        <is>
+          <t>por votar</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C49" s="44" t="inlineStr">
+        <is>
+          <t>Publicar el contrato de la API y Postman</t>
+        </is>
+      </c>
+      <c r="D49" s="45" t="inlineStr">
+        <is>
+          <t>HT-06</t>
+        </is>
+      </c>
+      <c r="E49" s="45" t="inlineStr">
+        <is>
+          <t>por votar</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C50" s="44" t="inlineStr">
+        <is>
+          <t>Cargar los datos de prueba reales</t>
+        </is>
+      </c>
+      <c r="D50" s="45" t="inlineStr">
+        <is>
+          <t>HT-07</t>
+        </is>
+      </c>
+      <c r="E50" s="45" t="inlineStr">
+        <is>
+          <t>por votar</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C51" s="44" t="inlineStr">
+        <is>
+          <t>Autenticar a los servicios entre sí</t>
+        </is>
+      </c>
+      <c r="D51" s="45" t="inlineStr">
+        <is>
+          <t>HT-08</t>
+        </is>
+      </c>
+      <c r="E51" s="45" t="inlineStr">
+        <is>
+          <t>por votar</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B42:E42"/>
     <mergeCell ref="B6:E7"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:M16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>PRODUCT BACKLOG · Historias técnicas (habilitadoras)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Lo que el equipo necesita para que las HU de usuario se construyan, se prueben y se acepten · votación con Planning Poker en el próximo Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Historia técnica</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Qué destraba</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Nicolás</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Henry</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>MODA</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Puntaje</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>HT-01</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero un ambiente de pruebas desplegado con la API, la base de datos y la web, para que cada HU se pruebe y se acepte fuera de la máquina de quien la programó.</t>
+        </is>
+      </c>
+      <c r="D6" s="34" t="inlineStr">
+        <is>
+          <t>T8 de la DoD: sin esto ninguna HU llega a Done</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="G6" s="46" t="n"/>
+      <c r="H6" s="46" t="n"/>
+      <c r="I6" s="46" t="n"/>
+      <c r="J6" s="46" t="n"/>
+      <c r="K6" s="5">
+        <f>IFERROR(MODE(G6:J6),"por votar")</f>
+        <v/>
+      </c>
+      <c r="L6" s="11">
+        <f>K6</f>
+        <v/>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>HT-02</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero que cada Pull Request compile y corra las pruebas automáticamente, para detectar un error antes de que llegue a main.</t>
+        </is>
+      </c>
+      <c r="D7" s="34" t="inlineStr">
+        <is>
+          <t>T1 y T5 de la DoD</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="G7" s="46" t="n"/>
+      <c r="H7" s="46" t="n"/>
+      <c r="I7" s="46" t="n"/>
+      <c r="J7" s="46" t="n"/>
+      <c r="K7" s="5">
+        <f>IFERROR(MODE(G7:J7),"por votar")</f>
+        <v/>
+      </c>
+      <c r="L7" s="11">
+        <f>K7</f>
+        <v/>
+      </c>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>HT-03</t>
+        </is>
+      </c>
+      <c r="C8" s="34" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero el repositorio privado y la rama main protegida, para que los datos del cliente no queden expuestos y nada entre sin revisión.</t>
+        </is>
+      </c>
+      <c r="D8" s="34" t="inlineStr">
+        <is>
+          <t>T1 de la DoD y la confidencialidad de los datos de SEVENS</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="G8" s="46" t="n"/>
+      <c r="H8" s="46" t="n"/>
+      <c r="I8" s="46" t="n"/>
+      <c r="J8" s="46" t="n"/>
+      <c r="K8" s="5">
+        <f>IFERROR(MODE(G8:J8),"por votar")</f>
+        <v/>
+      </c>
+      <c r="L8" s="11">
+        <f>K8</f>
+        <v/>
+      </c>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>HT-04</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero un cliente HTTP único en la web que hable con la API, para conectar todas las pantallas sin rehacerlas.</t>
+        </is>
+      </c>
+      <c r="D9" s="34" t="inlineStr">
+        <is>
+          <t>Todas las tareas «Conectar con la API» de la web</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Henry</t>
+        </is>
+      </c>
+      <c r="G9" s="46" t="n"/>
+      <c r="H9" s="46" t="n"/>
+      <c r="I9" s="46" t="n"/>
+      <c r="J9" s="46" t="n"/>
+      <c r="K9" s="5">
+        <f>IFERROR(MODE(G9:J9),"por votar")</f>
+        <v/>
+      </c>
+      <c r="L9" s="11">
+        <f>K9</f>
+        <v/>
+      </c>
+      <c r="M9" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>HT-05</t>
+        </is>
+      </c>
+      <c r="C10" s="34" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero el proyecto base de la app con Compose, Room, WorkManager, sesión y cliente de la API, para construir encima las pantallas del almacenero.</t>
+        </is>
+      </c>
+      <c r="D10" s="34" t="inlineStr">
+        <is>
+          <t>Todas las HU de la app (HU-12, 15, 35, 37, 38, 40, 43, 62 y 63)</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Nicolás</t>
+        </is>
+      </c>
+      <c r="G10" s="46" t="n"/>
+      <c r="H10" s="46" t="n"/>
+      <c r="I10" s="46" t="n"/>
+      <c r="J10" s="46" t="n"/>
+      <c r="K10" s="5">
+        <f>IFERROR(MODE(G10:J10),"por votar")</f>
+        <v/>
+      </c>
+      <c r="L10" s="11">
+        <f>K10</f>
+        <v/>
+      </c>
+      <c r="M10" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>HT-06</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero el contrato de la API publicado (OpenAPI) y una colección de Postman compartida, para probar cada endpoint igual y sin adivinar cómo llamarlo.</t>
+        </is>
+      </c>
+      <c r="D11" s="34" t="inlineStr">
+        <is>
+          <t>La prueba con Postman de cada HU (modelo del docente)</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="G11" s="46" t="n"/>
+      <c r="H11" s="46" t="n"/>
+      <c r="I11" s="46" t="n"/>
+      <c r="J11" s="46" t="n"/>
+      <c r="K11" s="5">
+        <f>IFERROR(MODE(G11:J11),"por votar")</f>
+        <v/>
+      </c>
+      <c r="L11" s="11">
+        <f>K11</f>
+        <v/>
+      </c>
+      <c r="M11" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>HT-07</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero la base de pruebas cargada con los datos reales del cliente, para que ninguna HU se pruebe con datos inventados.</t>
+        </is>
+      </c>
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>L8 de la DoR y las pruebas de importación</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="G12" s="46" t="n"/>
+      <c r="H12" s="46" t="n"/>
+      <c r="I12" s="46" t="n"/>
+      <c r="J12" s="46" t="n"/>
+      <c r="K12" s="5">
+        <f>IFERROR(MODE(G12:J12),"por votar")</f>
+        <v/>
+      </c>
+      <c r="L12" s="11">
+        <f>K12</f>
+        <v/>
+      </c>
+      <c r="M12" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>HT-08</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero que Integraciones y Notificaciones solo atiendan a la API con un token de servicio, para que nadie gaste las consultas de Factiliza ni envíe avisos falsos.</t>
+        </is>
+      </c>
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>La seguridad de las integraciones (incidencia del 22/10)</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="G13" s="46" t="n"/>
+      <c r="H13" s="46" t="n"/>
+      <c r="I13" s="46" t="n"/>
+      <c r="J13" s="46" t="n"/>
+      <c r="K13" s="5">
+        <f>IFERROR(MODE(G13:J13),"por votar")</f>
+        <v/>
+      </c>
+      <c r="L13" s="11">
+        <f>K13</f>
+        <v/>
+      </c>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L14" s="11">
+        <f>SUM(L6:L13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Cada integrante escribe su carta (1, 2, 3, 5, 8 o 13) en su columna; la MODA y el puntaje se calculan solos. Si el máximo y el mínimo se separan más de dos valores de la serie, se explica y se revota.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B16:M16"/>
+    <mergeCell ref="B2:M2"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>